--- a/cari acik/odemeler_dengesi_raw.xlsx
+++ b/cari acik/odemeler_dengesi_raw.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,96 +429,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R199"/>
+  <dimension ref="A1:R200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Cari İşlemler Dengesi</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Dış Ticaret Dengesi</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Toplam Mal İhracatı</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Toplam Mal İthalatı</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Parasal Olmayan Altın (net)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Altın İhracatı</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Altın İthalatı</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Hizmetler Dengesi</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Hizmet Gelirleri</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Hizmet Giderleri</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Taşımacılık - Gelir</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Taşımacılık - Gider</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Seyahat - Gelir</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Seyahat - Gider</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Birincil Gelir Dengesi</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>İkincil Gelir Dengesi</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Tarih_dt</t>
         </is>
@@ -566,7 +578,7 @@
       <c r="Q2" t="n">
         <v>115</v>
       </c>
-      <c r="R2" s="1" t="n">
+      <c r="R2" s="2" t="n">
         <v>40179</v>
       </c>
     </row>
@@ -624,7 +636,7 @@
       <c r="Q3" t="n">
         <v>72</v>
       </c>
-      <c r="R3" s="1" t="n">
+      <c r="R3" s="2" t="n">
         <v>40210</v>
       </c>
     </row>
@@ -682,7 +694,7 @@
       <c r="Q4" t="n">
         <v>114</v>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="R4" s="2" t="n">
         <v>40238</v>
       </c>
     </row>
@@ -740,7 +752,7 @@
       <c r="Q5" t="n">
         <v>82</v>
       </c>
-      <c r="R5" s="1" t="n">
+      <c r="R5" s="2" t="n">
         <v>40269</v>
       </c>
     </row>
@@ -798,7 +810,7 @@
       <c r="Q6" t="n">
         <v>73</v>
       </c>
-      <c r="R6" s="1" t="n">
+      <c r="R6" s="2" t="n">
         <v>40299</v>
       </c>
     </row>
@@ -856,7 +868,7 @@
       <c r="Q7" t="n">
         <v>121</v>
       </c>
-      <c r="R7" s="1" t="n">
+      <c r="R7" s="2" t="n">
         <v>40330</v>
       </c>
     </row>
@@ -914,7 +926,7 @@
       <c r="Q8" t="n">
         <v>109</v>
       </c>
-      <c r="R8" s="1" t="n">
+      <c r="R8" s="2" t="n">
         <v>40360</v>
       </c>
     </row>
@@ -972,7 +984,7 @@
       <c r="Q9" t="n">
         <v>155</v>
       </c>
-      <c r="R9" s="1" t="n">
+      <c r="R9" s="2" t="n">
         <v>40391</v>
       </c>
     </row>
@@ -1030,7 +1042,7 @@
       <c r="Q10" t="n">
         <v>159</v>
       </c>
-      <c r="R10" s="1" t="n">
+      <c r="R10" s="2" t="n">
         <v>40422</v>
       </c>
     </row>
@@ -1088,7 +1100,7 @@
       <c r="Q11" t="n">
         <v>183</v>
       </c>
-      <c r="R11" s="1" t="n">
+      <c r="R11" s="2" t="n">
         <v>40452</v>
       </c>
     </row>
@@ -1146,7 +1158,7 @@
       <c r="Q12" t="n">
         <v>100</v>
       </c>
-      <c r="R12" s="1" t="n">
+      <c r="R12" s="2" t="n">
         <v>40483</v>
       </c>
     </row>
@@ -1204,7 +1216,7 @@
       <c r="Q13" t="n">
         <v>192</v>
       </c>
-      <c r="R13" s="1" t="n">
+      <c r="R13" s="2" t="n">
         <v>40513</v>
       </c>
     </row>
@@ -1262,7 +1274,7 @@
       <c r="Q14" t="n">
         <v>222</v>
       </c>
-      <c r="R14" s="1" t="n">
+      <c r="R14" s="2" t="n">
         <v>40544</v>
       </c>
     </row>
@@ -1320,7 +1332,7 @@
       <c r="Q15" t="n">
         <v>85</v>
       </c>
-      <c r="R15" s="1" t="n">
+      <c r="R15" s="2" t="n">
         <v>40575</v>
       </c>
     </row>
@@ -1378,7 +1390,7 @@
       <c r="Q16" t="n">
         <v>77</v>
       </c>
-      <c r="R16" s="1" t="n">
+      <c r="R16" s="2" t="n">
         <v>40603</v>
       </c>
     </row>
@@ -1436,7 +1448,7 @@
       <c r="Q17" t="n">
         <v>49</v>
       </c>
-      <c r="R17" s="1" t="n">
+      <c r="R17" s="2" t="n">
         <v>40634</v>
       </c>
     </row>
@@ -1494,7 +1506,7 @@
       <c r="Q18" t="n">
         <v>139</v>
       </c>
-      <c r="R18" s="1" t="n">
+      <c r="R18" s="2" t="n">
         <v>40664</v>
       </c>
     </row>
@@ -1552,7 +1564,7 @@
       <c r="Q19" t="n">
         <v>99</v>
       </c>
-      <c r="R19" s="1" t="n">
+      <c r="R19" s="2" t="n">
         <v>40695</v>
       </c>
     </row>
@@ -1610,7 +1622,7 @@
       <c r="Q20" t="n">
         <v>103</v>
       </c>
-      <c r="R20" s="1" t="n">
+      <c r="R20" s="2" t="n">
         <v>40725</v>
       </c>
     </row>
@@ -1668,7 +1680,7 @@
       <c r="Q21" t="n">
         <v>241</v>
       </c>
-      <c r="R21" s="1" t="n">
+      <c r="R21" s="2" t="n">
         <v>40756</v>
       </c>
     </row>
@@ -1726,7 +1738,7 @@
       <c r="Q22" t="n">
         <v>149</v>
       </c>
-      <c r="R22" s="1" t="n">
+      <c r="R22" s="2" t="n">
         <v>40787</v>
       </c>
     </row>
@@ -1784,7 +1796,7 @@
       <c r="Q23" t="n">
         <v>67</v>
       </c>
-      <c r="R23" s="1" t="n">
+      <c r="R23" s="2" t="n">
         <v>40817</v>
       </c>
     </row>
@@ -1842,7 +1854,7 @@
       <c r="Q24" t="n">
         <v>106</v>
       </c>
-      <c r="R24" s="1" t="n">
+      <c r="R24" s="2" t="n">
         <v>40848</v>
       </c>
     </row>
@@ -1900,7 +1912,7 @@
       <c r="Q25" t="n">
         <v>382</v>
       </c>
-      <c r="R25" s="1" t="n">
+      <c r="R25" s="2" t="n">
         <v>40878</v>
       </c>
     </row>
@@ -1958,7 +1970,7 @@
       <c r="Q26" t="n">
         <v>69</v>
       </c>
-      <c r="R26" s="1" t="n">
+      <c r="R26" s="2" t="n">
         <v>40909</v>
       </c>
     </row>
@@ -2016,7 +2028,7 @@
       <c r="Q27" t="n">
         <v>224</v>
       </c>
-      <c r="R27" s="1" t="n">
+      <c r="R27" s="2" t="n">
         <v>40940</v>
       </c>
     </row>
@@ -2074,7 +2086,7 @@
       <c r="Q28" t="n">
         <v>57</v>
       </c>
-      <c r="R28" s="1" t="n">
+      <c r="R28" s="2" t="n">
         <v>40969</v>
       </c>
     </row>
@@ -2132,7 +2144,7 @@
       <c r="Q29" t="n">
         <v>105</v>
       </c>
-      <c r="R29" s="1" t="n">
+      <c r="R29" s="2" t="n">
         <v>41000</v>
       </c>
     </row>
@@ -2190,7 +2202,7 @@
       <c r="Q30" t="n">
         <v>90</v>
       </c>
-      <c r="R30" s="1" t="n">
+      <c r="R30" s="2" t="n">
         <v>41030</v>
       </c>
     </row>
@@ -2248,7 +2260,7 @@
       <c r="Q31" t="n">
         <v>73</v>
       </c>
-      <c r="R31" s="1" t="n">
+      <c r="R31" s="2" t="n">
         <v>41061</v>
       </c>
     </row>
@@ -2306,7 +2318,7 @@
       <c r="Q32" t="n">
         <v>72</v>
       </c>
-      <c r="R32" s="1" t="n">
+      <c r="R32" s="2" t="n">
         <v>41091</v>
       </c>
     </row>
@@ -2364,7 +2376,7 @@
       <c r="Q33" t="n">
         <v>156</v>
       </c>
-      <c r="R33" s="1" t="n">
+      <c r="R33" s="2" t="n">
         <v>41122</v>
       </c>
     </row>
@@ -2422,7 +2434,7 @@
       <c r="Q34" t="n">
         <v>122</v>
       </c>
-      <c r="R34" s="1" t="n">
+      <c r="R34" s="2" t="n">
         <v>41153</v>
       </c>
     </row>
@@ -2480,7 +2492,7 @@
       <c r="Q35" t="n">
         <v>89</v>
       </c>
-      <c r="R35" s="1" t="n">
+      <c r="R35" s="2" t="n">
         <v>41183</v>
       </c>
     </row>
@@ -2538,7 +2550,7 @@
       <c r="Q36" t="n">
         <v>116</v>
       </c>
-      <c r="R36" s="1" t="n">
+      <c r="R36" s="2" t="n">
         <v>41214</v>
       </c>
     </row>
@@ -2596,7 +2608,7 @@
       <c r="Q37" t="n">
         <v>278</v>
       </c>
-      <c r="R37" s="1" t="n">
+      <c r="R37" s="2" t="n">
         <v>41244</v>
       </c>
     </row>
@@ -2654,7 +2666,7 @@
       <c r="Q38" t="n">
         <v>49</v>
       </c>
-      <c r="R38" s="1" t="n">
+      <c r="R38" s="2" t="n">
         <v>41275</v>
       </c>
     </row>
@@ -2712,7 +2724,7 @@
       <c r="Q39" t="n">
         <v>161</v>
       </c>
-      <c r="R39" s="1" t="n">
+      <c r="R39" s="2" t="n">
         <v>41306</v>
       </c>
     </row>
@@ -2770,7 +2782,7 @@
       <c r="Q40" t="n">
         <v>66</v>
       </c>
-      <c r="R40" s="1" t="n">
+      <c r="R40" s="2" t="n">
         <v>41334</v>
       </c>
     </row>
@@ -2828,7 +2840,7 @@
       <c r="Q41" t="n">
         <v>45</v>
       </c>
-      <c r="R41" s="1" t="n">
+      <c r="R41" s="2" t="n">
         <v>41365</v>
       </c>
     </row>
@@ -2886,7 +2898,7 @@
       <c r="Q42" t="n">
         <v>159</v>
       </c>
-      <c r="R42" s="1" t="n">
+      <c r="R42" s="2" t="n">
         <v>41395</v>
       </c>
     </row>
@@ -2944,7 +2956,7 @@
       <c r="Q43" t="n">
         <v>92</v>
       </c>
-      <c r="R43" s="1" t="n">
+      <c r="R43" s="2" t="n">
         <v>41426</v>
       </c>
     </row>
@@ -3002,7 +3014,7 @@
       <c r="Q44" t="n">
         <v>107</v>
       </c>
-      <c r="R44" s="1" t="n">
+      <c r="R44" s="2" t="n">
         <v>41456</v>
       </c>
     </row>
@@ -3060,7 +3072,7 @@
       <c r="Q45" t="n">
         <v>108</v>
       </c>
-      <c r="R45" s="1" t="n">
+      <c r="R45" s="2" t="n">
         <v>41487</v>
       </c>
     </row>
@@ -3118,7 +3130,7 @@
       <c r="Q46" t="n">
         <v>110</v>
       </c>
-      <c r="R46" s="1" t="n">
+      <c r="R46" s="2" t="n">
         <v>41518</v>
       </c>
     </row>
@@ -3176,7 +3188,7 @@
       <c r="Q47" t="n">
         <v>113</v>
       </c>
-      <c r="R47" s="1" t="n">
+      <c r="R47" s="2" t="n">
         <v>41548</v>
       </c>
     </row>
@@ -3234,7 +3246,7 @@
       <c r="Q48" t="n">
         <v>115</v>
       </c>
-      <c r="R48" s="1" t="n">
+      <c r="R48" s="2" t="n">
         <v>41579</v>
       </c>
     </row>
@@ -3292,7 +3304,7 @@
       <c r="Q49" t="n">
         <v>152</v>
       </c>
-      <c r="R49" s="1" t="n">
+      <c r="R49" s="2" t="n">
         <v>41609</v>
       </c>
     </row>
@@ -3350,7 +3362,7 @@
       <c r="Q50" t="n">
         <v>35</v>
       </c>
-      <c r="R50" s="1" t="n">
+      <c r="R50" s="2" t="n">
         <v>41640</v>
       </c>
     </row>
@@ -3408,7 +3420,7 @@
       <c r="Q51" t="n">
         <v>157</v>
       </c>
-      <c r="R51" s="1" t="n">
+      <c r="R51" s="2" t="n">
         <v>41671</v>
       </c>
     </row>
@@ -3466,7 +3478,7 @@
       <c r="Q52" t="n">
         <v>222</v>
       </c>
-      <c r="R52" s="1" t="n">
+      <c r="R52" s="2" t="n">
         <v>41699</v>
       </c>
     </row>
@@ -3524,7 +3536,7 @@
       <c r="Q53" t="n">
         <v>37</v>
       </c>
-      <c r="R53" s="1" t="n">
+      <c r="R53" s="2" t="n">
         <v>41730</v>
       </c>
     </row>
@@ -3582,7 +3594,7 @@
       <c r="Q54" t="n">
         <v>86</v>
       </c>
-      <c r="R54" s="1" t="n">
+      <c r="R54" s="2" t="n">
         <v>41760</v>
       </c>
     </row>
@@ -3640,7 +3652,7 @@
       <c r="Q55" t="n">
         <v>111</v>
       </c>
-      <c r="R55" s="1" t="n">
+      <c r="R55" s="2" t="n">
         <v>41791</v>
       </c>
     </row>
@@ -3698,7 +3710,7 @@
       <c r="Q56" t="n">
         <v>19</v>
       </c>
-      <c r="R56" s="1" t="n">
+      <c r="R56" s="2" t="n">
         <v>41821</v>
       </c>
     </row>
@@ -3756,7 +3768,7 @@
       <c r="Q57" t="n">
         <v>121</v>
       </c>
-      <c r="R57" s="1" t="n">
+      <c r="R57" s="2" t="n">
         <v>41852</v>
       </c>
     </row>
@@ -3814,7 +3826,7 @@
       <c r="Q58" t="n">
         <v>263</v>
       </c>
-      <c r="R58" s="1" t="n">
+      <c r="R58" s="2" t="n">
         <v>41883</v>
       </c>
     </row>
@@ -3872,7 +3884,7 @@
       <c r="Q59" t="n">
         <v>88</v>
       </c>
-      <c r="R59" s="1" t="n">
+      <c r="R59" s="2" t="n">
         <v>41913</v>
       </c>
     </row>
@@ -3930,7 +3942,7 @@
       <c r="Q60" t="n">
         <v>169</v>
       </c>
-      <c r="R60" s="1" t="n">
+      <c r="R60" s="2" t="n">
         <v>41944</v>
       </c>
     </row>
@@ -3988,7 +4000,7 @@
       <c r="Q61" t="n">
         <v>212</v>
       </c>
-      <c r="R61" s="1" t="n">
+      <c r="R61" s="2" t="n">
         <v>41974</v>
       </c>
     </row>
@@ -4046,7 +4058,7 @@
       <c r="Q62" t="n">
         <v>15</v>
       </c>
-      <c r="R62" s="1" t="n">
+      <c r="R62" s="2" t="n">
         <v>42005</v>
       </c>
     </row>
@@ -4104,7 +4116,7 @@
       <c r="Q63" t="n">
         <v>231</v>
       </c>
-      <c r="R63" s="1" t="n">
+      <c r="R63" s="2" t="n">
         <v>42036</v>
       </c>
     </row>
@@ -4162,7 +4174,7 @@
       <c r="Q64" t="n">
         <v>145</v>
       </c>
-      <c r="R64" s="1" t="n">
+      <c r="R64" s="2" t="n">
         <v>42064</v>
       </c>
     </row>
@@ -4220,7 +4232,7 @@
       <c r="Q65" t="n">
         <v>62</v>
       </c>
-      <c r="R65" s="1" t="n">
+      <c r="R65" s="2" t="n">
         <v>42095</v>
       </c>
     </row>
@@ -4278,7 +4290,7 @@
       <c r="Q66" t="n">
         <v>21</v>
       </c>
-      <c r="R66" s="1" t="n">
+      <c r="R66" s="2" t="n">
         <v>42125</v>
       </c>
     </row>
@@ -4336,7 +4348,7 @@
       <c r="Q67" t="n">
         <v>86</v>
       </c>
-      <c r="R67" s="1" t="n">
+      <c r="R67" s="2" t="n">
         <v>42156</v>
       </c>
     </row>
@@ -4394,7 +4406,7 @@
       <c r="Q68" t="n">
         <v>125</v>
       </c>
-      <c r="R68" s="1" t="n">
+      <c r="R68" s="2" t="n">
         <v>42186</v>
       </c>
     </row>
@@ -4452,7 +4464,7 @@
       <c r="Q69" t="n">
         <v>109</v>
       </c>
-      <c r="R69" s="1" t="n">
+      <c r="R69" s="2" t="n">
         <v>42217</v>
       </c>
     </row>
@@ -4510,7 +4522,7 @@
       <c r="Q70" t="n">
         <v>110</v>
       </c>
-      <c r="R70" s="1" t="n">
+      <c r="R70" s="2" t="n">
         <v>42248</v>
       </c>
     </row>
@@ -4568,7 +4580,7 @@
       <c r="Q71" t="n">
         <v>55</v>
       </c>
-      <c r="R71" s="1" t="n">
+      <c r="R71" s="2" t="n">
         <v>42278</v>
       </c>
     </row>
@@ -4626,7 +4638,7 @@
       <c r="Q72" t="n">
         <v>213</v>
       </c>
-      <c r="R72" s="1" t="n">
+      <c r="R72" s="2" t="n">
         <v>42309</v>
       </c>
     </row>
@@ -4684,7 +4696,7 @@
       <c r="Q73" t="n">
         <v>225</v>
       </c>
-      <c r="R73" s="1" t="n">
+      <c r="R73" s="2" t="n">
         <v>42339</v>
       </c>
     </row>
@@ -4742,7 +4754,7 @@
       <c r="Q74" t="n">
         <v>112</v>
       </c>
-      <c r="R74" s="1" t="n">
+      <c r="R74" s="2" t="n">
         <v>42370</v>
       </c>
     </row>
@@ -4800,7 +4812,7 @@
       <c r="Q75" t="n">
         <v>365</v>
       </c>
-      <c r="R75" s="1" t="n">
+      <c r="R75" s="2" t="n">
         <v>42401</v>
       </c>
     </row>
@@ -4858,7 +4870,7 @@
       <c r="Q76" t="n">
         <v>-19</v>
       </c>
-      <c r="R76" s="1" t="n">
+      <c r="R76" s="2" t="n">
         <v>42430</v>
       </c>
     </row>
@@ -4916,7 +4928,7 @@
       <c r="Q77" t="n">
         <v>292</v>
       </c>
-      <c r="R77" s="1" t="n">
+      <c r="R77" s="2" t="n">
         <v>42461</v>
       </c>
     </row>
@@ -4974,7 +4986,7 @@
       <c r="Q78" t="n">
         <v>-42</v>
       </c>
-      <c r="R78" s="1" t="n">
+      <c r="R78" s="2" t="n">
         <v>42491</v>
       </c>
     </row>
@@ -5032,7 +5044,7 @@
       <c r="Q79" t="n">
         <v>71</v>
       </c>
-      <c r="R79" s="1" t="n">
+      <c r="R79" s="2" t="n">
         <v>42522</v>
       </c>
     </row>
@@ -5090,7 +5102,7 @@
       <c r="Q80" t="n">
         <v>46</v>
       </c>
-      <c r="R80" s="1" t="n">
+      <c r="R80" s="2" t="n">
         <v>42552</v>
       </c>
     </row>
@@ -5148,7 +5160,7 @@
       <c r="Q81" t="n">
         <v>49</v>
       </c>
-      <c r="R81" s="1" t="n">
+      <c r="R81" s="2" t="n">
         <v>42583</v>
       </c>
     </row>
@@ -5206,7 +5218,7 @@
       <c r="Q82" t="n">
         <v>138</v>
       </c>
-      <c r="R82" s="1" t="n">
+      <c r="R82" s="2" t="n">
         <v>42614</v>
       </c>
     </row>
@@ -5264,7 +5276,7 @@
       <c r="Q83" t="n">
         <v>112</v>
       </c>
-      <c r="R83" s="1" t="n">
+      <c r="R83" s="2" t="n">
         <v>42644</v>
       </c>
     </row>
@@ -5322,7 +5334,7 @@
       <c r="Q84" t="n">
         <v>199</v>
       </c>
-      <c r="R84" s="1" t="n">
+      <c r="R84" s="2" t="n">
         <v>42675</v>
       </c>
     </row>
@@ -5380,7 +5392,7 @@
       <c r="Q85" t="n">
         <v>235</v>
       </c>
-      <c r="R85" s="1" t="n">
+      <c r="R85" s="2" t="n">
         <v>42705</v>
       </c>
     </row>
@@ -5438,7 +5450,7 @@
       <c r="Q86" t="n">
         <v>133</v>
       </c>
-      <c r="R86" s="1" t="n">
+      <c r="R86" s="2" t="n">
         <v>42736</v>
       </c>
     </row>
@@ -5496,7 +5508,7 @@
       <c r="Q87" t="n">
         <v>103</v>
       </c>
-      <c r="R87" s="1" t="n">
+      <c r="R87" s="2" t="n">
         <v>42767</v>
       </c>
     </row>
@@ -5554,7 +5566,7 @@
       <c r="Q88" t="n">
         <v>223</v>
       </c>
-      <c r="R88" s="1" t="n">
+      <c r="R88" s="2" t="n">
         <v>42795</v>
       </c>
     </row>
@@ -5612,7 +5624,7 @@
       <c r="Q89" t="n">
         <v>31</v>
       </c>
-      <c r="R89" s="1" t="n">
+      <c r="R89" s="2" t="n">
         <v>42826</v>
       </c>
     </row>
@@ -5670,7 +5682,7 @@
       <c r="Q90" t="n">
         <v>245</v>
       </c>
-      <c r="R90" s="1" t="n">
+      <c r="R90" s="2" t="n">
         <v>42856</v>
       </c>
     </row>
@@ -5728,7 +5740,7 @@
       <c r="Q91" t="n">
         <v>273</v>
       </c>
-      <c r="R91" s="1" t="n">
+      <c r="R91" s="2" t="n">
         <v>42887</v>
       </c>
     </row>
@@ -5786,7 +5798,7 @@
       <c r="Q92" t="n">
         <v>305</v>
       </c>
-      <c r="R92" s="1" t="n">
+      <c r="R92" s="2" t="n">
         <v>42917</v>
       </c>
     </row>
@@ -5844,7 +5856,7 @@
       <c r="Q93" t="n">
         <v>213</v>
       </c>
-      <c r="R93" s="1" t="n">
+      <c r="R93" s="2" t="n">
         <v>42948</v>
       </c>
     </row>
@@ -5902,7 +5914,7 @@
       <c r="Q94" t="n">
         <v>209</v>
       </c>
-      <c r="R94" s="1" t="n">
+      <c r="R94" s="2" t="n">
         <v>42979</v>
       </c>
     </row>
@@ -5960,7 +5972,7 @@
       <c r="Q95" t="n">
         <v>262</v>
       </c>
-      <c r="R95" s="1" t="n">
+      <c r="R95" s="2" t="n">
         <v>43009</v>
       </c>
     </row>
@@ -6018,7 +6030,7 @@
       <c r="Q96" t="n">
         <v>277</v>
       </c>
-      <c r="R96" s="1" t="n">
+      <c r="R96" s="2" t="n">
         <v>43040</v>
       </c>
     </row>
@@ -6076,7 +6088,7 @@
       <c r="Q97" t="n">
         <v>259</v>
       </c>
-      <c r="R97" s="1" t="n">
+      <c r="R97" s="2" t="n">
         <v>43070</v>
       </c>
     </row>
@@ -6134,7 +6146,7 @@
       <c r="Q98" t="n">
         <v>201</v>
       </c>
-      <c r="R98" s="1" t="n">
+      <c r="R98" s="2" t="n">
         <v>43101</v>
       </c>
     </row>
@@ -6192,7 +6204,7 @@
       <c r="Q99" t="n">
         <v>-9</v>
       </c>
-      <c r="R99" s="1" t="n">
+      <c r="R99" s="2" t="n">
         <v>43132</v>
       </c>
     </row>
@@ -6250,7 +6262,7 @@
       <c r="Q100" t="n">
         <v>-3</v>
       </c>
-      <c r="R100" s="1" t="n">
+      <c r="R100" s="2" t="n">
         <v>43160</v>
       </c>
     </row>
@@ -6308,7 +6320,7 @@
       <c r="Q101" t="n">
         <v>65</v>
       </c>
-      <c r="R101" s="1" t="n">
+      <c r="R101" s="2" t="n">
         <v>43191</v>
       </c>
     </row>
@@ -6366,7 +6378,7 @@
       <c r="Q102" t="n">
         <v>-145</v>
       </c>
-      <c r="R102" s="1" t="n">
+      <c r="R102" s="2" t="n">
         <v>43221</v>
       </c>
     </row>
@@ -6424,7 +6436,7 @@
       <c r="Q103" t="n">
         <v>35</v>
       </c>
-      <c r="R103" s="1" t="n">
+      <c r="R103" s="2" t="n">
         <v>43252</v>
       </c>
     </row>
@@ -6482,7 +6494,7 @@
       <c r="Q104" t="n">
         <v>62</v>
       </c>
-      <c r="R104" s="1" t="n">
+      <c r="R104" s="2" t="n">
         <v>43282</v>
       </c>
     </row>
@@ -6540,7 +6552,7 @@
       <c r="Q105" t="n">
         <v>28</v>
       </c>
-      <c r="R105" s="1" t="n">
+      <c r="R105" s="2" t="n">
         <v>43313</v>
       </c>
     </row>
@@ -6598,7 +6610,7 @@
       <c r="Q106" t="n">
         <v>104</v>
       </c>
-      <c r="R106" s="1" t="n">
+      <c r="R106" s="2" t="n">
         <v>43344</v>
       </c>
     </row>
@@ -6656,7 +6668,7 @@
       <c r="Q107" t="n">
         <v>111</v>
       </c>
-      <c r="R107" s="1" t="n">
+      <c r="R107" s="2" t="n">
         <v>43374</v>
       </c>
     </row>
@@ -6714,7 +6726,7 @@
       <c r="Q108" t="n">
         <v>212</v>
       </c>
-      <c r="R108" s="1" t="n">
+      <c r="R108" s="2" t="n">
         <v>43405</v>
       </c>
     </row>
@@ -6772,7 +6784,7 @@
       <c r="Q109" t="n">
         <v>120</v>
       </c>
-      <c r="R109" s="1" t="n">
+      <c r="R109" s="2" t="n">
         <v>43435</v>
       </c>
     </row>
@@ -6830,7 +6842,7 @@
       <c r="Q110" t="n">
         <v>92</v>
       </c>
-      <c r="R110" s="1" t="n">
+      <c r="R110" s="2" t="n">
         <v>43466</v>
       </c>
     </row>
@@ -6888,7 +6900,7 @@
       <c r="Q111" t="n">
         <v>-67</v>
       </c>
-      <c r="R111" s="1" t="n">
+      <c r="R111" s="2" t="n">
         <v>43497</v>
       </c>
     </row>
@@ -6946,7 +6958,7 @@
       <c r="Q112" t="n">
         <v>125</v>
       </c>
-      <c r="R112" s="1" t="n">
+      <c r="R112" s="2" t="n">
         <v>43525</v>
       </c>
     </row>
@@ -7004,7 +7016,7 @@
       <c r="Q113" t="n">
         <v>-16</v>
       </c>
-      <c r="R113" s="1" t="n">
+      <c r="R113" s="2" t="n">
         <v>43556</v>
       </c>
     </row>
@@ -7062,7 +7074,7 @@
       <c r="Q114" t="n">
         <v>-71</v>
       </c>
-      <c r="R114" s="1" t="n">
+      <c r="R114" s="2" t="n">
         <v>43586</v>
       </c>
     </row>
@@ -7120,7 +7132,7 @@
       <c r="Q115" t="n">
         <v>19</v>
       </c>
-      <c r="R115" s="1" t="n">
+      <c r="R115" s="2" t="n">
         <v>43617</v>
       </c>
     </row>
@@ -7178,7 +7190,7 @@
       <c r="Q116" t="n">
         <v>141</v>
       </c>
-      <c r="R116" s="1" t="n">
+      <c r="R116" s="2" t="n">
         <v>43647</v>
       </c>
     </row>
@@ -7236,7 +7248,7 @@
       <c r="Q117" t="n">
         <v>99</v>
       </c>
-      <c r="R117" s="1" t="n">
+      <c r="R117" s="2" t="n">
         <v>43678</v>
       </c>
     </row>
@@ -7294,7 +7306,7 @@
       <c r="Q118" t="n">
         <v>100</v>
       </c>
-      <c r="R118" s="1" t="n">
+      <c r="R118" s="2" t="n">
         <v>43709</v>
       </c>
     </row>
@@ -7352,7 +7364,7 @@
       <c r="Q119" t="n">
         <v>109</v>
       </c>
-      <c r="R119" s="1" t="n">
+      <c r="R119" s="2" t="n">
         <v>43739</v>
       </c>
     </row>
@@ -7410,7 +7422,7 @@
       <c r="Q120" t="n">
         <v>92</v>
       </c>
-      <c r="R120" s="1" t="n">
+      <c r="R120" s="2" t="n">
         <v>43770</v>
       </c>
     </row>
@@ -7468,7 +7480,7 @@
       <c r="Q121" t="n">
         <v>248</v>
       </c>
-      <c r="R121" s="1" t="n">
+      <c r="R121" s="2" t="n">
         <v>43800</v>
       </c>
     </row>
@@ -7526,7 +7538,7 @@
       <c r="Q122" t="n">
         <v>94</v>
       </c>
-      <c r="R122" s="1" t="n">
+      <c r="R122" s="2" t="n">
         <v>43831</v>
       </c>
     </row>
@@ -7584,7 +7596,7 @@
       <c r="Q123" t="n">
         <v>-130</v>
       </c>
-      <c r="R123" s="1" t="n">
+      <c r="R123" s="2" t="n">
         <v>43862</v>
       </c>
     </row>
@@ -7642,7 +7654,7 @@
       <c r="Q124" t="n">
         <v>-266</v>
       </c>
-      <c r="R124" s="1" t="n">
+      <c r="R124" s="2" t="n">
         <v>43891</v>
       </c>
     </row>
@@ -7700,7 +7712,7 @@
       <c r="Q125" t="n">
         <v>40</v>
       </c>
-      <c r="R125" s="1" t="n">
+      <c r="R125" s="2" t="n">
         <v>43922</v>
       </c>
     </row>
@@ -7758,7 +7770,7 @@
       <c r="Q126" t="n">
         <v>-35</v>
       </c>
-      <c r="R126" s="1" t="n">
+      <c r="R126" s="2" t="n">
         <v>43952</v>
       </c>
     </row>
@@ -7816,7 +7828,7 @@
       <c r="Q127" t="n">
         <v>-60</v>
       </c>
-      <c r="R127" s="1" t="n">
+      <c r="R127" s="2" t="n">
         <v>43983</v>
       </c>
     </row>
@@ -7874,7 +7886,7 @@
       <c r="Q128" t="n">
         <v>85</v>
       </c>
-      <c r="R128" s="1" t="n">
+      <c r="R128" s="2" t="n">
         <v>44013</v>
       </c>
     </row>
@@ -7932,7 +7944,7 @@
       <c r="Q129" t="n">
         <v>150</v>
       </c>
-      <c r="R129" s="1" t="n">
+      <c r="R129" s="2" t="n">
         <v>44044</v>
       </c>
     </row>
@@ -7990,7 +8002,7 @@
       <c r="Q130" t="n">
         <v>206</v>
       </c>
-      <c r="R130" s="1" t="n">
+      <c r="R130" s="2" t="n">
         <v>44075</v>
       </c>
     </row>
@@ -8048,7 +8060,7 @@
       <c r="Q131" t="n">
         <v>-23</v>
       </c>
-      <c r="R131" s="1" t="n">
+      <c r="R131" s="2" t="n">
         <v>44105</v>
       </c>
     </row>
@@ -8106,7 +8118,7 @@
       <c r="Q132" t="n">
         <v>174</v>
       </c>
-      <c r="R132" s="1" t="n">
+      <c r="R132" s="2" t="n">
         <v>44136</v>
       </c>
     </row>
@@ -8164,7 +8176,7 @@
       <c r="Q133" t="n">
         <v>-34</v>
       </c>
-      <c r="R133" s="1" t="n">
+      <c r="R133" s="2" t="n">
         <v>44166</v>
       </c>
     </row>
@@ -8222,7 +8234,7 @@
       <c r="Q134" t="n">
         <v>44</v>
       </c>
-      <c r="R134" s="1" t="n">
+      <c r="R134" s="2" t="n">
         <v>44197</v>
       </c>
     </row>
@@ -8280,7 +8292,7 @@
       <c r="Q135" t="n">
         <v>146</v>
       </c>
-      <c r="R135" s="1" t="n">
+      <c r="R135" s="2" t="n">
         <v>44228</v>
       </c>
     </row>
@@ -8338,7 +8350,7 @@
       <c r="Q136" t="n">
         <v>44</v>
       </c>
-      <c r="R136" s="1" t="n">
+      <c r="R136" s="2" t="n">
         <v>44256</v>
       </c>
     </row>
@@ -8396,7 +8408,7 @@
       <c r="Q137" t="n">
         <v>282</v>
       </c>
-      <c r="R137" s="1" t="n">
+      <c r="R137" s="2" t="n">
         <v>44287</v>
       </c>
     </row>
@@ -8454,7 +8466,7 @@
       <c r="Q138" t="n">
         <v>152</v>
       </c>
-      <c r="R138" s="1" t="n">
+      <c r="R138" s="2" t="n">
         <v>44317</v>
       </c>
     </row>
@@ -8512,7 +8524,7 @@
       <c r="Q139" t="n">
         <v>-23</v>
       </c>
-      <c r="R139" s="1" t="n">
+      <c r="R139" s="2" t="n">
         <v>44348</v>
       </c>
     </row>
@@ -8570,7 +8582,7 @@
       <c r="Q140" t="n">
         <v>53</v>
       </c>
-      <c r="R140" s="1" t="n">
+      <c r="R140" s="2" t="n">
         <v>44378</v>
       </c>
     </row>
@@ -8628,7 +8640,7 @@
       <c r="Q141" t="n">
         <v>81</v>
       </c>
-      <c r="R141" s="1" t="n">
+      <c r="R141" s="2" t="n">
         <v>44409</v>
       </c>
     </row>
@@ -8686,7 +8698,7 @@
       <c r="Q142" t="n">
         <v>50</v>
       </c>
-      <c r="R142" s="1" t="n">
+      <c r="R142" s="2" t="n">
         <v>44440</v>
       </c>
     </row>
@@ -8744,7 +8756,7 @@
       <c r="Q143" t="n">
         <v>115</v>
       </c>
-      <c r="R143" s="1" t="n">
+      <c r="R143" s="2" t="n">
         <v>44470</v>
       </c>
     </row>
@@ -8802,7 +8814,7 @@
       <c r="Q144" t="n">
         <v>-106</v>
       </c>
-      <c r="R144" s="1" t="n">
+      <c r="R144" s="2" t="n">
         <v>44501</v>
       </c>
     </row>
@@ -8860,7 +8872,7 @@
       <c r="Q145" t="n">
         <v>112</v>
       </c>
-      <c r="R145" s="1" t="n">
+      <c r="R145" s="2" t="n">
         <v>44531</v>
       </c>
     </row>
@@ -8918,7 +8930,7 @@
       <c r="Q146" t="n">
         <v>-158</v>
       </c>
-      <c r="R146" s="1" t="n">
+      <c r="R146" s="2" t="n">
         <v>44562</v>
       </c>
     </row>
@@ -8976,7 +8988,7 @@
       <c r="Q147" t="n">
         <v>-43</v>
       </c>
-      <c r="R147" s="1" t="n">
+      <c r="R147" s="2" t="n">
         <v>44593</v>
       </c>
     </row>
@@ -9034,7 +9046,7 @@
       <c r="Q148" t="n">
         <v>-190</v>
       </c>
-      <c r="R148" s="1" t="n">
+      <c r="R148" s="2" t="n">
         <v>44621</v>
       </c>
     </row>
@@ -9092,7 +9104,7 @@
       <c r="Q149" t="n">
         <v>-107</v>
       </c>
-      <c r="R149" s="1" t="n">
+      <c r="R149" s="2" t="n">
         <v>44652</v>
       </c>
     </row>
@@ -9150,7 +9162,7 @@
       <c r="Q150" t="n">
         <v>-92</v>
       </c>
-      <c r="R150" s="1" t="n">
+      <c r="R150" s="2" t="n">
         <v>44682</v>
       </c>
     </row>
@@ -9208,7 +9220,7 @@
       <c r="Q151" t="n">
         <v>-123</v>
       </c>
-      <c r="R151" s="1" t="n">
+      <c r="R151" s="2" t="n">
         <v>44713</v>
       </c>
     </row>
@@ -9266,7 +9278,7 @@
       <c r="Q152" t="n">
         <v>60</v>
       </c>
-      <c r="R152" s="1" t="n">
+      <c r="R152" s="2" t="n">
         <v>44743</v>
       </c>
     </row>
@@ -9324,7 +9336,7 @@
       <c r="Q153" t="n">
         <v>53</v>
       </c>
-      <c r="R153" s="1" t="n">
+      <c r="R153" s="2" t="n">
         <v>44774</v>
       </c>
     </row>
@@ -9382,7 +9394,7 @@
       <c r="Q154" t="n">
         <v>1</v>
       </c>
-      <c r="R154" s="1" t="n">
+      <c r="R154" s="2" t="n">
         <v>44805</v>
       </c>
     </row>
@@ -9440,7 +9452,7 @@
       <c r="Q155" t="n">
         <v>34</v>
       </c>
-      <c r="R155" s="1" t="n">
+      <c r="R155" s="2" t="n">
         <v>44835</v>
       </c>
     </row>
@@ -9498,7 +9510,7 @@
       <c r="Q156" t="n">
         <v>-15</v>
       </c>
-      <c r="R156" s="1" t="n">
+      <c r="R156" s="2" t="n">
         <v>44866</v>
       </c>
     </row>
@@ -9556,7 +9568,7 @@
       <c r="Q157" t="n">
         <v>211</v>
       </c>
-      <c r="R157" s="1" t="n">
+      <c r="R157" s="2" t="n">
         <v>44896</v>
       </c>
     </row>
@@ -9614,7 +9626,7 @@
       <c r="Q158" t="n">
         <v>-228</v>
       </c>
-      <c r="R158" s="1" t="n">
+      <c r="R158" s="2" t="n">
         <v>44927</v>
       </c>
     </row>
@@ -9672,7 +9684,7 @@
       <c r="Q159" t="n">
         <v>157</v>
       </c>
-      <c r="R159" s="1" t="n">
+      <c r="R159" s="2" t="n">
         <v>44958</v>
       </c>
     </row>
@@ -9730,7 +9742,7 @@
       <c r="Q160" t="n">
         <v>77</v>
       </c>
-      <c r="R160" s="1" t="n">
+      <c r="R160" s="2" t="n">
         <v>44986</v>
       </c>
     </row>
@@ -9788,7 +9800,7 @@
       <c r="Q161" t="n">
         <v>60</v>
       </c>
-      <c r="R161" s="1" t="n">
+      <c r="R161" s="2" t="n">
         <v>45017</v>
       </c>
     </row>
@@ -9846,7 +9858,7 @@
       <c r="Q162" t="n">
         <v>21</v>
       </c>
-      <c r="R162" s="1" t="n">
+      <c r="R162" s="2" t="n">
         <v>45047</v>
       </c>
     </row>
@@ -9904,7 +9916,7 @@
       <c r="Q163" t="n">
         <v>190</v>
       </c>
-      <c r="R163" s="1" t="n">
+      <c r="R163" s="2" t="n">
         <v>45078</v>
       </c>
     </row>
@@ -9962,7 +9974,7 @@
       <c r="Q164" t="n">
         <v>-81</v>
       </c>
-      <c r="R164" s="1" t="n">
+      <c r="R164" s="2" t="n">
         <v>45108</v>
       </c>
     </row>
@@ -10020,7 +10032,7 @@
       <c r="Q165" t="n">
         <v>89</v>
       </c>
-      <c r="R165" s="1" t="n">
+      <c r="R165" s="2" t="n">
         <v>45139</v>
       </c>
     </row>
@@ -10078,7 +10090,7 @@
       <c r="Q166" t="n">
         <v>197</v>
       </c>
-      <c r="R166" s="1" t="n">
+      <c r="R166" s="2" t="n">
         <v>45170</v>
       </c>
     </row>
@@ -10136,7 +10148,7 @@
       <c r="Q167" t="n">
         <v>-53</v>
       </c>
-      <c r="R167" s="1" t="n">
+      <c r="R167" s="2" t="n">
         <v>45200</v>
       </c>
     </row>
@@ -10194,7 +10206,7 @@
       <c r="Q168" t="n">
         <v>-21</v>
       </c>
-      <c r="R168" s="1" t="n">
+      <c r="R168" s="2" t="n">
         <v>45231</v>
       </c>
     </row>
@@ -10252,7 +10264,7 @@
       <c r="Q169" t="n">
         <v>149</v>
       </c>
-      <c r="R169" s="1" t="n">
+      <c r="R169" s="2" t="n">
         <v>45261</v>
       </c>
     </row>
@@ -10263,7 +10275,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-2496</v>
+        <v>-2543</v>
       </c>
       <c r="C170" t="n">
         <v>-4332</v>
@@ -10284,19 +10296,19 @@
         <v>1024</v>
       </c>
       <c r="I170" t="n">
-        <v>3182</v>
+        <v>3135</v>
       </c>
       <c r="J170" t="n">
-        <v>7178</v>
+        <v>7180</v>
       </c>
       <c r="K170" t="n">
-        <v>3996</v>
+        <v>4045</v>
       </c>
       <c r="L170" t="n">
-        <v>2882</v>
+        <v>2887</v>
       </c>
       <c r="M170" t="n">
-        <v>1584</v>
+        <v>1593</v>
       </c>
       <c r="N170" t="n">
         <v>2955</v>
@@ -10310,7 +10322,7 @@
       <c r="Q170" t="n">
         <v>-157</v>
       </c>
-      <c r="R170" s="1" t="n">
+      <c r="R170" s="2" t="n">
         <v>45292</v>
       </c>
     </row>
@@ -10321,7 +10333,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-3160</v>
+        <v>-3202</v>
       </c>
       <c r="C171" t="n">
         <v>-4682</v>
@@ -10342,19 +10354,19 @@
         <v>1108</v>
       </c>
       <c r="I171" t="n">
-        <v>2372</v>
+        <v>2330</v>
       </c>
       <c r="J171" t="n">
-        <v>6535</v>
+        <v>6538</v>
       </c>
       <c r="K171" t="n">
-        <v>4163</v>
+        <v>4208</v>
       </c>
       <c r="L171" t="n">
-        <v>2810</v>
+        <v>2817</v>
       </c>
       <c r="M171" t="n">
-        <v>1671</v>
+        <v>1679</v>
       </c>
       <c r="N171" t="n">
         <v>2449</v>
@@ -10368,7 +10380,7 @@
       <c r="Q171" t="n">
         <v>-123</v>
       </c>
-      <c r="R171" s="1" t="n">
+      <c r="R171" s="2" t="n">
         <v>45323</v>
       </c>
     </row>
@@ -10379,7 +10391,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-4031</v>
+        <v>-4079</v>
       </c>
       <c r="C172" t="n">
         <v>-5011</v>
@@ -10400,19 +10412,19 @@
         <v>1608</v>
       </c>
       <c r="I172" t="n">
-        <v>2797</v>
+        <v>2749</v>
       </c>
       <c r="J172" t="n">
-        <v>7771</v>
+        <v>7773</v>
       </c>
       <c r="K172" t="n">
-        <v>4974</v>
+        <v>5024</v>
       </c>
       <c r="L172" t="n">
-        <v>3192</v>
+        <v>3199</v>
       </c>
       <c r="M172" t="n">
-        <v>1871</v>
+        <v>1880</v>
       </c>
       <c r="N172" t="n">
         <v>2736</v>
@@ -10426,7 +10438,7 @@
       <c r="Q172" t="n">
         <v>-206</v>
       </c>
-      <c r="R172" s="1" t="n">
+      <c r="R172" s="2" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -10437,7 +10449,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-4947</v>
+        <v>-4993</v>
       </c>
       <c r="C173" t="n">
         <v>-7666</v>
@@ -10458,19 +10470,19 @@
         <v>1551</v>
       </c>
       <c r="I173" t="n">
-        <v>3707</v>
+        <v>3661</v>
       </c>
       <c r="J173" t="n">
-        <v>8026</v>
+        <v>8030</v>
       </c>
       <c r="K173" t="n">
-        <v>4319</v>
+        <v>4369</v>
       </c>
       <c r="L173" t="n">
-        <v>3154</v>
+        <v>3163</v>
       </c>
       <c r="M173" t="n">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="N173" t="n">
         <v>3484</v>
@@ -10484,7 +10496,7 @@
       <c r="Q173" t="n">
         <v>520</v>
       </c>
-      <c r="R173" s="1" t="n">
+      <c r="R173" s="2" t="n">
         <v>45383</v>
       </c>
     </row>
@@ -10495,7 +10507,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>-820</v>
+        <v>-855</v>
       </c>
       <c r="C174" t="n">
         <v>-4153</v>
@@ -10516,19 +10528,19 @@
         <v>1430</v>
       </c>
       <c r="I174" t="n">
-        <v>5307</v>
+        <v>5272</v>
       </c>
       <c r="J174" t="n">
-        <v>9817</v>
+        <v>9825</v>
       </c>
       <c r="K174" t="n">
-        <v>4510</v>
+        <v>4553</v>
       </c>
       <c r="L174" t="n">
-        <v>3454</v>
+        <v>3465</v>
       </c>
       <c r="M174" t="n">
-        <v>1918</v>
+        <v>1926</v>
       </c>
       <c r="N174" t="n">
         <v>4876</v>
@@ -10542,7 +10554,7 @@
       <c r="Q174" t="n">
         <v>-152</v>
       </c>
-      <c r="R174" s="1" t="n">
+      <c r="R174" s="2" t="n">
         <v>45413</v>
       </c>
     </row>
@@ -10553,7 +10565,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>627</v>
+        <v>587</v>
       </c>
       <c r="C175" t="n">
         <v>-4109</v>
@@ -10574,19 +10586,19 @@
         <v>1063</v>
       </c>
       <c r="I175" t="n">
-        <v>6003</v>
+        <v>5963</v>
       </c>
       <c r="J175" t="n">
-        <v>10686</v>
+        <v>10697</v>
       </c>
       <c r="K175" t="n">
-        <v>4683</v>
+        <v>4734</v>
       </c>
       <c r="L175" t="n">
-        <v>3506</v>
+        <v>3519</v>
       </c>
       <c r="M175" t="n">
-        <v>1649</v>
+        <v>1656</v>
       </c>
       <c r="N175" t="n">
         <v>5528</v>
@@ -10600,7 +10612,7 @@
       <c r="Q175" t="n">
         <v>3</v>
       </c>
-      <c r="R175" s="1" t="n">
+      <c r="R175" s="2" t="n">
         <v>45444</v>
       </c>
     </row>
@@ -10611,7 +10623,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>1270</v>
+        <v>1227</v>
       </c>
       <c r="C176" t="n">
         <v>-5063</v>
@@ -10632,19 +10644,19 @@
         <v>998</v>
       </c>
       <c r="I176" t="n">
-        <v>7709</v>
+        <v>7666</v>
       </c>
       <c r="J176" t="n">
-        <v>12426</v>
+        <v>12433</v>
       </c>
       <c r="K176" t="n">
-        <v>4717</v>
+        <v>4767</v>
       </c>
       <c r="L176" t="n">
-        <v>3929</v>
+        <v>3943</v>
       </c>
       <c r="M176" t="n">
-        <v>1910</v>
+        <v>1917</v>
       </c>
       <c r="N176" t="n">
         <v>6883</v>
@@ -10658,7 +10670,7 @@
       <c r="Q176" t="n">
         <v>92</v>
       </c>
-      <c r="R176" s="1" t="n">
+      <c r="R176" s="2" t="n">
         <v>45474</v>
       </c>
     </row>
@@ -10669,7 +10681,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>4456</v>
+        <v>4415</v>
       </c>
       <c r="C177" t="n">
         <v>-2886</v>
@@ -10690,19 +10702,19 @@
         <v>1293</v>
       </c>
       <c r="I177" t="n">
-        <v>9248</v>
+        <v>9207</v>
       </c>
       <c r="J177" t="n">
-        <v>13658</v>
+        <v>13667</v>
       </c>
       <c r="K177" t="n">
-        <v>4410</v>
+        <v>4460</v>
       </c>
       <c r="L177" t="n">
-        <v>4074</v>
+        <v>4086</v>
       </c>
       <c r="M177" t="n">
-        <v>1769</v>
+        <v>1778</v>
       </c>
       <c r="N177" t="n">
         <v>8163</v>
@@ -10716,7 +10728,7 @@
       <c r="Q177" t="n">
         <v>-5</v>
       </c>
-      <c r="R177" s="1" t="n">
+      <c r="R177" s="2" t="n">
         <v>45505</v>
       </c>
     </row>
@@ -10727,7 +10739,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>2641</v>
+        <v>2598</v>
       </c>
       <c r="C178" t="n">
         <v>-3108</v>
@@ -10748,19 +10760,19 @@
         <v>1205</v>
       </c>
       <c r="I178" t="n">
-        <v>7213</v>
+        <v>7170</v>
       </c>
       <c r="J178" t="n">
-        <v>11954</v>
+        <v>11965</v>
       </c>
       <c r="K178" t="n">
-        <v>4741</v>
+        <v>4795</v>
       </c>
       <c r="L178" t="n">
-        <v>3783</v>
+        <v>3799</v>
       </c>
       <c r="M178" t="n">
-        <v>1723</v>
+        <v>1731</v>
       </c>
       <c r="N178" t="n">
         <v>6453</v>
@@ -10774,7 +10786,7 @@
       <c r="Q178" t="n">
         <v>-19</v>
       </c>
-      <c r="R178" s="1" t="n">
+      <c r="R178" s="2" t="n">
         <v>45536</v>
       </c>
     </row>
@@ -10785,7 +10797,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1746</v>
+        <v>1714</v>
       </c>
       <c r="C179" t="n">
         <v>-3504</v>
@@ -10806,19 +10818,19 @@
         <v>1739</v>
       </c>
       <c r="I179" t="n">
-        <v>6903</v>
+        <v>6871</v>
       </c>
       <c r="J179" t="n">
-        <v>11469</v>
+        <v>11493</v>
       </c>
       <c r="K179" t="n">
-        <v>4566</v>
+        <v>4622</v>
       </c>
       <c r="L179" t="n">
-        <v>3696</v>
+        <v>3724</v>
       </c>
       <c r="M179" t="n">
-        <v>1844</v>
+        <v>1853</v>
       </c>
       <c r="N179" t="n">
         <v>6202</v>
@@ -10832,7 +10844,7 @@
       <c r="Q179" t="n">
         <v>-15</v>
       </c>
-      <c r="R179" s="1" t="n">
+      <c r="R179" s="2" t="n">
         <v>45566</v>
       </c>
     </row>
@@ -10843,7 +10855,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>-3388</v>
+        <v>-3448</v>
       </c>
       <c r="C180" t="n">
         <v>-5242</v>
@@ -10864,19 +10876,19 @@
         <v>2080</v>
       </c>
       <c r="I180" t="n">
-        <v>3897</v>
+        <v>3837</v>
       </c>
       <c r="J180" t="n">
-        <v>8548</v>
+        <v>8545</v>
       </c>
       <c r="K180" t="n">
-        <v>4651</v>
+        <v>4708</v>
       </c>
       <c r="L180" t="n">
-        <v>3111</v>
+        <v>3114</v>
       </c>
       <c r="M180" t="n">
-        <v>1717</v>
+        <v>1726</v>
       </c>
       <c r="N180" t="n">
         <v>3686</v>
@@ -10890,7 +10902,7 @@
       <c r="Q180" t="n">
         <v>21</v>
       </c>
-      <c r="R180" s="1" t="n">
+      <c r="R180" s="2" t="n">
         <v>45597</v>
       </c>
     </row>
@@ -10901,7 +10913,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-4925</v>
+        <v>-5010</v>
       </c>
       <c r="C181" t="n">
         <v>-6231</v>
@@ -10922,19 +10934,19 @@
         <v>2001</v>
       </c>
       <c r="I181" t="n">
-        <v>3031</v>
+        <v>2946</v>
       </c>
       <c r="J181" t="n">
-        <v>9121</v>
+        <v>9109</v>
       </c>
       <c r="K181" t="n">
-        <v>6090</v>
+        <v>6163</v>
       </c>
       <c r="L181" t="n">
-        <v>3400</v>
+        <v>3406</v>
       </c>
       <c r="M181" t="n">
-        <v>1883</v>
+        <v>1892</v>
       </c>
       <c r="N181" t="n">
         <v>2863</v>
@@ -10948,7 +10960,7 @@
       <c r="Q181" t="n">
         <v>113</v>
       </c>
-      <c r="R181" s="1" t="n">
+      <c r="R181" s="2" t="n">
         <v>45627</v>
       </c>
     </row>
@@ -10959,16 +10971,16 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>-4034</v>
+        <v>-3987</v>
       </c>
       <c r="C182" t="n">
-        <v>-5536</v>
+        <v>-5499</v>
       </c>
       <c r="D182" t="n">
-        <v>21077</v>
+        <v>21075</v>
       </c>
       <c r="E182" t="n">
-        <v>26613</v>
+        <v>26574</v>
       </c>
       <c r="F182" t="n">
         <v>-1092</v>
@@ -10980,19 +10992,19 @@
         <v>1472</v>
       </c>
       <c r="I182" t="n">
-        <v>3042</v>
+        <v>3052</v>
       </c>
       <c r="J182" t="n">
-        <v>7645</v>
+        <v>7794</v>
       </c>
       <c r="K182" t="n">
-        <v>4603</v>
+        <v>4742</v>
       </c>
       <c r="L182" t="n">
-        <v>2936</v>
+        <v>2952</v>
       </c>
       <c r="M182" t="n">
-        <v>1526</v>
+        <v>1555</v>
       </c>
       <c r="N182" t="n">
         <v>3251</v>
@@ -11006,7 +11018,7 @@
       <c r="Q182" t="n">
         <v>-154</v>
       </c>
-      <c r="R182" s="1" t="n">
+      <c r="R182" s="2" t="n">
         <v>45658</v>
       </c>
     </row>
@@ -11017,16 +11029,16 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>-5219</v>
+        <v>-5290</v>
       </c>
       <c r="C183" t="n">
-        <v>-5477</v>
+        <v>-5435</v>
       </c>
       <c r="D183" t="n">
-        <v>21142</v>
+        <v>21141</v>
       </c>
       <c r="E183" t="n">
-        <v>26619</v>
+        <v>26576</v>
       </c>
       <c r="F183" t="n">
         <v>-1850</v>
@@ -11038,19 +11050,19 @@
         <v>2110</v>
       </c>
       <c r="I183" t="n">
-        <v>2266</v>
+        <v>2153</v>
       </c>
       <c r="J183" t="n">
-        <v>6567</v>
+        <v>6720</v>
       </c>
       <c r="K183" t="n">
-        <v>4301</v>
+        <v>4567</v>
       </c>
       <c r="L183" t="n">
-        <v>2585</v>
+        <v>2612</v>
       </c>
       <c r="M183" t="n">
-        <v>1427</v>
+        <v>1455</v>
       </c>
       <c r="N183" t="n">
         <v>2695</v>
@@ -11064,7 +11076,7 @@
       <c r="Q183" t="n">
         <v>8</v>
       </c>
-      <c r="R183" s="1" t="n">
+      <c r="R183" s="2" t="n">
         <v>45689</v>
       </c>
     </row>
@@ -11075,16 +11087,16 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>-4925</v>
+        <v>-4996</v>
       </c>
       <c r="C184" t="n">
-        <v>-4853</v>
+        <v>-4800</v>
       </c>
       <c r="D184" t="n">
-        <v>23420</v>
+        <v>23417</v>
       </c>
       <c r="E184" t="n">
-        <v>28273</v>
+        <v>28217</v>
       </c>
       <c r="F184" t="n">
         <v>-1147</v>
@@ -11096,19 +11108,19 @@
         <v>1593</v>
       </c>
       <c r="I184" t="n">
-        <v>2685</v>
+        <v>2561</v>
       </c>
       <c r="J184" t="n">
-        <v>7436</v>
+        <v>7608</v>
       </c>
       <c r="K184" t="n">
-        <v>4751</v>
+        <v>5047</v>
       </c>
       <c r="L184" t="n">
-        <v>2959</v>
+        <v>2986</v>
       </c>
       <c r="M184" t="n">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="N184" t="n">
         <v>2842</v>
@@ -11122,7 +11134,7 @@
       <c r="Q184" t="n">
         <v>-9</v>
       </c>
-      <c r="R184" s="1" t="n">
+      <c r="R184" s="2" t="n">
         <v>45717</v>
       </c>
     </row>
@@ -11133,16 +11145,16 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>-8445</v>
+        <v>-8497</v>
       </c>
       <c r="C185" t="n">
-        <v>-9894</v>
+        <v>-9850</v>
       </c>
       <c r="D185" t="n">
-        <v>20743</v>
+        <v>20741</v>
       </c>
       <c r="E185" t="n">
-        <v>30637</v>
+        <v>30591</v>
       </c>
       <c r="F185" t="n">
         <v>-2185</v>
@@ -11154,19 +11166,19 @@
         <v>2402</v>
       </c>
       <c r="I185" t="n">
-        <v>3937</v>
+        <v>3841</v>
       </c>
       <c r="J185" t="n">
-        <v>8756</v>
+        <v>8924</v>
       </c>
       <c r="K185" t="n">
-        <v>4819</v>
+        <v>5083</v>
       </c>
       <c r="L185" t="n">
-        <v>3422</v>
+        <v>3435</v>
       </c>
       <c r="M185" t="n">
-        <v>1714</v>
+        <v>1743</v>
       </c>
       <c r="N185" t="n">
         <v>3917</v>
@@ -11180,7 +11192,7 @@
       <c r="Q185" t="n">
         <v>-104</v>
       </c>
-      <c r="R185" s="1" t="n">
+      <c r="R185" s="2" t="n">
         <v>45748</v>
       </c>
     </row>
@@ -11191,16 +11203,16 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-1105</v>
+        <v>-1049</v>
       </c>
       <c r="C186" t="n">
-        <v>-4782</v>
+        <v>-4726</v>
       </c>
       <c r="D186" t="n">
-        <v>24296</v>
+        <v>24294</v>
       </c>
       <c r="E186" t="n">
-        <v>29078</v>
+        <v>29020</v>
       </c>
       <c r="F186" t="n">
         <v>-1774</v>
@@ -11215,16 +11227,16 @@
         <v>5545</v>
       </c>
       <c r="J186" t="n">
-        <v>10161</v>
+        <v>10326</v>
       </c>
       <c r="K186" t="n">
-        <v>4616</v>
+        <v>4781</v>
       </c>
       <c r="L186" t="n">
-        <v>3535</v>
+        <v>3550</v>
       </c>
       <c r="M186" t="n">
-        <v>1669</v>
+        <v>1697</v>
       </c>
       <c r="N186" t="n">
         <v>5109</v>
@@ -11238,7 +11250,7 @@
       <c r="Q186" t="n">
         <v>-25</v>
       </c>
-      <c r="R186" s="1" t="n">
+      <c r="R186" s="2" t="n">
         <v>45778</v>
       </c>
     </row>
@@ -11249,16 +11261,16 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>-2270</v>
+        <v>-2197</v>
       </c>
       <c r="C187" t="n">
-        <v>-6521</v>
+        <v>-6471</v>
       </c>
       <c r="D187" t="n">
-        <v>20334</v>
+        <v>20331</v>
       </c>
       <c r="E187" t="n">
-        <v>26855</v>
+        <v>26802</v>
       </c>
       <c r="F187" t="n">
         <v>-1423</v>
@@ -11270,19 +11282,19 @@
         <v>1551</v>
       </c>
       <c r="I187" t="n">
-        <v>6088</v>
+        <v>6111</v>
       </c>
       <c r="J187" t="n">
-        <v>11350</v>
+        <v>11551</v>
       </c>
       <c r="K187" t="n">
-        <v>5262</v>
+        <v>5440</v>
       </c>
       <c r="L187" t="n">
-        <v>3669</v>
+        <v>3673</v>
       </c>
       <c r="M187" t="n">
-        <v>1633</v>
+        <v>1642</v>
       </c>
       <c r="N187" t="n">
         <v>5953</v>
@@ -11296,7 +11308,7 @@
       <c r="Q187" t="n">
         <v>-82</v>
       </c>
-      <c r="R187" s="1" t="n">
+      <c r="R187" s="2" t="n">
         <v>45809</v>
       </c>
     </row>
@@ -11307,16 +11319,16 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1686</v>
+        <v>1762</v>
       </c>
       <c r="C188" t="n">
-        <v>-4616</v>
+        <v>-4561</v>
       </c>
       <c r="D188" t="n">
-        <v>24622</v>
+        <v>24620</v>
       </c>
       <c r="E188" t="n">
-        <v>29238</v>
+        <v>29181</v>
       </c>
       <c r="F188" t="n">
         <v>-501</v>
@@ -11328,22 +11340,22 @@
         <v>943</v>
       </c>
       <c r="I188" t="n">
-        <v>7994</v>
+        <v>8015</v>
       </c>
       <c r="J188" t="n">
-        <v>12972</v>
+        <v>13162</v>
       </c>
       <c r="K188" t="n">
-        <v>4978</v>
+        <v>5147</v>
       </c>
       <c r="L188" t="n">
-        <v>4144</v>
+        <v>4145</v>
       </c>
       <c r="M188" t="n">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="N188" t="n">
-        <v>7008</v>
+        <v>7021</v>
       </c>
       <c r="O188" t="n">
         <v>819</v>
@@ -11354,7 +11366,7 @@
       <c r="Q188" t="n">
         <v>-153</v>
       </c>
-      <c r="R188" s="1" t="n">
+      <c r="R188" s="2" t="n">
         <v>45839</v>
       </c>
     </row>
@@ -11365,16 +11377,16 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>4703</v>
+        <v>4654</v>
       </c>
       <c r="C189" t="n">
-        <v>-2827</v>
+        <v>-2773</v>
       </c>
       <c r="D189" t="n">
-        <v>21411</v>
+        <v>21409</v>
       </c>
       <c r="E189" t="n">
-        <v>24238</v>
+        <v>24182</v>
       </c>
       <c r="F189" t="n">
         <v>-987</v>
@@ -11386,22 +11398,22 @@
         <v>1146</v>
       </c>
       <c r="I189" t="n">
-        <v>9452</v>
+        <v>9349</v>
       </c>
       <c r="J189" t="n">
-        <v>14172</v>
+        <v>14319</v>
       </c>
       <c r="K189" t="n">
-        <v>4720</v>
+        <v>4970</v>
       </c>
       <c r="L189" t="n">
-        <v>4290</v>
+        <v>4279</v>
       </c>
       <c r="M189" t="n">
-        <v>1521</v>
+        <v>1528</v>
       </c>
       <c r="N189" t="n">
-        <v>8362</v>
+        <v>8378</v>
       </c>
       <c r="O189" t="n">
         <v>755</v>
@@ -11412,7 +11424,7 @@
       <c r="Q189" t="n">
         <v>-21</v>
       </c>
-      <c r="R189" s="1" t="n">
+      <c r="R189" s="2" t="n">
         <v>45870</v>
       </c>
     </row>
@@ -11423,16 +11435,16 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>497</v>
+        <v>611</v>
       </c>
       <c r="C190" t="n">
-        <v>-5410</v>
+        <v>-5333</v>
       </c>
       <c r="D190" t="n">
-        <v>22129</v>
+        <v>22126</v>
       </c>
       <c r="E190" t="n">
-        <v>27539</v>
+        <v>27459</v>
       </c>
       <c r="F190" t="n">
         <v>-2329</v>
@@ -11444,22 +11456,22 @@
         <v>2501</v>
       </c>
       <c r="I190" t="n">
-        <v>7701</v>
+        <v>7738</v>
       </c>
       <c r="J190" t="n">
-        <v>12801</v>
+        <v>13048</v>
       </c>
       <c r="K190" t="n">
-        <v>5100</v>
+        <v>5310</v>
       </c>
       <c r="L190" t="n">
-        <v>3889</v>
+        <v>3895</v>
       </c>
       <c r="M190" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="N190" t="n">
-        <v>6962</v>
+        <v>6976</v>
       </c>
       <c r="O190" t="n">
         <v>703</v>
@@ -11470,7 +11482,7 @@
       <c r="Q190" t="n">
         <v>89</v>
       </c>
-      <c r="R190" s="1" t="n">
+      <c r="R190" s="2" t="n">
         <v>45901</v>
       </c>
     </row>
@@ -11481,16 +11493,16 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="C191" t="n">
-        <v>-5948</v>
+        <v>-5884</v>
       </c>
       <c r="D191" t="n">
-        <v>23492</v>
+        <v>23490</v>
       </c>
       <c r="E191" t="n">
-        <v>29440</v>
+        <v>29374</v>
       </c>
       <c r="F191" t="n">
         <v>-2744</v>
@@ -11502,19 +11514,19 @@
         <v>2838</v>
       </c>
       <c r="I191" t="n">
-        <v>7951</v>
+        <v>7937</v>
       </c>
       <c r="J191" t="n">
-        <v>12601</v>
+        <v>12791</v>
       </c>
       <c r="K191" t="n">
-        <v>4650</v>
+        <v>4854</v>
       </c>
       <c r="L191" t="n">
-        <v>4101</v>
+        <v>4095</v>
       </c>
       <c r="M191" t="n">
-        <v>1639</v>
+        <v>1647</v>
       </c>
       <c r="N191" t="n">
         <v>6748</v>
@@ -11528,7 +11540,7 @@
       <c r="Q191" t="n">
         <v>-7</v>
       </c>
-      <c r="R191" s="1" t="n">
+      <c r="R191" s="2" t="n">
         <v>45931</v>
       </c>
     </row>
@@ -11539,16 +11551,16 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>-4159</v>
+        <v>-4198</v>
       </c>
       <c r="C192" t="n">
-        <v>-6418</v>
+        <v>-6351</v>
       </c>
       <c r="D192" t="n">
-        <v>22150</v>
+        <v>22146</v>
       </c>
       <c r="E192" t="n">
-        <v>28568</v>
+        <v>28497</v>
       </c>
       <c r="F192" t="n">
         <v>-2385</v>
@@ -11560,19 +11572,19 @@
         <v>2464</v>
       </c>
       <c r="I192" t="n">
-        <v>4193</v>
+        <v>4087</v>
       </c>
       <c r="J192" t="n">
-        <v>8921</v>
+        <v>9090</v>
       </c>
       <c r="K192" t="n">
-        <v>4728</v>
+        <v>5003</v>
       </c>
       <c r="L192" t="n">
-        <v>3328</v>
+        <v>3337</v>
       </c>
       <c r="M192" t="n">
-        <v>1611</v>
+        <v>1625</v>
       </c>
       <c r="N192" t="n">
         <v>4005</v>
@@ -11586,7 +11598,7 @@
       <c r="Q192" t="n">
         <v>13</v>
       </c>
-      <c r="R192" s="1" t="n">
+      <c r="R192" s="2" t="n">
         <v>45962</v>
       </c>
     </row>
@@ -11597,16 +11609,16 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-7494</v>
+        <v>-7420</v>
       </c>
       <c r="C193" t="n">
-        <v>-7576</v>
+        <v>-7460</v>
       </c>
       <c r="D193" t="n">
-        <v>25857</v>
+        <v>25850</v>
       </c>
       <c r="E193" t="n">
-        <v>33433</v>
+        <v>33310</v>
       </c>
       <c r="F193" t="n">
         <v>-1658</v>
@@ -11618,19 +11630,19 @@
         <v>1996</v>
       </c>
       <c r="I193" t="n">
-        <v>2649</v>
+        <v>2607</v>
       </c>
       <c r="J193" t="n">
-        <v>9222</v>
+        <v>9547</v>
       </c>
       <c r="K193" t="n">
-        <v>6573</v>
+        <v>6940</v>
       </c>
       <c r="L193" t="n">
-        <v>3590</v>
+        <v>3610</v>
       </c>
       <c r="M193" t="n">
-        <v>1916</v>
+        <v>1938</v>
       </c>
       <c r="N193" t="n">
         <v>3143</v>
@@ -11644,7 +11656,7 @@
       <c r="Q193" t="n">
         <v>-99</v>
       </c>
-      <c r="R193" s="1" t="n">
+      <c r="R193" s="2" t="n">
         <v>45992</v>
       </c>
     </row>
@@ -11655,13 +11667,13 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>-6724</v>
+        <v>-6739</v>
       </c>
       <c r="C194" t="n">
-        <v>-6884</v>
+        <v>-6885</v>
       </c>
       <c r="D194" t="n">
-        <v>19768</v>
+        <v>19767</v>
       </c>
       <c r="E194" t="n">
         <v>26652</v>
@@ -11676,13 +11688,13 @@
         <v>1658</v>
       </c>
       <c r="I194" t="n">
-        <v>2694</v>
+        <v>2680</v>
       </c>
       <c r="J194" t="n">
-        <v>7731</v>
+        <v>7734</v>
       </c>
       <c r="K194" t="n">
-        <v>5037</v>
+        <v>5054</v>
       </c>
       <c r="L194" t="n">
         <v>2874</v>
@@ -11702,7 +11714,7 @@
       <c r="Q194" t="n">
         <v>-314</v>
       </c>
-      <c r="R194" s="1" t="n">
+      <c r="R194" s="2" t="n">
         <v>46023</v>
       </c>
     </row>
@@ -11713,13 +11725,13 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>-7342</v>
+        <v>-7365</v>
       </c>
       <c r="C195" t="n">
-        <v>-7510</v>
+        <v>-7511</v>
       </c>
       <c r="D195" t="n">
-        <v>20637</v>
+        <v>20636</v>
       </c>
       <c r="E195" t="n">
         <v>28147</v>
@@ -11734,13 +11746,13 @@
         <v>2238</v>
       </c>
       <c r="I195" t="n">
-        <v>2276</v>
+        <v>2254</v>
       </c>
       <c r="J195" t="n">
-        <v>6371</v>
+        <v>6377</v>
       </c>
       <c r="K195" t="n">
-        <v>4095</v>
+        <v>4123</v>
       </c>
       <c r="L195" t="n">
         <v>2534</v>
@@ -11760,7 +11772,7 @@
       <c r="Q195" t="n">
         <v>-193</v>
       </c>
-      <c r="R195" s="1" t="n">
+      <c r="R195" s="2" t="n">
         <v>46054</v>
       </c>
     </row>
@@ -11771,16 +11783,16 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>-9567</v>
+        <v>-9604</v>
       </c>
       <c r="C196" t="n">
-        <v>-9469</v>
+        <v>-9472</v>
       </c>
       <c r="D196" t="n">
-        <v>21708</v>
+        <v>21704</v>
       </c>
       <c r="E196" t="n">
-        <v>31177</v>
+        <v>31176</v>
       </c>
       <c r="F196" t="n">
         <v>-1603</v>
@@ -11792,13 +11804,13 @@
         <v>1701</v>
       </c>
       <c r="I196" t="n">
-        <v>2585</v>
+        <v>2552</v>
       </c>
       <c r="J196" t="n">
-        <v>7513</v>
+        <v>7520</v>
       </c>
       <c r="K196" t="n">
-        <v>4928</v>
+        <v>4968</v>
       </c>
       <c r="L196" t="n">
         <v>3189</v>
@@ -11813,12 +11825,12 @@
         <v>659</v>
       </c>
       <c r="P196" t="n">
-        <v>-2438</v>
+        <v>-2439</v>
       </c>
       <c r="Q196" t="n">
         <v>-245</v>
       </c>
-      <c r="R196" s="1" t="n">
+      <c r="R196" s="2" t="n">
         <v>46082</v>
       </c>
     </row>
@@ -11829,13 +11841,13 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>-5467</v>
+        <v>-5505</v>
       </c>
       <c r="C197" t="n">
-        <v>-6898</v>
+        <v>-6900</v>
       </c>
       <c r="D197" t="n">
-        <v>24740</v>
+        <v>24738</v>
       </c>
       <c r="E197" t="n">
         <v>31638</v>
@@ -11850,13 +11862,13 @@
         <v>1152</v>
       </c>
       <c r="I197" t="n">
-        <v>3854</v>
+        <v>3819</v>
       </c>
       <c r="J197" t="n">
-        <v>8641</v>
+        <v>8648</v>
       </c>
       <c r="K197" t="n">
-        <v>4787</v>
+        <v>4829</v>
       </c>
       <c r="L197" t="n">
         <v>3300</v>
@@ -11871,12 +11883,12 @@
         <v>823</v>
       </c>
       <c r="P197" t="n">
-        <v>-2280</v>
+        <v>-2281</v>
       </c>
       <c r="Q197" t="n">
         <v>-143</v>
       </c>
-      <c r="R197" s="1" t="n">
+      <c r="R197" s="2" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -11887,16 +11899,16 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>-1254</v>
+        <v>-1320</v>
       </c>
       <c r="C198" t="n">
-        <v>-4426</v>
+        <v>-4452</v>
       </c>
       <c r="D198" t="n">
-        <v>21843</v>
+        <v>21819</v>
       </c>
       <c r="E198" t="n">
-        <v>26269</v>
+        <v>26271</v>
       </c>
       <c r="F198" t="n">
         <v>-563</v>
@@ -11908,13 +11920,13 @@
         <v>940</v>
       </c>
       <c r="I198" t="n">
-        <v>5547</v>
+        <v>5510</v>
       </c>
       <c r="J198" t="n">
-        <v>10223</v>
+        <v>10229</v>
       </c>
       <c r="K198" t="n">
-        <v>4676</v>
+        <v>4719</v>
       </c>
       <c r="L198" t="n">
         <v>3762</v>
@@ -11929,12 +11941,12 @@
         <v>1026</v>
       </c>
       <c r="P198" t="n">
-        <v>-2211</v>
+        <v>-2214</v>
       </c>
       <c r="Q198" t="n">
         <v>-164</v>
       </c>
-      <c r="R198" s="1" t="n">
+      <c r="R198" s="2" t="n">
         <v>46143</v>
       </c>
     </row>
@@ -11945,13 +11957,13 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>-4194</v>
+        <v>-4333</v>
       </c>
       <c r="C199" t="n">
-        <v>-8533</v>
+        <v>-8566</v>
       </c>
       <c r="D199" t="n">
-        <v>24429</v>
+        <v>24396</v>
       </c>
       <c r="E199" t="n">
         <v>32962</v>
@@ -11966,19 +11978,19 @@
         <v>1352</v>
       </c>
       <c r="I199" t="n">
-        <v>6851</v>
+        <v>6754</v>
       </c>
       <c r="J199" t="n">
-        <v>12169</v>
+        <v>12110</v>
       </c>
       <c r="K199" t="n">
-        <v>5318</v>
+        <v>5356</v>
       </c>
       <c r="L199" t="n">
-        <v>4246</v>
+        <v>4191</v>
       </c>
       <c r="M199" t="n">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="N199" t="n">
         <v>5799</v>
@@ -11987,13 +11999,71 @@
         <v>942</v>
       </c>
       <c r="P199" t="n">
-        <v>-1785</v>
+        <v>-1792</v>
       </c>
       <c r="Q199" t="n">
-        <v>-727</v>
-      </c>
-      <c r="R199" s="1" t="n">
+        <v>-729</v>
+      </c>
+      <c r="R199" s="2" t="n">
         <v>46174</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-7</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>36</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-5579</v>
+      </c>
+      <c r="D200" t="n">
+        <v>25185</v>
+      </c>
+      <c r="E200" t="n">
+        <v>30764</v>
+      </c>
+      <c r="F200" t="n">
+        <v>-462</v>
+      </c>
+      <c r="G200" t="n">
+        <v>484</v>
+      </c>
+      <c r="H200" t="n">
+        <v>946</v>
+      </c>
+      <c r="I200" t="n">
+        <v>8228</v>
+      </c>
+      <c r="J200" t="n">
+        <v>13325</v>
+      </c>
+      <c r="K200" t="n">
+        <v>5097</v>
+      </c>
+      <c r="L200" t="n">
+        <v>4585</v>
+      </c>
+      <c r="M200" t="n">
+        <v>1692</v>
+      </c>
+      <c r="N200" t="n">
+        <v>6964</v>
+      </c>
+      <c r="O200" t="n">
+        <v>996</v>
+      </c>
+      <c r="P200" t="n">
+        <v>-2557</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>-56</v>
+      </c>
+      <c r="R200" s="2" t="n">
+        <v>46204</v>
       </c>
     </row>
   </sheetData>

--- a/cari acik/odemeler_dengesi_raw.xlsx
+++ b/cari acik/odemeler_dengesi_raw.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,92 +421,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Cari İşlemler Dengesi</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Dış Ticaret Dengesi</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Toplam Mal İhracatı</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Toplam Mal İthalatı</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Parasal Olmayan Altın (net)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Altın İhracatı</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Altın İthalatı</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Hizmetler Dengesi</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Hizmet Gelirleri</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Hizmet Giderleri</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Taşımacılık - Gelir</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Taşımacılık - Gider</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Seyahat - Gelir</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Seyahat - Gider</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Birincil Gelir Dengesi</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>İkincil Gelir Dengesi</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Tarih_dt</t>
         </is>
@@ -578,7 +566,7 @@
       <c r="Q2" t="n">
         <v>115</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="R2" s="1" t="n">
         <v>40179</v>
       </c>
     </row>
@@ -636,7 +624,7 @@
       <c r="Q3" t="n">
         <v>72</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="R3" s="1" t="n">
         <v>40210</v>
       </c>
     </row>
@@ -694,7 +682,7 @@
       <c r="Q4" t="n">
         <v>114</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="R4" s="1" t="n">
         <v>40238</v>
       </c>
     </row>
@@ -752,7 +740,7 @@
       <c r="Q5" t="n">
         <v>82</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="R5" s="1" t="n">
         <v>40269</v>
       </c>
     </row>
@@ -810,7 +798,7 @@
       <c r="Q6" t="n">
         <v>73</v>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="R6" s="1" t="n">
         <v>40299</v>
       </c>
     </row>
@@ -868,7 +856,7 @@
       <c r="Q7" t="n">
         <v>121</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="R7" s="1" t="n">
         <v>40330</v>
       </c>
     </row>
@@ -926,7 +914,7 @@
       <c r="Q8" t="n">
         <v>109</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R8" s="1" t="n">
         <v>40360</v>
       </c>
     </row>
@@ -984,7 +972,7 @@
       <c r="Q9" t="n">
         <v>155</v>
       </c>
-      <c r="R9" s="2" t="n">
+      <c r="R9" s="1" t="n">
         <v>40391</v>
       </c>
     </row>
@@ -1042,7 +1030,7 @@
       <c r="Q10" t="n">
         <v>159</v>
       </c>
-      <c r="R10" s="2" t="n">
+      <c r="R10" s="1" t="n">
         <v>40422</v>
       </c>
     </row>
@@ -1100,7 +1088,7 @@
       <c r="Q11" t="n">
         <v>183</v>
       </c>
-      <c r="R11" s="2" t="n">
+      <c r="R11" s="1" t="n">
         <v>40452</v>
       </c>
     </row>
@@ -1158,7 +1146,7 @@
       <c r="Q12" t="n">
         <v>100</v>
       </c>
-      <c r="R12" s="2" t="n">
+      <c r="R12" s="1" t="n">
         <v>40483</v>
       </c>
     </row>
@@ -1216,7 +1204,7 @@
       <c r="Q13" t="n">
         <v>192</v>
       </c>
-      <c r="R13" s="2" t="n">
+      <c r="R13" s="1" t="n">
         <v>40513</v>
       </c>
     </row>
@@ -1274,7 +1262,7 @@
       <c r="Q14" t="n">
         <v>222</v>
       </c>
-      <c r="R14" s="2" t="n">
+      <c r="R14" s="1" t="n">
         <v>40544</v>
       </c>
     </row>
@@ -1332,7 +1320,7 @@
       <c r="Q15" t="n">
         <v>85</v>
       </c>
-      <c r="R15" s="2" t="n">
+      <c r="R15" s="1" t="n">
         <v>40575</v>
       </c>
     </row>
@@ -1390,7 +1378,7 @@
       <c r="Q16" t="n">
         <v>77</v>
       </c>
-      <c r="R16" s="2" t="n">
+      <c r="R16" s="1" t="n">
         <v>40603</v>
       </c>
     </row>
@@ -1448,7 +1436,7 @@
       <c r="Q17" t="n">
         <v>49</v>
       </c>
-      <c r="R17" s="2" t="n">
+      <c r="R17" s="1" t="n">
         <v>40634</v>
       </c>
     </row>
@@ -1506,7 +1494,7 @@
       <c r="Q18" t="n">
         <v>139</v>
       </c>
-      <c r="R18" s="2" t="n">
+      <c r="R18" s="1" t="n">
         <v>40664</v>
       </c>
     </row>
@@ -1564,7 +1552,7 @@
       <c r="Q19" t="n">
         <v>99</v>
       </c>
-      <c r="R19" s="2" t="n">
+      <c r="R19" s="1" t="n">
         <v>40695</v>
       </c>
     </row>
@@ -1622,7 +1610,7 @@
       <c r="Q20" t="n">
         <v>103</v>
       </c>
-      <c r="R20" s="2" t="n">
+      <c r="R20" s="1" t="n">
         <v>40725</v>
       </c>
     </row>
@@ -1680,7 +1668,7 @@
       <c r="Q21" t="n">
         <v>241</v>
       </c>
-      <c r="R21" s="2" t="n">
+      <c r="R21" s="1" t="n">
         <v>40756</v>
       </c>
     </row>
@@ -1738,7 +1726,7 @@
       <c r="Q22" t="n">
         <v>149</v>
       </c>
-      <c r="R22" s="2" t="n">
+      <c r="R22" s="1" t="n">
         <v>40787</v>
       </c>
     </row>
@@ -1796,7 +1784,7 @@
       <c r="Q23" t="n">
         <v>67</v>
       </c>
-      <c r="R23" s="2" t="n">
+      <c r="R23" s="1" t="n">
         <v>40817</v>
       </c>
     </row>
@@ -1854,7 +1842,7 @@
       <c r="Q24" t="n">
         <v>106</v>
       </c>
-      <c r="R24" s="2" t="n">
+      <c r="R24" s="1" t="n">
         <v>40848</v>
       </c>
     </row>
@@ -1912,7 +1900,7 @@
       <c r="Q25" t="n">
         <v>382</v>
       </c>
-      <c r="R25" s="2" t="n">
+      <c r="R25" s="1" t="n">
         <v>40878</v>
       </c>
     </row>
@@ -1970,7 +1958,7 @@
       <c r="Q26" t="n">
         <v>69</v>
       </c>
-      <c r="R26" s="2" t="n">
+      <c r="R26" s="1" t="n">
         <v>40909</v>
       </c>
     </row>
@@ -2028,7 +2016,7 @@
       <c r="Q27" t="n">
         <v>224</v>
       </c>
-      <c r="R27" s="2" t="n">
+      <c r="R27" s="1" t="n">
         <v>40940</v>
       </c>
     </row>
@@ -2086,7 +2074,7 @@
       <c r="Q28" t="n">
         <v>57</v>
       </c>
-      <c r="R28" s="2" t="n">
+      <c r="R28" s="1" t="n">
         <v>40969</v>
       </c>
     </row>
@@ -2144,7 +2132,7 @@
       <c r="Q29" t="n">
         <v>105</v>
       </c>
-      <c r="R29" s="2" t="n">
+      <c r="R29" s="1" t="n">
         <v>41000</v>
       </c>
     </row>
@@ -2202,7 +2190,7 @@
       <c r="Q30" t="n">
         <v>90</v>
       </c>
-      <c r="R30" s="2" t="n">
+      <c r="R30" s="1" t="n">
         <v>41030</v>
       </c>
     </row>
@@ -2260,7 +2248,7 @@
       <c r="Q31" t="n">
         <v>73</v>
       </c>
-      <c r="R31" s="2" t="n">
+      <c r="R31" s="1" t="n">
         <v>41061</v>
       </c>
     </row>
@@ -2318,7 +2306,7 @@
       <c r="Q32" t="n">
         <v>72</v>
       </c>
-      <c r="R32" s="2" t="n">
+      <c r="R32" s="1" t="n">
         <v>41091</v>
       </c>
     </row>
@@ -2376,7 +2364,7 @@
       <c r="Q33" t="n">
         <v>156</v>
       </c>
-      <c r="R33" s="2" t="n">
+      <c r="R33" s="1" t="n">
         <v>41122</v>
       </c>
     </row>
@@ -2434,7 +2422,7 @@
       <c r="Q34" t="n">
         <v>122</v>
       </c>
-      <c r="R34" s="2" t="n">
+      <c r="R34" s="1" t="n">
         <v>41153</v>
       </c>
     </row>
@@ -2492,7 +2480,7 @@
       <c r="Q35" t="n">
         <v>89</v>
       </c>
-      <c r="R35" s="2" t="n">
+      <c r="R35" s="1" t="n">
         <v>41183</v>
       </c>
     </row>
@@ -2550,7 +2538,7 @@
       <c r="Q36" t="n">
         <v>116</v>
       </c>
-      <c r="R36" s="2" t="n">
+      <c r="R36" s="1" t="n">
         <v>41214</v>
       </c>
     </row>
@@ -2608,7 +2596,7 @@
       <c r="Q37" t="n">
         <v>278</v>
       </c>
-      <c r="R37" s="2" t="n">
+      <c r="R37" s="1" t="n">
         <v>41244</v>
       </c>
     </row>
@@ -2666,7 +2654,7 @@
       <c r="Q38" t="n">
         <v>49</v>
       </c>
-      <c r="R38" s="2" t="n">
+      <c r="R38" s="1" t="n">
         <v>41275</v>
       </c>
     </row>
@@ -2724,7 +2712,7 @@
       <c r="Q39" t="n">
         <v>161</v>
       </c>
-      <c r="R39" s="2" t="n">
+      <c r="R39" s="1" t="n">
         <v>41306</v>
       </c>
     </row>
@@ -2782,7 +2770,7 @@
       <c r="Q40" t="n">
         <v>66</v>
       </c>
-      <c r="R40" s="2" t="n">
+      <c r="R40" s="1" t="n">
         <v>41334</v>
       </c>
     </row>
@@ -2840,7 +2828,7 @@
       <c r="Q41" t="n">
         <v>45</v>
       </c>
-      <c r="R41" s="2" t="n">
+      <c r="R41" s="1" t="n">
         <v>41365</v>
       </c>
     </row>
@@ -2898,7 +2886,7 @@
       <c r="Q42" t="n">
         <v>159</v>
       </c>
-      <c r="R42" s="2" t="n">
+      <c r="R42" s="1" t="n">
         <v>41395</v>
       </c>
     </row>
@@ -2956,7 +2944,7 @@
       <c r="Q43" t="n">
         <v>92</v>
       </c>
-      <c r="R43" s="2" t="n">
+      <c r="R43" s="1" t="n">
         <v>41426</v>
       </c>
     </row>
@@ -3014,7 +3002,7 @@
       <c r="Q44" t="n">
         <v>107</v>
       </c>
-      <c r="R44" s="2" t="n">
+      <c r="R44" s="1" t="n">
         <v>41456</v>
       </c>
     </row>
@@ -3072,7 +3060,7 @@
       <c r="Q45" t="n">
         <v>108</v>
       </c>
-      <c r="R45" s="2" t="n">
+      <c r="R45" s="1" t="n">
         <v>41487</v>
       </c>
     </row>
@@ -3130,7 +3118,7 @@
       <c r="Q46" t="n">
         <v>110</v>
       </c>
-      <c r="R46" s="2" t="n">
+      <c r="R46" s="1" t="n">
         <v>41518</v>
       </c>
     </row>
@@ -3188,7 +3176,7 @@
       <c r="Q47" t="n">
         <v>113</v>
       </c>
-      <c r="R47" s="2" t="n">
+      <c r="R47" s="1" t="n">
         <v>41548</v>
       </c>
     </row>
@@ -3246,7 +3234,7 @@
       <c r="Q48" t="n">
         <v>115</v>
       </c>
-      <c r="R48" s="2" t="n">
+      <c r="R48" s="1" t="n">
         <v>41579</v>
       </c>
     </row>
@@ -3304,7 +3292,7 @@
       <c r="Q49" t="n">
         <v>152</v>
       </c>
-      <c r="R49" s="2" t="n">
+      <c r="R49" s="1" t="n">
         <v>41609</v>
       </c>
     </row>
@@ -3362,7 +3350,7 @@
       <c r="Q50" t="n">
         <v>35</v>
       </c>
-      <c r="R50" s="2" t="n">
+      <c r="R50" s="1" t="n">
         <v>41640</v>
       </c>
     </row>
@@ -3420,7 +3408,7 @@
       <c r="Q51" t="n">
         <v>157</v>
       </c>
-      <c r="R51" s="2" t="n">
+      <c r="R51" s="1" t="n">
         <v>41671</v>
       </c>
     </row>
@@ -3478,7 +3466,7 @@
       <c r="Q52" t="n">
         <v>222</v>
       </c>
-      <c r="R52" s="2" t="n">
+      <c r="R52" s="1" t="n">
         <v>41699</v>
       </c>
     </row>
@@ -3536,7 +3524,7 @@
       <c r="Q53" t="n">
         <v>37</v>
       </c>
-      <c r="R53" s="2" t="n">
+      <c r="R53" s="1" t="n">
         <v>41730</v>
       </c>
     </row>
@@ -3594,7 +3582,7 @@
       <c r="Q54" t="n">
         <v>86</v>
       </c>
-      <c r="R54" s="2" t="n">
+      <c r="R54" s="1" t="n">
         <v>41760</v>
       </c>
     </row>
@@ -3652,7 +3640,7 @@
       <c r="Q55" t="n">
         <v>111</v>
       </c>
-      <c r="R55" s="2" t="n">
+      <c r="R55" s="1" t="n">
         <v>41791</v>
       </c>
     </row>
@@ -3710,7 +3698,7 @@
       <c r="Q56" t="n">
         <v>19</v>
       </c>
-      <c r="R56" s="2" t="n">
+      <c r="R56" s="1" t="n">
         <v>41821</v>
       </c>
     </row>
@@ -3768,7 +3756,7 @@
       <c r="Q57" t="n">
         <v>121</v>
       </c>
-      <c r="R57" s="2" t="n">
+      <c r="R57" s="1" t="n">
         <v>41852</v>
       </c>
     </row>
@@ -3826,7 +3814,7 @@
       <c r="Q58" t="n">
         <v>263</v>
       </c>
-      <c r="R58" s="2" t="n">
+      <c r="R58" s="1" t="n">
         <v>41883</v>
       </c>
     </row>
@@ -3884,7 +3872,7 @@
       <c r="Q59" t="n">
         <v>88</v>
       </c>
-      <c r="R59" s="2" t="n">
+      <c r="R59" s="1" t="n">
         <v>41913</v>
       </c>
     </row>
@@ -3942,7 +3930,7 @@
       <c r="Q60" t="n">
         <v>169</v>
       </c>
-      <c r="R60" s="2" t="n">
+      <c r="R60" s="1" t="n">
         <v>41944</v>
       </c>
     </row>
@@ -4000,7 +3988,7 @@
       <c r="Q61" t="n">
         <v>212</v>
       </c>
-      <c r="R61" s="2" t="n">
+      <c r="R61" s="1" t="n">
         <v>41974</v>
       </c>
     </row>
@@ -4058,7 +4046,7 @@
       <c r="Q62" t="n">
         <v>15</v>
       </c>
-      <c r="R62" s="2" t="n">
+      <c r="R62" s="1" t="n">
         <v>42005</v>
       </c>
     </row>
@@ -4116,7 +4104,7 @@
       <c r="Q63" t="n">
         <v>231</v>
       </c>
-      <c r="R63" s="2" t="n">
+      <c r="R63" s="1" t="n">
         <v>42036</v>
       </c>
     </row>
@@ -4174,7 +4162,7 @@
       <c r="Q64" t="n">
         <v>145</v>
       </c>
-      <c r="R64" s="2" t="n">
+      <c r="R64" s="1" t="n">
         <v>42064</v>
       </c>
     </row>
@@ -4232,7 +4220,7 @@
       <c r="Q65" t="n">
         <v>62</v>
       </c>
-      <c r="R65" s="2" t="n">
+      <c r="R65" s="1" t="n">
         <v>42095</v>
       </c>
     </row>
@@ -4290,7 +4278,7 @@
       <c r="Q66" t="n">
         <v>21</v>
       </c>
-      <c r="R66" s="2" t="n">
+      <c r="R66" s="1" t="n">
         <v>42125</v>
       </c>
     </row>
@@ -4348,7 +4336,7 @@
       <c r="Q67" t="n">
         <v>86</v>
       </c>
-      <c r="R67" s="2" t="n">
+      <c r="R67" s="1" t="n">
         <v>42156</v>
       </c>
     </row>
@@ -4406,7 +4394,7 @@
       <c r="Q68" t="n">
         <v>125</v>
       </c>
-      <c r="R68" s="2" t="n">
+      <c r="R68" s="1" t="n">
         <v>42186</v>
       </c>
     </row>
@@ -4464,7 +4452,7 @@
       <c r="Q69" t="n">
         <v>109</v>
       </c>
-      <c r="R69" s="2" t="n">
+      <c r="R69" s="1" t="n">
         <v>42217</v>
       </c>
     </row>
@@ -4522,7 +4510,7 @@
       <c r="Q70" t="n">
         <v>110</v>
       </c>
-      <c r="R70" s="2" t="n">
+      <c r="R70" s="1" t="n">
         <v>42248</v>
       </c>
     </row>
@@ -4580,7 +4568,7 @@
       <c r="Q71" t="n">
         <v>55</v>
       </c>
-      <c r="R71" s="2" t="n">
+      <c r="R71" s="1" t="n">
         <v>42278</v>
       </c>
     </row>
@@ -4638,7 +4626,7 @@
       <c r="Q72" t="n">
         <v>213</v>
       </c>
-      <c r="R72" s="2" t="n">
+      <c r="R72" s="1" t="n">
         <v>42309</v>
       </c>
     </row>
@@ -4696,7 +4684,7 @@
       <c r="Q73" t="n">
         <v>225</v>
       </c>
-      <c r="R73" s="2" t="n">
+      <c r="R73" s="1" t="n">
         <v>42339</v>
       </c>
     </row>
@@ -4754,7 +4742,7 @@
       <c r="Q74" t="n">
         <v>112</v>
       </c>
-      <c r="R74" s="2" t="n">
+      <c r="R74" s="1" t="n">
         <v>42370</v>
       </c>
     </row>
@@ -4812,7 +4800,7 @@
       <c r="Q75" t="n">
         <v>365</v>
       </c>
-      <c r="R75" s="2" t="n">
+      <c r="R75" s="1" t="n">
         <v>42401</v>
       </c>
     </row>
@@ -4870,7 +4858,7 @@
       <c r="Q76" t="n">
         <v>-19</v>
       </c>
-      <c r="R76" s="2" t="n">
+      <c r="R76" s="1" t="n">
         <v>42430</v>
       </c>
     </row>
@@ -4928,7 +4916,7 @@
       <c r="Q77" t="n">
         <v>292</v>
       </c>
-      <c r="R77" s="2" t="n">
+      <c r="R77" s="1" t="n">
         <v>42461</v>
       </c>
     </row>
@@ -4986,7 +4974,7 @@
       <c r="Q78" t="n">
         <v>-42</v>
       </c>
-      <c r="R78" s="2" t="n">
+      <c r="R78" s="1" t="n">
         <v>42491</v>
       </c>
     </row>
@@ -5044,7 +5032,7 @@
       <c r="Q79" t="n">
         <v>71</v>
       </c>
-      <c r="R79" s="2" t="n">
+      <c r="R79" s="1" t="n">
         <v>42522</v>
       </c>
     </row>
@@ -5102,7 +5090,7 @@
       <c r="Q80" t="n">
         <v>46</v>
       </c>
-      <c r="R80" s="2" t="n">
+      <c r="R80" s="1" t="n">
         <v>42552</v>
       </c>
     </row>
@@ -5160,7 +5148,7 @@
       <c r="Q81" t="n">
         <v>49</v>
       </c>
-      <c r="R81" s="2" t="n">
+      <c r="R81" s="1" t="n">
         <v>42583</v>
       </c>
     </row>
@@ -5218,7 +5206,7 @@
       <c r="Q82" t="n">
         <v>138</v>
       </c>
-      <c r="R82" s="2" t="n">
+      <c r="R82" s="1" t="n">
         <v>42614</v>
       </c>
     </row>
@@ -5276,7 +5264,7 @@
       <c r="Q83" t="n">
         <v>112</v>
       </c>
-      <c r="R83" s="2" t="n">
+      <c r="R83" s="1" t="n">
         <v>42644</v>
       </c>
     </row>
@@ -5334,7 +5322,7 @@
       <c r="Q84" t="n">
         <v>199</v>
       </c>
-      <c r="R84" s="2" t="n">
+      <c r="R84" s="1" t="n">
         <v>42675</v>
       </c>
     </row>
@@ -5392,7 +5380,7 @@
       <c r="Q85" t="n">
         <v>235</v>
       </c>
-      <c r="R85" s="2" t="n">
+      <c r="R85" s="1" t="n">
         <v>42705</v>
       </c>
     </row>
@@ -5450,7 +5438,7 @@
       <c r="Q86" t="n">
         <v>133</v>
       </c>
-      <c r="R86" s="2" t="n">
+      <c r="R86" s="1" t="n">
         <v>42736</v>
       </c>
     </row>
@@ -5508,7 +5496,7 @@
       <c r="Q87" t="n">
         <v>103</v>
       </c>
-      <c r="R87" s="2" t="n">
+      <c r="R87" s="1" t="n">
         <v>42767</v>
       </c>
     </row>
@@ -5566,7 +5554,7 @@
       <c r="Q88" t="n">
         <v>223</v>
       </c>
-      <c r="R88" s="2" t="n">
+      <c r="R88" s="1" t="n">
         <v>42795</v>
       </c>
     </row>
@@ -5624,7 +5612,7 @@
       <c r="Q89" t="n">
         <v>31</v>
       </c>
-      <c r="R89" s="2" t="n">
+      <c r="R89" s="1" t="n">
         <v>42826</v>
       </c>
     </row>
@@ -5682,7 +5670,7 @@
       <c r="Q90" t="n">
         <v>245</v>
       </c>
-      <c r="R90" s="2" t="n">
+      <c r="R90" s="1" t="n">
         <v>42856</v>
       </c>
     </row>
@@ -5740,7 +5728,7 @@
       <c r="Q91" t="n">
         <v>273</v>
       </c>
-      <c r="R91" s="2" t="n">
+      <c r="R91" s="1" t="n">
         <v>42887</v>
       </c>
     </row>
@@ -5798,7 +5786,7 @@
       <c r="Q92" t="n">
         <v>305</v>
       </c>
-      <c r="R92" s="2" t="n">
+      <c r="R92" s="1" t="n">
         <v>42917</v>
       </c>
     </row>
@@ -5856,7 +5844,7 @@
       <c r="Q93" t="n">
         <v>213</v>
       </c>
-      <c r="R93" s="2" t="n">
+      <c r="R93" s="1" t="n">
         <v>42948</v>
       </c>
     </row>
@@ -5914,7 +5902,7 @@
       <c r="Q94" t="n">
         <v>209</v>
       </c>
-      <c r="R94" s="2" t="n">
+      <c r="R94" s="1" t="n">
         <v>42979</v>
       </c>
     </row>
@@ -5972,7 +5960,7 @@
       <c r="Q95" t="n">
         <v>262</v>
       </c>
-      <c r="R95" s="2" t="n">
+      <c r="R95" s="1" t="n">
         <v>43009</v>
       </c>
     </row>
@@ -6030,7 +6018,7 @@
       <c r="Q96" t="n">
         <v>277</v>
       </c>
-      <c r="R96" s="2" t="n">
+      <c r="R96" s="1" t="n">
         <v>43040</v>
       </c>
     </row>
@@ -6088,7 +6076,7 @@
       <c r="Q97" t="n">
         <v>259</v>
       </c>
-      <c r="R97" s="2" t="n">
+      <c r="R97" s="1" t="n">
         <v>43070</v>
       </c>
     </row>
@@ -6146,7 +6134,7 @@
       <c r="Q98" t="n">
         <v>201</v>
       </c>
-      <c r="R98" s="2" t="n">
+      <c r="R98" s="1" t="n">
         <v>43101</v>
       </c>
     </row>
@@ -6204,7 +6192,7 @@
       <c r="Q99" t="n">
         <v>-9</v>
       </c>
-      <c r="R99" s="2" t="n">
+      <c r="R99" s="1" t="n">
         <v>43132</v>
       </c>
     </row>
@@ -6262,7 +6250,7 @@
       <c r="Q100" t="n">
         <v>-3</v>
       </c>
-      <c r="R100" s="2" t="n">
+      <c r="R100" s="1" t="n">
         <v>43160</v>
       </c>
     </row>
@@ -6320,7 +6308,7 @@
       <c r="Q101" t="n">
         <v>65</v>
       </c>
-      <c r="R101" s="2" t="n">
+      <c r="R101" s="1" t="n">
         <v>43191</v>
       </c>
     </row>
@@ -6378,7 +6366,7 @@
       <c r="Q102" t="n">
         <v>-145</v>
       </c>
-      <c r="R102" s="2" t="n">
+      <c r="R102" s="1" t="n">
         <v>43221</v>
       </c>
     </row>
@@ -6436,7 +6424,7 @@
       <c r="Q103" t="n">
         <v>35</v>
       </c>
-      <c r="R103" s="2" t="n">
+      <c r="R103" s="1" t="n">
         <v>43252</v>
       </c>
     </row>
@@ -6494,7 +6482,7 @@
       <c r="Q104" t="n">
         <v>62</v>
       </c>
-      <c r="R104" s="2" t="n">
+      <c r="R104" s="1" t="n">
         <v>43282</v>
       </c>
     </row>
@@ -6552,7 +6540,7 @@
       <c r="Q105" t="n">
         <v>28</v>
       </c>
-      <c r="R105" s="2" t="n">
+      <c r="R105" s="1" t="n">
         <v>43313</v>
       </c>
     </row>
@@ -6610,7 +6598,7 @@
       <c r="Q106" t="n">
         <v>104</v>
       </c>
-      <c r="R106" s="2" t="n">
+      <c r="R106" s="1" t="n">
         <v>43344</v>
       </c>
     </row>
@@ -6668,7 +6656,7 @@
       <c r="Q107" t="n">
         <v>111</v>
       </c>
-      <c r="R107" s="2" t="n">
+      <c r="R107" s="1" t="n">
         <v>43374</v>
       </c>
     </row>
@@ -6726,7 +6714,7 @@
       <c r="Q108" t="n">
         <v>212</v>
       </c>
-      <c r="R108" s="2" t="n">
+      <c r="R108" s="1" t="n">
         <v>43405</v>
       </c>
     </row>
@@ -6784,7 +6772,7 @@
       <c r="Q109" t="n">
         <v>120</v>
       </c>
-      <c r="R109" s="2" t="n">
+      <c r="R109" s="1" t="n">
         <v>43435</v>
       </c>
     </row>
@@ -6842,7 +6830,7 @@
       <c r="Q110" t="n">
         <v>92</v>
       </c>
-      <c r="R110" s="2" t="n">
+      <c r="R110" s="1" t="n">
         <v>43466</v>
       </c>
     </row>
@@ -6900,7 +6888,7 @@
       <c r="Q111" t="n">
         <v>-67</v>
       </c>
-      <c r="R111" s="2" t="n">
+      <c r="R111" s="1" t="n">
         <v>43497</v>
       </c>
     </row>
@@ -6958,7 +6946,7 @@
       <c r="Q112" t="n">
         <v>125</v>
       </c>
-      <c r="R112" s="2" t="n">
+      <c r="R112" s="1" t="n">
         <v>43525</v>
       </c>
     </row>
@@ -7016,7 +7004,7 @@
       <c r="Q113" t="n">
         <v>-16</v>
       </c>
-      <c r="R113" s="2" t="n">
+      <c r="R113" s="1" t="n">
         <v>43556</v>
       </c>
     </row>
@@ -7074,7 +7062,7 @@
       <c r="Q114" t="n">
         <v>-71</v>
       </c>
-      <c r="R114" s="2" t="n">
+      <c r="R114" s="1" t="n">
         <v>43586</v>
       </c>
     </row>
@@ -7132,7 +7120,7 @@
       <c r="Q115" t="n">
         <v>19</v>
       </c>
-      <c r="R115" s="2" t="n">
+      <c r="R115" s="1" t="n">
         <v>43617</v>
       </c>
     </row>
@@ -7190,7 +7178,7 @@
       <c r="Q116" t="n">
         <v>141</v>
       </c>
-      <c r="R116" s="2" t="n">
+      <c r="R116" s="1" t="n">
         <v>43647</v>
       </c>
     </row>
@@ -7248,7 +7236,7 @@
       <c r="Q117" t="n">
         <v>99</v>
       </c>
-      <c r="R117" s="2" t="n">
+      <c r="R117" s="1" t="n">
         <v>43678</v>
       </c>
     </row>
@@ -7306,7 +7294,7 @@
       <c r="Q118" t="n">
         <v>100</v>
       </c>
-      <c r="R118" s="2" t="n">
+      <c r="R118" s="1" t="n">
         <v>43709</v>
       </c>
     </row>
@@ -7364,7 +7352,7 @@
       <c r="Q119" t="n">
         <v>109</v>
       </c>
-      <c r="R119" s="2" t="n">
+      <c r="R119" s="1" t="n">
         <v>43739</v>
       </c>
     </row>
@@ -7422,7 +7410,7 @@
       <c r="Q120" t="n">
         <v>92</v>
       </c>
-      <c r="R120" s="2" t="n">
+      <c r="R120" s="1" t="n">
         <v>43770</v>
       </c>
     </row>
@@ -7480,7 +7468,7 @@
       <c r="Q121" t="n">
         <v>248</v>
       </c>
-      <c r="R121" s="2" t="n">
+      <c r="R121" s="1" t="n">
         <v>43800</v>
       </c>
     </row>
@@ -7538,7 +7526,7 @@
       <c r="Q122" t="n">
         <v>94</v>
       </c>
-      <c r="R122" s="2" t="n">
+      <c r="R122" s="1" t="n">
         <v>43831</v>
       </c>
     </row>
@@ -7596,7 +7584,7 @@
       <c r="Q123" t="n">
         <v>-130</v>
       </c>
-      <c r="R123" s="2" t="n">
+      <c r="R123" s="1" t="n">
         <v>43862</v>
       </c>
     </row>
@@ -7654,7 +7642,7 @@
       <c r="Q124" t="n">
         <v>-266</v>
       </c>
-      <c r="R124" s="2" t="n">
+      <c r="R124" s="1" t="n">
         <v>43891</v>
       </c>
     </row>
@@ -7712,7 +7700,7 @@
       <c r="Q125" t="n">
         <v>40</v>
       </c>
-      <c r="R125" s="2" t="n">
+      <c r="R125" s="1" t="n">
         <v>43922</v>
       </c>
     </row>
@@ -7770,7 +7758,7 @@
       <c r="Q126" t="n">
         <v>-35</v>
       </c>
-      <c r="R126" s="2" t="n">
+      <c r="R126" s="1" t="n">
         <v>43952</v>
       </c>
     </row>
@@ -7828,7 +7816,7 @@
       <c r="Q127" t="n">
         <v>-60</v>
       </c>
-      <c r="R127" s="2" t="n">
+      <c r="R127" s="1" t="n">
         <v>43983</v>
       </c>
     </row>
@@ -7886,7 +7874,7 @@
       <c r="Q128" t="n">
         <v>85</v>
       </c>
-      <c r="R128" s="2" t="n">
+      <c r="R128" s="1" t="n">
         <v>44013</v>
       </c>
     </row>
@@ -7944,7 +7932,7 @@
       <c r="Q129" t="n">
         <v>150</v>
       </c>
-      <c r="R129" s="2" t="n">
+      <c r="R129" s="1" t="n">
         <v>44044</v>
       </c>
     </row>
@@ -8002,7 +7990,7 @@
       <c r="Q130" t="n">
         <v>206</v>
       </c>
-      <c r="R130" s="2" t="n">
+      <c r="R130" s="1" t="n">
         <v>44075</v>
       </c>
     </row>
@@ -8060,7 +8048,7 @@
       <c r="Q131" t="n">
         <v>-23</v>
       </c>
-      <c r="R131" s="2" t="n">
+      <c r="R131" s="1" t="n">
         <v>44105</v>
       </c>
     </row>
@@ -8118,7 +8106,7 @@
       <c r="Q132" t="n">
         <v>174</v>
       </c>
-      <c r="R132" s="2" t="n">
+      <c r="R132" s="1" t="n">
         <v>44136</v>
       </c>
     </row>
@@ -8176,7 +8164,7 @@
       <c r="Q133" t="n">
         <v>-34</v>
       </c>
-      <c r="R133" s="2" t="n">
+      <c r="R133" s="1" t="n">
         <v>44166</v>
       </c>
     </row>
@@ -8234,7 +8222,7 @@
       <c r="Q134" t="n">
         <v>44</v>
       </c>
-      <c r="R134" s="2" t="n">
+      <c r="R134" s="1" t="n">
         <v>44197</v>
       </c>
     </row>
@@ -8292,7 +8280,7 @@
       <c r="Q135" t="n">
         <v>146</v>
       </c>
-      <c r="R135" s="2" t="n">
+      <c r="R135" s="1" t="n">
         <v>44228</v>
       </c>
     </row>
@@ -8350,7 +8338,7 @@
       <c r="Q136" t="n">
         <v>44</v>
       </c>
-      <c r="R136" s="2" t="n">
+      <c r="R136" s="1" t="n">
         <v>44256</v>
       </c>
     </row>
@@ -8408,7 +8396,7 @@
       <c r="Q137" t="n">
         <v>282</v>
       </c>
-      <c r="R137" s="2" t="n">
+      <c r="R137" s="1" t="n">
         <v>44287</v>
       </c>
     </row>
@@ -8466,7 +8454,7 @@
       <c r="Q138" t="n">
         <v>152</v>
       </c>
-      <c r="R138" s="2" t="n">
+      <c r="R138" s="1" t="n">
         <v>44317</v>
       </c>
     </row>
@@ -8524,7 +8512,7 @@
       <c r="Q139" t="n">
         <v>-23</v>
       </c>
-      <c r="R139" s="2" t="n">
+      <c r="R139" s="1" t="n">
         <v>44348</v>
       </c>
     </row>
@@ -8582,7 +8570,7 @@
       <c r="Q140" t="n">
         <v>53</v>
       </c>
-      <c r="R140" s="2" t="n">
+      <c r="R140" s="1" t="n">
         <v>44378</v>
       </c>
     </row>
@@ -8640,7 +8628,7 @@
       <c r="Q141" t="n">
         <v>81</v>
       </c>
-      <c r="R141" s="2" t="n">
+      <c r="R141" s="1" t="n">
         <v>44409</v>
       </c>
     </row>
@@ -8698,7 +8686,7 @@
       <c r="Q142" t="n">
         <v>50</v>
       </c>
-      <c r="R142" s="2" t="n">
+      <c r="R142" s="1" t="n">
         <v>44440</v>
       </c>
     </row>
@@ -8756,7 +8744,7 @@
       <c r="Q143" t="n">
         <v>115</v>
       </c>
-      <c r="R143" s="2" t="n">
+      <c r="R143" s="1" t="n">
         <v>44470</v>
       </c>
     </row>
@@ -8814,7 +8802,7 @@
       <c r="Q144" t="n">
         <v>-106</v>
       </c>
-      <c r="R144" s="2" t="n">
+      <c r="R144" s="1" t="n">
         <v>44501</v>
       </c>
     </row>
@@ -8872,7 +8860,7 @@
       <c r="Q145" t="n">
         <v>112</v>
       </c>
-      <c r="R145" s="2" t="n">
+      <c r="R145" s="1" t="n">
         <v>44531</v>
       </c>
     </row>
@@ -8930,7 +8918,7 @@
       <c r="Q146" t="n">
         <v>-158</v>
       </c>
-      <c r="R146" s="2" t="n">
+      <c r="R146" s="1" t="n">
         <v>44562</v>
       </c>
     </row>
@@ -8988,7 +8976,7 @@
       <c r="Q147" t="n">
         <v>-43</v>
       </c>
-      <c r="R147" s="2" t="n">
+      <c r="R147" s="1" t="n">
         <v>44593</v>
       </c>
     </row>
@@ -9046,7 +9034,7 @@
       <c r="Q148" t="n">
         <v>-190</v>
       </c>
-      <c r="R148" s="2" t="n">
+      <c r="R148" s="1" t="n">
         <v>44621</v>
       </c>
     </row>
@@ -9104,7 +9092,7 @@
       <c r="Q149" t="n">
         <v>-107</v>
       </c>
-      <c r="R149" s="2" t="n">
+      <c r="R149" s="1" t="n">
         <v>44652</v>
       </c>
     </row>
@@ -9162,7 +9150,7 @@
       <c r="Q150" t="n">
         <v>-92</v>
       </c>
-      <c r="R150" s="2" t="n">
+      <c r="R150" s="1" t="n">
         <v>44682</v>
       </c>
     </row>
@@ -9220,7 +9208,7 @@
       <c r="Q151" t="n">
         <v>-123</v>
       </c>
-      <c r="R151" s="2" t="n">
+      <c r="R151" s="1" t="n">
         <v>44713</v>
       </c>
     </row>
@@ -9278,7 +9266,7 @@
       <c r="Q152" t="n">
         <v>60</v>
       </c>
-      <c r="R152" s="2" t="n">
+      <c r="R152" s="1" t="n">
         <v>44743</v>
       </c>
     </row>
@@ -9336,7 +9324,7 @@
       <c r="Q153" t="n">
         <v>53</v>
       </c>
-      <c r="R153" s="2" t="n">
+      <c r="R153" s="1" t="n">
         <v>44774</v>
       </c>
     </row>
@@ -9394,7 +9382,7 @@
       <c r="Q154" t="n">
         <v>1</v>
       </c>
-      <c r="R154" s="2" t="n">
+      <c r="R154" s="1" t="n">
         <v>44805</v>
       </c>
     </row>
@@ -9452,7 +9440,7 @@
       <c r="Q155" t="n">
         <v>34</v>
       </c>
-      <c r="R155" s="2" t="n">
+      <c r="R155" s="1" t="n">
         <v>44835</v>
       </c>
     </row>
@@ -9510,7 +9498,7 @@
       <c r="Q156" t="n">
         <v>-15</v>
       </c>
-      <c r="R156" s="2" t="n">
+      <c r="R156" s="1" t="n">
         <v>44866</v>
       </c>
     </row>
@@ -9568,7 +9556,7 @@
       <c r="Q157" t="n">
         <v>211</v>
       </c>
-      <c r="R157" s="2" t="n">
+      <c r="R157" s="1" t="n">
         <v>44896</v>
       </c>
     </row>
@@ -9626,7 +9614,7 @@
       <c r="Q158" t="n">
         <v>-228</v>
       </c>
-      <c r="R158" s="2" t="n">
+      <c r="R158" s="1" t="n">
         <v>44927</v>
       </c>
     </row>
@@ -9684,7 +9672,7 @@
       <c r="Q159" t="n">
         <v>157</v>
       </c>
-      <c r="R159" s="2" t="n">
+      <c r="R159" s="1" t="n">
         <v>44958</v>
       </c>
     </row>
@@ -9742,7 +9730,7 @@
       <c r="Q160" t="n">
         <v>77</v>
       </c>
-      <c r="R160" s="2" t="n">
+      <c r="R160" s="1" t="n">
         <v>44986</v>
       </c>
     </row>
@@ -9800,7 +9788,7 @@
       <c r="Q161" t="n">
         <v>60</v>
       </c>
-      <c r="R161" s="2" t="n">
+      <c r="R161" s="1" t="n">
         <v>45017</v>
       </c>
     </row>
@@ -9858,7 +9846,7 @@
       <c r="Q162" t="n">
         <v>21</v>
       </c>
-      <c r="R162" s="2" t="n">
+      <c r="R162" s="1" t="n">
         <v>45047</v>
       </c>
     </row>
@@ -9916,7 +9904,7 @@
       <c r="Q163" t="n">
         <v>190</v>
       </c>
-      <c r="R163" s="2" t="n">
+      <c r="R163" s="1" t="n">
         <v>45078</v>
       </c>
     </row>
@@ -9974,7 +9962,7 @@
       <c r="Q164" t="n">
         <v>-81</v>
       </c>
-      <c r="R164" s="2" t="n">
+      <c r="R164" s="1" t="n">
         <v>45108</v>
       </c>
     </row>
@@ -10032,7 +10020,7 @@
       <c r="Q165" t="n">
         <v>89</v>
       </c>
-      <c r="R165" s="2" t="n">
+      <c r="R165" s="1" t="n">
         <v>45139</v>
       </c>
     </row>
@@ -10090,7 +10078,7 @@
       <c r="Q166" t="n">
         <v>197</v>
       </c>
-      <c r="R166" s="2" t="n">
+      <c r="R166" s="1" t="n">
         <v>45170</v>
       </c>
     </row>
@@ -10148,7 +10136,7 @@
       <c r="Q167" t="n">
         <v>-53</v>
       </c>
-      <c r="R167" s="2" t="n">
+      <c r="R167" s="1" t="n">
         <v>45200</v>
       </c>
     </row>
@@ -10206,7 +10194,7 @@
       <c r="Q168" t="n">
         <v>-21</v>
       </c>
-      <c r="R168" s="2" t="n">
+      <c r="R168" s="1" t="n">
         <v>45231</v>
       </c>
     </row>
@@ -10264,7 +10252,7 @@
       <c r="Q169" t="n">
         <v>149</v>
       </c>
-      <c r="R169" s="2" t="n">
+      <c r="R169" s="1" t="n">
         <v>45261</v>
       </c>
     </row>
@@ -10322,7 +10310,7 @@
       <c r="Q170" t="n">
         <v>-157</v>
       </c>
-      <c r="R170" s="2" t="n">
+      <c r="R170" s="1" t="n">
         <v>45292</v>
       </c>
     </row>
@@ -10380,7 +10368,7 @@
       <c r="Q171" t="n">
         <v>-123</v>
       </c>
-      <c r="R171" s="2" t="n">
+      <c r="R171" s="1" t="n">
         <v>45323</v>
       </c>
     </row>
@@ -10438,7 +10426,7 @@
       <c r="Q172" t="n">
         <v>-206</v>
       </c>
-      <c r="R172" s="2" t="n">
+      <c r="R172" s="1" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -10496,7 +10484,7 @@
       <c r="Q173" t="n">
         <v>520</v>
       </c>
-      <c r="R173" s="2" t="n">
+      <c r="R173" s="1" t="n">
         <v>45383</v>
       </c>
     </row>
@@ -10554,7 +10542,7 @@
       <c r="Q174" t="n">
         <v>-152</v>
       </c>
-      <c r="R174" s="2" t="n">
+      <c r="R174" s="1" t="n">
         <v>45413</v>
       </c>
     </row>
@@ -10612,7 +10600,7 @@
       <c r="Q175" t="n">
         <v>3</v>
       </c>
-      <c r="R175" s="2" t="n">
+      <c r="R175" s="1" t="n">
         <v>45444</v>
       </c>
     </row>
@@ -10670,7 +10658,7 @@
       <c r="Q176" t="n">
         <v>92</v>
       </c>
-      <c r="R176" s="2" t="n">
+      <c r="R176" s="1" t="n">
         <v>45474</v>
       </c>
     </row>
@@ -10728,7 +10716,7 @@
       <c r="Q177" t="n">
         <v>-5</v>
       </c>
-      <c r="R177" s="2" t="n">
+      <c r="R177" s="1" t="n">
         <v>45505</v>
       </c>
     </row>
@@ -10786,7 +10774,7 @@
       <c r="Q178" t="n">
         <v>-19</v>
       </c>
-      <c r="R178" s="2" t="n">
+      <c r="R178" s="1" t="n">
         <v>45536</v>
       </c>
     </row>
@@ -10844,7 +10832,7 @@
       <c r="Q179" t="n">
         <v>-15</v>
       </c>
-      <c r="R179" s="2" t="n">
+      <c r="R179" s="1" t="n">
         <v>45566</v>
       </c>
     </row>
@@ -10902,7 +10890,7 @@
       <c r="Q180" t="n">
         <v>21</v>
       </c>
-      <c r="R180" s="2" t="n">
+      <c r="R180" s="1" t="n">
         <v>45597</v>
       </c>
     </row>
@@ -10960,7 +10948,7 @@
       <c r="Q181" t="n">
         <v>113</v>
       </c>
-      <c r="R181" s="2" t="n">
+      <c r="R181" s="1" t="n">
         <v>45627</v>
       </c>
     </row>
@@ -11018,7 +11006,7 @@
       <c r="Q182" t="n">
         <v>-154</v>
       </c>
-      <c r="R182" s="2" t="n">
+      <c r="R182" s="1" t="n">
         <v>45658</v>
       </c>
     </row>
@@ -11076,7 +11064,7 @@
       <c r="Q183" t="n">
         <v>8</v>
       </c>
-      <c r="R183" s="2" t="n">
+      <c r="R183" s="1" t="n">
         <v>45689</v>
       </c>
     </row>
@@ -11134,7 +11122,7 @@
       <c r="Q184" t="n">
         <v>-9</v>
       </c>
-      <c r="R184" s="2" t="n">
+      <c r="R184" s="1" t="n">
         <v>45717</v>
       </c>
     </row>
@@ -11192,7 +11180,7 @@
       <c r="Q185" t="n">
         <v>-104</v>
       </c>
-      <c r="R185" s="2" t="n">
+      <c r="R185" s="1" t="n">
         <v>45748</v>
       </c>
     </row>
@@ -11250,7 +11238,7 @@
       <c r="Q186" t="n">
         <v>-25</v>
       </c>
-      <c r="R186" s="2" t="n">
+      <c r="R186" s="1" t="n">
         <v>45778</v>
       </c>
     </row>
@@ -11308,7 +11296,7 @@
       <c r="Q187" t="n">
         <v>-82</v>
       </c>
-      <c r="R187" s="2" t="n">
+      <c r="R187" s="1" t="n">
         <v>45809</v>
       </c>
     </row>
@@ -11366,7 +11354,7 @@
       <c r="Q188" t="n">
         <v>-153</v>
       </c>
-      <c r="R188" s="2" t="n">
+      <c r="R188" s="1" t="n">
         <v>45839</v>
       </c>
     </row>
@@ -11424,7 +11412,7 @@
       <c r="Q189" t="n">
         <v>-21</v>
       </c>
-      <c r="R189" s="2" t="n">
+      <c r="R189" s="1" t="n">
         <v>45870</v>
       </c>
     </row>
@@ -11482,7 +11470,7 @@
       <c r="Q190" t="n">
         <v>89</v>
       </c>
-      <c r="R190" s="2" t="n">
+      <c r="R190" s="1" t="n">
         <v>45901</v>
       </c>
     </row>
@@ -11540,7 +11528,7 @@
       <c r="Q191" t="n">
         <v>-7</v>
       </c>
-      <c r="R191" s="2" t="n">
+      <c r="R191" s="1" t="n">
         <v>45931</v>
       </c>
     </row>
@@ -11598,7 +11586,7 @@
       <c r="Q192" t="n">
         <v>13</v>
       </c>
-      <c r="R192" s="2" t="n">
+      <c r="R192" s="1" t="n">
         <v>45962</v>
       </c>
     </row>
@@ -11656,7 +11644,7 @@
       <c r="Q193" t="n">
         <v>-99</v>
       </c>
-      <c r="R193" s="2" t="n">
+      <c r="R193" s="1" t="n">
         <v>45992</v>
       </c>
     </row>
@@ -11714,7 +11702,7 @@
       <c r="Q194" t="n">
         <v>-314</v>
       </c>
-      <c r="R194" s="2" t="n">
+      <c r="R194" s="1" t="n">
         <v>46023</v>
       </c>
     </row>
@@ -11772,7 +11760,7 @@
       <c r="Q195" t="n">
         <v>-193</v>
       </c>
-      <c r="R195" s="2" t="n">
+      <c r="R195" s="1" t="n">
         <v>46054</v>
       </c>
     </row>
@@ -11830,7 +11818,7 @@
       <c r="Q196" t="n">
         <v>-245</v>
       </c>
-      <c r="R196" s="2" t="n">
+      <c r="R196" s="1" t="n">
         <v>46082</v>
       </c>
     </row>
@@ -11888,7 +11876,7 @@
       <c r="Q197" t="n">
         <v>-143</v>
       </c>
-      <c r="R197" s="2" t="n">
+      <c r="R197" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -11946,7 +11934,7 @@
       <c r="Q198" t="n">
         <v>-164</v>
       </c>
-      <c r="R198" s="2" t="n">
+      <c r="R198" s="1" t="n">
         <v>46143</v>
       </c>
     </row>
@@ -12004,7 +11992,7 @@
       <c r="Q199" t="n">
         <v>-729</v>
       </c>
-      <c r="R199" s="2" t="n">
+      <c r="R199" s="1" t="n">
         <v>46174</v>
       </c>
     </row>
@@ -12062,7 +12050,7 @@
       <c r="Q200" t="n">
         <v>-56</v>
       </c>
-      <c r="R200" s="2" t="n">
+      <c r="R200" s="1" t="n">
         <v>46204</v>
       </c>
     </row>

--- a/cari acik/odemeler_dengesi_raw.xlsx
+++ b/cari acik/odemeler_dengesi_raw.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,92 +433,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Cari İşlemler Dengesi</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Dış Ticaret Dengesi</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Toplam Mal İhracatı</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Toplam Mal İthalatı</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Parasal Olmayan Altın (net)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Altın İhracatı</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Altın İthalatı</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Hizmetler Dengesi</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Hizmet Gelirleri</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Hizmet Giderleri</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Taşımacılık - Gelir</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Taşımacılık - Gider</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Seyahat - Gelir</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Seyahat - Gider</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Birincil Gelir Dengesi</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>İkincil Gelir Dengesi</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Tarih_dt</t>
         </is>
@@ -566,7 +578,7 @@
       <c r="Q2" t="n">
         <v>115</v>
       </c>
-      <c r="R2" s="1" t="n">
+      <c r="R2" s="2" t="n">
         <v>40179</v>
       </c>
     </row>
@@ -624,7 +636,7 @@
       <c r="Q3" t="n">
         <v>72</v>
       </c>
-      <c r="R3" s="1" t="n">
+      <c r="R3" s="2" t="n">
         <v>40210</v>
       </c>
     </row>
@@ -682,7 +694,7 @@
       <c r="Q4" t="n">
         <v>114</v>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="R4" s="2" t="n">
         <v>40238</v>
       </c>
     </row>
@@ -740,7 +752,7 @@
       <c r="Q5" t="n">
         <v>82</v>
       </c>
-      <c r="R5" s="1" t="n">
+      <c r="R5" s="2" t="n">
         <v>40269</v>
       </c>
     </row>
@@ -798,7 +810,7 @@
       <c r="Q6" t="n">
         <v>73</v>
       </c>
-      <c r="R6" s="1" t="n">
+      <c r="R6" s="2" t="n">
         <v>40299</v>
       </c>
     </row>
@@ -856,7 +868,7 @@
       <c r="Q7" t="n">
         <v>121</v>
       </c>
-      <c r="R7" s="1" t="n">
+      <c r="R7" s="2" t="n">
         <v>40330</v>
       </c>
     </row>
@@ -914,7 +926,7 @@
       <c r="Q8" t="n">
         <v>109</v>
       </c>
-      <c r="R8" s="1" t="n">
+      <c r="R8" s="2" t="n">
         <v>40360</v>
       </c>
     </row>
@@ -972,7 +984,7 @@
       <c r="Q9" t="n">
         <v>155</v>
       </c>
-      <c r="R9" s="1" t="n">
+      <c r="R9" s="2" t="n">
         <v>40391</v>
       </c>
     </row>
@@ -1030,7 +1042,7 @@
       <c r="Q10" t="n">
         <v>159</v>
       </c>
-      <c r="R10" s="1" t="n">
+      <c r="R10" s="2" t="n">
         <v>40422</v>
       </c>
     </row>
@@ -1088,7 +1100,7 @@
       <c r="Q11" t="n">
         <v>183</v>
       </c>
-      <c r="R11" s="1" t="n">
+      <c r="R11" s="2" t="n">
         <v>40452</v>
       </c>
     </row>
@@ -1146,7 +1158,7 @@
       <c r="Q12" t="n">
         <v>100</v>
       </c>
-      <c r="R12" s="1" t="n">
+      <c r="R12" s="2" t="n">
         <v>40483</v>
       </c>
     </row>
@@ -1204,7 +1216,7 @@
       <c r="Q13" t="n">
         <v>192</v>
       </c>
-      <c r="R13" s="1" t="n">
+      <c r="R13" s="2" t="n">
         <v>40513</v>
       </c>
     </row>
@@ -1262,7 +1274,7 @@
       <c r="Q14" t="n">
         <v>222</v>
       </c>
-      <c r="R14" s="1" t="n">
+      <c r="R14" s="2" t="n">
         <v>40544</v>
       </c>
     </row>
@@ -1320,7 +1332,7 @@
       <c r="Q15" t="n">
         <v>85</v>
       </c>
-      <c r="R15" s="1" t="n">
+      <c r="R15" s="2" t="n">
         <v>40575</v>
       </c>
     </row>
@@ -1378,7 +1390,7 @@
       <c r="Q16" t="n">
         <v>77</v>
       </c>
-      <c r="R16" s="1" t="n">
+      <c r="R16" s="2" t="n">
         <v>40603</v>
       </c>
     </row>
@@ -1436,7 +1448,7 @@
       <c r="Q17" t="n">
         <v>49</v>
       </c>
-      <c r="R17" s="1" t="n">
+      <c r="R17" s="2" t="n">
         <v>40634</v>
       </c>
     </row>
@@ -1494,7 +1506,7 @@
       <c r="Q18" t="n">
         <v>139</v>
       </c>
-      <c r="R18" s="1" t="n">
+      <c r="R18" s="2" t="n">
         <v>40664</v>
       </c>
     </row>
@@ -1552,7 +1564,7 @@
       <c r="Q19" t="n">
         <v>99</v>
       </c>
-      <c r="R19" s="1" t="n">
+      <c r="R19" s="2" t="n">
         <v>40695</v>
       </c>
     </row>
@@ -1610,7 +1622,7 @@
       <c r="Q20" t="n">
         <v>103</v>
       </c>
-      <c r="R20" s="1" t="n">
+      <c r="R20" s="2" t="n">
         <v>40725</v>
       </c>
     </row>
@@ -1668,7 +1680,7 @@
       <c r="Q21" t="n">
         <v>241</v>
       </c>
-      <c r="R21" s="1" t="n">
+      <c r="R21" s="2" t="n">
         <v>40756</v>
       </c>
     </row>
@@ -1726,7 +1738,7 @@
       <c r="Q22" t="n">
         <v>149</v>
       </c>
-      <c r="R22" s="1" t="n">
+      <c r="R22" s="2" t="n">
         <v>40787</v>
       </c>
     </row>
@@ -1784,7 +1796,7 @@
       <c r="Q23" t="n">
         <v>67</v>
       </c>
-      <c r="R23" s="1" t="n">
+      <c r="R23" s="2" t="n">
         <v>40817</v>
       </c>
     </row>
@@ -1842,7 +1854,7 @@
       <c r="Q24" t="n">
         <v>106</v>
       </c>
-      <c r="R24" s="1" t="n">
+      <c r="R24" s="2" t="n">
         <v>40848</v>
       </c>
     </row>
@@ -1900,7 +1912,7 @@
       <c r="Q25" t="n">
         <v>382</v>
       </c>
-      <c r="R25" s="1" t="n">
+      <c r="R25" s="2" t="n">
         <v>40878</v>
       </c>
     </row>
@@ -1958,7 +1970,7 @@
       <c r="Q26" t="n">
         <v>69</v>
       </c>
-      <c r="R26" s="1" t="n">
+      <c r="R26" s="2" t="n">
         <v>40909</v>
       </c>
     </row>
@@ -2016,7 +2028,7 @@
       <c r="Q27" t="n">
         <v>224</v>
       </c>
-      <c r="R27" s="1" t="n">
+      <c r="R27" s="2" t="n">
         <v>40940</v>
       </c>
     </row>
@@ -2074,7 +2086,7 @@
       <c r="Q28" t="n">
         <v>57</v>
       </c>
-      <c r="R28" s="1" t="n">
+      <c r="R28" s="2" t="n">
         <v>40969</v>
       </c>
     </row>
@@ -2132,7 +2144,7 @@
       <c r="Q29" t="n">
         <v>105</v>
       </c>
-      <c r="R29" s="1" t="n">
+      <c r="R29" s="2" t="n">
         <v>41000</v>
       </c>
     </row>
@@ -2190,7 +2202,7 @@
       <c r="Q30" t="n">
         <v>90</v>
       </c>
-      <c r="R30" s="1" t="n">
+      <c r="R30" s="2" t="n">
         <v>41030</v>
       </c>
     </row>
@@ -2248,7 +2260,7 @@
       <c r="Q31" t="n">
         <v>73</v>
       </c>
-      <c r="R31" s="1" t="n">
+      <c r="R31" s="2" t="n">
         <v>41061</v>
       </c>
     </row>
@@ -2306,7 +2318,7 @@
       <c r="Q32" t="n">
         <v>72</v>
       </c>
-      <c r="R32" s="1" t="n">
+      <c r="R32" s="2" t="n">
         <v>41091</v>
       </c>
     </row>
@@ -2364,7 +2376,7 @@
       <c r="Q33" t="n">
         <v>156</v>
       </c>
-      <c r="R33" s="1" t="n">
+      <c r="R33" s="2" t="n">
         <v>41122</v>
       </c>
     </row>
@@ -2422,7 +2434,7 @@
       <c r="Q34" t="n">
         <v>122</v>
       </c>
-      <c r="R34" s="1" t="n">
+      <c r="R34" s="2" t="n">
         <v>41153</v>
       </c>
     </row>
@@ -2480,7 +2492,7 @@
       <c r="Q35" t="n">
         <v>89</v>
       </c>
-      <c r="R35" s="1" t="n">
+      <c r="R35" s="2" t="n">
         <v>41183</v>
       </c>
     </row>
@@ -2538,7 +2550,7 @@
       <c r="Q36" t="n">
         <v>116</v>
       </c>
-      <c r="R36" s="1" t="n">
+      <c r="R36" s="2" t="n">
         <v>41214</v>
       </c>
     </row>
@@ -2596,7 +2608,7 @@
       <c r="Q37" t="n">
         <v>278</v>
       </c>
-      <c r="R37" s="1" t="n">
+      <c r="R37" s="2" t="n">
         <v>41244</v>
       </c>
     </row>
@@ -2654,7 +2666,7 @@
       <c r="Q38" t="n">
         <v>49</v>
       </c>
-      <c r="R38" s="1" t="n">
+      <c r="R38" s="2" t="n">
         <v>41275</v>
       </c>
     </row>
@@ -2712,7 +2724,7 @@
       <c r="Q39" t="n">
         <v>161</v>
       </c>
-      <c r="R39" s="1" t="n">
+      <c r="R39" s="2" t="n">
         <v>41306</v>
       </c>
     </row>
@@ -2770,7 +2782,7 @@
       <c r="Q40" t="n">
         <v>66</v>
       </c>
-      <c r="R40" s="1" t="n">
+      <c r="R40" s="2" t="n">
         <v>41334</v>
       </c>
     </row>
@@ -2828,7 +2840,7 @@
       <c r="Q41" t="n">
         <v>45</v>
       </c>
-      <c r="R41" s="1" t="n">
+      <c r="R41" s="2" t="n">
         <v>41365</v>
       </c>
     </row>
@@ -2886,7 +2898,7 @@
       <c r="Q42" t="n">
         <v>159</v>
       </c>
-      <c r="R42" s="1" t="n">
+      <c r="R42" s="2" t="n">
         <v>41395</v>
       </c>
     </row>
@@ -2944,7 +2956,7 @@
       <c r="Q43" t="n">
         <v>92</v>
       </c>
-      <c r="R43" s="1" t="n">
+      <c r="R43" s="2" t="n">
         <v>41426</v>
       </c>
     </row>
@@ -3002,7 +3014,7 @@
       <c r="Q44" t="n">
         <v>107</v>
       </c>
-      <c r="R44" s="1" t="n">
+      <c r="R44" s="2" t="n">
         <v>41456</v>
       </c>
     </row>
@@ -3060,7 +3072,7 @@
       <c r="Q45" t="n">
         <v>108</v>
       </c>
-      <c r="R45" s="1" t="n">
+      <c r="R45" s="2" t="n">
         <v>41487</v>
       </c>
     </row>
@@ -3118,7 +3130,7 @@
       <c r="Q46" t="n">
         <v>110</v>
       </c>
-      <c r="R46" s="1" t="n">
+      <c r="R46" s="2" t="n">
         <v>41518</v>
       </c>
     </row>
@@ -3176,7 +3188,7 @@
       <c r="Q47" t="n">
         <v>113</v>
       </c>
-      <c r="R47" s="1" t="n">
+      <c r="R47" s="2" t="n">
         <v>41548</v>
       </c>
     </row>
@@ -3234,7 +3246,7 @@
       <c r="Q48" t="n">
         <v>115</v>
       </c>
-      <c r="R48" s="1" t="n">
+      <c r="R48" s="2" t="n">
         <v>41579</v>
       </c>
     </row>
@@ -3292,7 +3304,7 @@
       <c r="Q49" t="n">
         <v>152</v>
       </c>
-      <c r="R49" s="1" t="n">
+      <c r="R49" s="2" t="n">
         <v>41609</v>
       </c>
     </row>
@@ -3350,7 +3362,7 @@
       <c r="Q50" t="n">
         <v>35</v>
       </c>
-      <c r="R50" s="1" t="n">
+      <c r="R50" s="2" t="n">
         <v>41640</v>
       </c>
     </row>
@@ -3408,7 +3420,7 @@
       <c r="Q51" t="n">
         <v>157</v>
       </c>
-      <c r="R51" s="1" t="n">
+      <c r="R51" s="2" t="n">
         <v>41671</v>
       </c>
     </row>
@@ -3466,7 +3478,7 @@
       <c r="Q52" t="n">
         <v>222</v>
       </c>
-      <c r="R52" s="1" t="n">
+      <c r="R52" s="2" t="n">
         <v>41699</v>
       </c>
     </row>
@@ -3524,7 +3536,7 @@
       <c r="Q53" t="n">
         <v>37</v>
       </c>
-      <c r="R53" s="1" t="n">
+      <c r="R53" s="2" t="n">
         <v>41730</v>
       </c>
     </row>
@@ -3582,7 +3594,7 @@
       <c r="Q54" t="n">
         <v>86</v>
       </c>
-      <c r="R54" s="1" t="n">
+      <c r="R54" s="2" t="n">
         <v>41760</v>
       </c>
     </row>
@@ -3640,7 +3652,7 @@
       <c r="Q55" t="n">
         <v>111</v>
       </c>
-      <c r="R55" s="1" t="n">
+      <c r="R55" s="2" t="n">
         <v>41791</v>
       </c>
     </row>
@@ -3698,7 +3710,7 @@
       <c r="Q56" t="n">
         <v>19</v>
       </c>
-      <c r="R56" s="1" t="n">
+      <c r="R56" s="2" t="n">
         <v>41821</v>
       </c>
     </row>
@@ -3756,7 +3768,7 @@
       <c r="Q57" t="n">
         <v>121</v>
       </c>
-      <c r="R57" s="1" t="n">
+      <c r="R57" s="2" t="n">
         <v>41852</v>
       </c>
     </row>
@@ -3814,7 +3826,7 @@
       <c r="Q58" t="n">
         <v>263</v>
       </c>
-      <c r="R58" s="1" t="n">
+      <c r="R58" s="2" t="n">
         <v>41883</v>
       </c>
     </row>
@@ -3872,7 +3884,7 @@
       <c r="Q59" t="n">
         <v>88</v>
       </c>
-      <c r="R59" s="1" t="n">
+      <c r="R59" s="2" t="n">
         <v>41913</v>
       </c>
     </row>
@@ -3930,7 +3942,7 @@
       <c r="Q60" t="n">
         <v>169</v>
       </c>
-      <c r="R60" s="1" t="n">
+      <c r="R60" s="2" t="n">
         <v>41944</v>
       </c>
     </row>
@@ -3988,7 +4000,7 @@
       <c r="Q61" t="n">
         <v>212</v>
       </c>
-      <c r="R61" s="1" t="n">
+      <c r="R61" s="2" t="n">
         <v>41974</v>
       </c>
     </row>
@@ -4046,7 +4058,7 @@
       <c r="Q62" t="n">
         <v>15</v>
       </c>
-      <c r="R62" s="1" t="n">
+      <c r="R62" s="2" t="n">
         <v>42005</v>
       </c>
     </row>
@@ -4104,7 +4116,7 @@
       <c r="Q63" t="n">
         <v>231</v>
       </c>
-      <c r="R63" s="1" t="n">
+      <c r="R63" s="2" t="n">
         <v>42036</v>
       </c>
     </row>
@@ -4162,7 +4174,7 @@
       <c r="Q64" t="n">
         <v>145</v>
       </c>
-      <c r="R64" s="1" t="n">
+      <c r="R64" s="2" t="n">
         <v>42064</v>
       </c>
     </row>
@@ -4220,7 +4232,7 @@
       <c r="Q65" t="n">
         <v>62</v>
       </c>
-      <c r="R65" s="1" t="n">
+      <c r="R65" s="2" t="n">
         <v>42095</v>
       </c>
     </row>
@@ -4278,7 +4290,7 @@
       <c r="Q66" t="n">
         <v>21</v>
       </c>
-      <c r="R66" s="1" t="n">
+      <c r="R66" s="2" t="n">
         <v>42125</v>
       </c>
     </row>
@@ -4336,7 +4348,7 @@
       <c r="Q67" t="n">
         <v>86</v>
       </c>
-      <c r="R67" s="1" t="n">
+      <c r="R67" s="2" t="n">
         <v>42156</v>
       </c>
     </row>
@@ -4394,7 +4406,7 @@
       <c r="Q68" t="n">
         <v>125</v>
       </c>
-      <c r="R68" s="1" t="n">
+      <c r="R68" s="2" t="n">
         <v>42186</v>
       </c>
     </row>
@@ -4452,7 +4464,7 @@
       <c r="Q69" t="n">
         <v>109</v>
       </c>
-      <c r="R69" s="1" t="n">
+      <c r="R69" s="2" t="n">
         <v>42217</v>
       </c>
     </row>
@@ -4510,7 +4522,7 @@
       <c r="Q70" t="n">
         <v>110</v>
       </c>
-      <c r="R70" s="1" t="n">
+      <c r="R70" s="2" t="n">
         <v>42248</v>
       </c>
     </row>
@@ -4568,7 +4580,7 @@
       <c r="Q71" t="n">
         <v>55</v>
       </c>
-      <c r="R71" s="1" t="n">
+      <c r="R71" s="2" t="n">
         <v>42278</v>
       </c>
     </row>
@@ -4626,7 +4638,7 @@
       <c r="Q72" t="n">
         <v>213</v>
       </c>
-      <c r="R72" s="1" t="n">
+      <c r="R72" s="2" t="n">
         <v>42309</v>
       </c>
     </row>
@@ -4684,7 +4696,7 @@
       <c r="Q73" t="n">
         <v>225</v>
       </c>
-      <c r="R73" s="1" t="n">
+      <c r="R73" s="2" t="n">
         <v>42339</v>
       </c>
     </row>
@@ -4742,7 +4754,7 @@
       <c r="Q74" t="n">
         <v>112</v>
       </c>
-      <c r="R74" s="1" t="n">
+      <c r="R74" s="2" t="n">
         <v>42370</v>
       </c>
     </row>
@@ -4800,7 +4812,7 @@
       <c r="Q75" t="n">
         <v>365</v>
       </c>
-      <c r="R75" s="1" t="n">
+      <c r="R75" s="2" t="n">
         <v>42401</v>
       </c>
     </row>
@@ -4858,7 +4870,7 @@
       <c r="Q76" t="n">
         <v>-19</v>
       </c>
-      <c r="R76" s="1" t="n">
+      <c r="R76" s="2" t="n">
         <v>42430</v>
       </c>
     </row>
@@ -4916,7 +4928,7 @@
       <c r="Q77" t="n">
         <v>292</v>
       </c>
-      <c r="R77" s="1" t="n">
+      <c r="R77" s="2" t="n">
         <v>42461</v>
       </c>
     </row>
@@ -4974,7 +4986,7 @@
       <c r="Q78" t="n">
         <v>-42</v>
       </c>
-      <c r="R78" s="1" t="n">
+      <c r="R78" s="2" t="n">
         <v>42491</v>
       </c>
     </row>
@@ -5032,7 +5044,7 @@
       <c r="Q79" t="n">
         <v>71</v>
       </c>
-      <c r="R79" s="1" t="n">
+      <c r="R79" s="2" t="n">
         <v>42522</v>
       </c>
     </row>
@@ -5090,7 +5102,7 @@
       <c r="Q80" t="n">
         <v>46</v>
       </c>
-      <c r="R80" s="1" t="n">
+      <c r="R80" s="2" t="n">
         <v>42552</v>
       </c>
     </row>
@@ -5148,7 +5160,7 @@
       <c r="Q81" t="n">
         <v>49</v>
       </c>
-      <c r="R81" s="1" t="n">
+      <c r="R81" s="2" t="n">
         <v>42583</v>
       </c>
     </row>
@@ -5206,7 +5218,7 @@
       <c r="Q82" t="n">
         <v>138</v>
       </c>
-      <c r="R82" s="1" t="n">
+      <c r="R82" s="2" t="n">
         <v>42614</v>
       </c>
     </row>
@@ -5264,7 +5276,7 @@
       <c r="Q83" t="n">
         <v>112</v>
       </c>
-      <c r="R83" s="1" t="n">
+      <c r="R83" s="2" t="n">
         <v>42644</v>
       </c>
     </row>
@@ -5322,7 +5334,7 @@
       <c r="Q84" t="n">
         <v>199</v>
       </c>
-      <c r="R84" s="1" t="n">
+      <c r="R84" s="2" t="n">
         <v>42675</v>
       </c>
     </row>
@@ -5380,7 +5392,7 @@
       <c r="Q85" t="n">
         <v>235</v>
       </c>
-      <c r="R85" s="1" t="n">
+      <c r="R85" s="2" t="n">
         <v>42705</v>
       </c>
     </row>
@@ -5438,7 +5450,7 @@
       <c r="Q86" t="n">
         <v>133</v>
       </c>
-      <c r="R86" s="1" t="n">
+      <c r="R86" s="2" t="n">
         <v>42736</v>
       </c>
     </row>
@@ -5496,7 +5508,7 @@
       <c r="Q87" t="n">
         <v>103</v>
       </c>
-      <c r="R87" s="1" t="n">
+      <c r="R87" s="2" t="n">
         <v>42767</v>
       </c>
     </row>
@@ -5554,7 +5566,7 @@
       <c r="Q88" t="n">
         <v>223</v>
       </c>
-      <c r="R88" s="1" t="n">
+      <c r="R88" s="2" t="n">
         <v>42795</v>
       </c>
     </row>
@@ -5612,7 +5624,7 @@
       <c r="Q89" t="n">
         <v>31</v>
       </c>
-      <c r="R89" s="1" t="n">
+      <c r="R89" s="2" t="n">
         <v>42826</v>
       </c>
     </row>
@@ -5670,7 +5682,7 @@
       <c r="Q90" t="n">
         <v>245</v>
       </c>
-      <c r="R90" s="1" t="n">
+      <c r="R90" s="2" t="n">
         <v>42856</v>
       </c>
     </row>
@@ -5728,7 +5740,7 @@
       <c r="Q91" t="n">
         <v>273</v>
       </c>
-      <c r="R91" s="1" t="n">
+      <c r="R91" s="2" t="n">
         <v>42887</v>
       </c>
     </row>
@@ -5786,7 +5798,7 @@
       <c r="Q92" t="n">
         <v>305</v>
       </c>
-      <c r="R92" s="1" t="n">
+      <c r="R92" s="2" t="n">
         <v>42917</v>
       </c>
     </row>
@@ -5844,7 +5856,7 @@
       <c r="Q93" t="n">
         <v>213</v>
       </c>
-      <c r="R93" s="1" t="n">
+      <c r="R93" s="2" t="n">
         <v>42948</v>
       </c>
     </row>
@@ -5902,7 +5914,7 @@
       <c r="Q94" t="n">
         <v>209</v>
       </c>
-      <c r="R94" s="1" t="n">
+      <c r="R94" s="2" t="n">
         <v>42979</v>
       </c>
     </row>
@@ -5960,7 +5972,7 @@
       <c r="Q95" t="n">
         <v>262</v>
       </c>
-      <c r="R95" s="1" t="n">
+      <c r="R95" s="2" t="n">
         <v>43009</v>
       </c>
     </row>
@@ -6018,7 +6030,7 @@
       <c r="Q96" t="n">
         <v>277</v>
       </c>
-      <c r="R96" s="1" t="n">
+      <c r="R96" s="2" t="n">
         <v>43040</v>
       </c>
     </row>
@@ -6076,7 +6088,7 @@
       <c r="Q97" t="n">
         <v>259</v>
       </c>
-      <c r="R97" s="1" t="n">
+      <c r="R97" s="2" t="n">
         <v>43070</v>
       </c>
     </row>
@@ -6134,7 +6146,7 @@
       <c r="Q98" t="n">
         <v>201</v>
       </c>
-      <c r="R98" s="1" t="n">
+      <c r="R98" s="2" t="n">
         <v>43101</v>
       </c>
     </row>
@@ -6192,7 +6204,7 @@
       <c r="Q99" t="n">
         <v>-9</v>
       </c>
-      <c r="R99" s="1" t="n">
+      <c r="R99" s="2" t="n">
         <v>43132</v>
       </c>
     </row>
@@ -6250,7 +6262,7 @@
       <c r="Q100" t="n">
         <v>-3</v>
       </c>
-      <c r="R100" s="1" t="n">
+      <c r="R100" s="2" t="n">
         <v>43160</v>
       </c>
     </row>
@@ -6308,7 +6320,7 @@
       <c r="Q101" t="n">
         <v>65</v>
       </c>
-      <c r="R101" s="1" t="n">
+      <c r="R101" s="2" t="n">
         <v>43191</v>
       </c>
     </row>
@@ -6366,7 +6378,7 @@
       <c r="Q102" t="n">
         <v>-145</v>
       </c>
-      <c r="R102" s="1" t="n">
+      <c r="R102" s="2" t="n">
         <v>43221</v>
       </c>
     </row>
@@ -6424,7 +6436,7 @@
       <c r="Q103" t="n">
         <v>35</v>
       </c>
-      <c r="R103" s="1" t="n">
+      <c r="R103" s="2" t="n">
         <v>43252</v>
       </c>
     </row>
@@ -6482,7 +6494,7 @@
       <c r="Q104" t="n">
         <v>62</v>
       </c>
-      <c r="R104" s="1" t="n">
+      <c r="R104" s="2" t="n">
         <v>43282</v>
       </c>
     </row>
@@ -6540,7 +6552,7 @@
       <c r="Q105" t="n">
         <v>28</v>
       </c>
-      <c r="R105" s="1" t="n">
+      <c r="R105" s="2" t="n">
         <v>43313</v>
       </c>
     </row>
@@ -6598,7 +6610,7 @@
       <c r="Q106" t="n">
         <v>104</v>
       </c>
-      <c r="R106" s="1" t="n">
+      <c r="R106" s="2" t="n">
         <v>43344</v>
       </c>
     </row>
@@ -6656,7 +6668,7 @@
       <c r="Q107" t="n">
         <v>111</v>
       </c>
-      <c r="R107" s="1" t="n">
+      <c r="R107" s="2" t="n">
         <v>43374</v>
       </c>
     </row>
@@ -6714,7 +6726,7 @@
       <c r="Q108" t="n">
         <v>212</v>
       </c>
-      <c r="R108" s="1" t="n">
+      <c r="R108" s="2" t="n">
         <v>43405</v>
       </c>
     </row>
@@ -6772,7 +6784,7 @@
       <c r="Q109" t="n">
         <v>120</v>
       </c>
-      <c r="R109" s="1" t="n">
+      <c r="R109" s="2" t="n">
         <v>43435</v>
       </c>
     </row>
@@ -6830,7 +6842,7 @@
       <c r="Q110" t="n">
         <v>92</v>
       </c>
-      <c r="R110" s="1" t="n">
+      <c r="R110" s="2" t="n">
         <v>43466</v>
       </c>
     </row>
@@ -6888,7 +6900,7 @@
       <c r="Q111" t="n">
         <v>-67</v>
       </c>
-      <c r="R111" s="1" t="n">
+      <c r="R111" s="2" t="n">
         <v>43497</v>
       </c>
     </row>
@@ -6946,7 +6958,7 @@
       <c r="Q112" t="n">
         <v>125</v>
       </c>
-      <c r="R112" s="1" t="n">
+      <c r="R112" s="2" t="n">
         <v>43525</v>
       </c>
     </row>
@@ -7004,7 +7016,7 @@
       <c r="Q113" t="n">
         <v>-16</v>
       </c>
-      <c r="R113" s="1" t="n">
+      <c r="R113" s="2" t="n">
         <v>43556</v>
       </c>
     </row>
@@ -7062,7 +7074,7 @@
       <c r="Q114" t="n">
         <v>-71</v>
       </c>
-      <c r="R114" s="1" t="n">
+      <c r="R114" s="2" t="n">
         <v>43586</v>
       </c>
     </row>
@@ -7120,7 +7132,7 @@
       <c r="Q115" t="n">
         <v>19</v>
       </c>
-      <c r="R115" s="1" t="n">
+      <c r="R115" s="2" t="n">
         <v>43617</v>
       </c>
     </row>
@@ -7178,7 +7190,7 @@
       <c r="Q116" t="n">
         <v>141</v>
       </c>
-      <c r="R116" s="1" t="n">
+      <c r="R116" s="2" t="n">
         <v>43647</v>
       </c>
     </row>
@@ -7236,7 +7248,7 @@
       <c r="Q117" t="n">
         <v>99</v>
       </c>
-      <c r="R117" s="1" t="n">
+      <c r="R117" s="2" t="n">
         <v>43678</v>
       </c>
     </row>
@@ -7294,7 +7306,7 @@
       <c r="Q118" t="n">
         <v>100</v>
       </c>
-      <c r="R118" s="1" t="n">
+      <c r="R118" s="2" t="n">
         <v>43709</v>
       </c>
     </row>
@@ -7352,7 +7364,7 @@
       <c r="Q119" t="n">
         <v>109</v>
       </c>
-      <c r="R119" s="1" t="n">
+      <c r="R119" s="2" t="n">
         <v>43739</v>
       </c>
     </row>
@@ -7410,7 +7422,7 @@
       <c r="Q120" t="n">
         <v>92</v>
       </c>
-      <c r="R120" s="1" t="n">
+      <c r="R120" s="2" t="n">
         <v>43770</v>
       </c>
     </row>
@@ -7468,7 +7480,7 @@
       <c r="Q121" t="n">
         <v>248</v>
       </c>
-      <c r="R121" s="1" t="n">
+      <c r="R121" s="2" t="n">
         <v>43800</v>
       </c>
     </row>
@@ -7526,7 +7538,7 @@
       <c r="Q122" t="n">
         <v>94</v>
       </c>
-      <c r="R122" s="1" t="n">
+      <c r="R122" s="2" t="n">
         <v>43831</v>
       </c>
     </row>
@@ -7584,7 +7596,7 @@
       <c r="Q123" t="n">
         <v>-130</v>
       </c>
-      <c r="R123" s="1" t="n">
+      <c r="R123" s="2" t="n">
         <v>43862</v>
       </c>
     </row>
@@ -7642,7 +7654,7 @@
       <c r="Q124" t="n">
         <v>-266</v>
       </c>
-      <c r="R124" s="1" t="n">
+      <c r="R124" s="2" t="n">
         <v>43891</v>
       </c>
     </row>
@@ -7700,7 +7712,7 @@
       <c r="Q125" t="n">
         <v>40</v>
       </c>
-      <c r="R125" s="1" t="n">
+      <c r="R125" s="2" t="n">
         <v>43922</v>
       </c>
     </row>
@@ -7758,7 +7770,7 @@
       <c r="Q126" t="n">
         <v>-35</v>
       </c>
-      <c r="R126" s="1" t="n">
+      <c r="R126" s="2" t="n">
         <v>43952</v>
       </c>
     </row>
@@ -7816,7 +7828,7 @@
       <c r="Q127" t="n">
         <v>-60</v>
       </c>
-      <c r="R127" s="1" t="n">
+      <c r="R127" s="2" t="n">
         <v>43983</v>
       </c>
     </row>
@@ -7874,7 +7886,7 @@
       <c r="Q128" t="n">
         <v>85</v>
       </c>
-      <c r="R128" s="1" t="n">
+      <c r="R128" s="2" t="n">
         <v>44013</v>
       </c>
     </row>
@@ -7932,7 +7944,7 @@
       <c r="Q129" t="n">
         <v>150</v>
       </c>
-      <c r="R129" s="1" t="n">
+      <c r="R129" s="2" t="n">
         <v>44044</v>
       </c>
     </row>
@@ -7990,7 +8002,7 @@
       <c r="Q130" t="n">
         <v>206</v>
       </c>
-      <c r="R130" s="1" t="n">
+      <c r="R130" s="2" t="n">
         <v>44075</v>
       </c>
     </row>
@@ -8048,7 +8060,7 @@
       <c r="Q131" t="n">
         <v>-23</v>
       </c>
-      <c r="R131" s="1" t="n">
+      <c r="R131" s="2" t="n">
         <v>44105</v>
       </c>
     </row>
@@ -8106,7 +8118,7 @@
       <c r="Q132" t="n">
         <v>174</v>
       </c>
-      <c r="R132" s="1" t="n">
+      <c r="R132" s="2" t="n">
         <v>44136</v>
       </c>
     </row>
@@ -8164,7 +8176,7 @@
       <c r="Q133" t="n">
         <v>-34</v>
       </c>
-      <c r="R133" s="1" t="n">
+      <c r="R133" s="2" t="n">
         <v>44166</v>
       </c>
     </row>
@@ -8222,7 +8234,7 @@
       <c r="Q134" t="n">
         <v>44</v>
       </c>
-      <c r="R134" s="1" t="n">
+      <c r="R134" s="2" t="n">
         <v>44197</v>
       </c>
     </row>
@@ -8280,7 +8292,7 @@
       <c r="Q135" t="n">
         <v>146</v>
       </c>
-      <c r="R135" s="1" t="n">
+      <c r="R135" s="2" t="n">
         <v>44228</v>
       </c>
     </row>
@@ -8338,7 +8350,7 @@
       <c r="Q136" t="n">
         <v>44</v>
       </c>
-      <c r="R136" s="1" t="n">
+      <c r="R136" s="2" t="n">
         <v>44256</v>
       </c>
     </row>
@@ -8396,7 +8408,7 @@
       <c r="Q137" t="n">
         <v>282</v>
       </c>
-      <c r="R137" s="1" t="n">
+      <c r="R137" s="2" t="n">
         <v>44287</v>
       </c>
     </row>
@@ -8454,7 +8466,7 @@
       <c r="Q138" t="n">
         <v>152</v>
       </c>
-      <c r="R138" s="1" t="n">
+      <c r="R138" s="2" t="n">
         <v>44317</v>
       </c>
     </row>
@@ -8512,7 +8524,7 @@
       <c r="Q139" t="n">
         <v>-23</v>
       </c>
-      <c r="R139" s="1" t="n">
+      <c r="R139" s="2" t="n">
         <v>44348</v>
       </c>
     </row>
@@ -8570,7 +8582,7 @@
       <c r="Q140" t="n">
         <v>53</v>
       </c>
-      <c r="R140" s="1" t="n">
+      <c r="R140" s="2" t="n">
         <v>44378</v>
       </c>
     </row>
@@ -8628,7 +8640,7 @@
       <c r="Q141" t="n">
         <v>81</v>
       </c>
-      <c r="R141" s="1" t="n">
+      <c r="R141" s="2" t="n">
         <v>44409</v>
       </c>
     </row>
@@ -8686,7 +8698,7 @@
       <c r="Q142" t="n">
         <v>50</v>
       </c>
-      <c r="R142" s="1" t="n">
+      <c r="R142" s="2" t="n">
         <v>44440</v>
       </c>
     </row>
@@ -8744,7 +8756,7 @@
       <c r="Q143" t="n">
         <v>115</v>
       </c>
-      <c r="R143" s="1" t="n">
+      <c r="R143" s="2" t="n">
         <v>44470</v>
       </c>
     </row>
@@ -8802,7 +8814,7 @@
       <c r="Q144" t="n">
         <v>-106</v>
       </c>
-      <c r="R144" s="1" t="n">
+      <c r="R144" s="2" t="n">
         <v>44501</v>
       </c>
     </row>
@@ -8860,7 +8872,7 @@
       <c r="Q145" t="n">
         <v>112</v>
       </c>
-      <c r="R145" s="1" t="n">
+      <c r="R145" s="2" t="n">
         <v>44531</v>
       </c>
     </row>
@@ -8918,7 +8930,7 @@
       <c r="Q146" t="n">
         <v>-158</v>
       </c>
-      <c r="R146" s="1" t="n">
+      <c r="R146" s="2" t="n">
         <v>44562</v>
       </c>
     </row>
@@ -8976,7 +8988,7 @@
       <c r="Q147" t="n">
         <v>-43</v>
       </c>
-      <c r="R147" s="1" t="n">
+      <c r="R147" s="2" t="n">
         <v>44593</v>
       </c>
     </row>
@@ -9034,7 +9046,7 @@
       <c r="Q148" t="n">
         <v>-190</v>
       </c>
-      <c r="R148" s="1" t="n">
+      <c r="R148" s="2" t="n">
         <v>44621</v>
       </c>
     </row>
@@ -9092,7 +9104,7 @@
       <c r="Q149" t="n">
         <v>-107</v>
       </c>
-      <c r="R149" s="1" t="n">
+      <c r="R149" s="2" t="n">
         <v>44652</v>
       </c>
     </row>
@@ -9150,7 +9162,7 @@
       <c r="Q150" t="n">
         <v>-92</v>
       </c>
-      <c r="R150" s="1" t="n">
+      <c r="R150" s="2" t="n">
         <v>44682</v>
       </c>
     </row>
@@ -9208,7 +9220,7 @@
       <c r="Q151" t="n">
         <v>-123</v>
       </c>
-      <c r="R151" s="1" t="n">
+      <c r="R151" s="2" t="n">
         <v>44713</v>
       </c>
     </row>
@@ -9266,7 +9278,7 @@
       <c r="Q152" t="n">
         <v>60</v>
       </c>
-      <c r="R152" s="1" t="n">
+      <c r="R152" s="2" t="n">
         <v>44743</v>
       </c>
     </row>
@@ -9324,7 +9336,7 @@
       <c r="Q153" t="n">
         <v>53</v>
       </c>
-      <c r="R153" s="1" t="n">
+      <c r="R153" s="2" t="n">
         <v>44774</v>
       </c>
     </row>
@@ -9382,7 +9394,7 @@
       <c r="Q154" t="n">
         <v>1</v>
       </c>
-      <c r="R154" s="1" t="n">
+      <c r="R154" s="2" t="n">
         <v>44805</v>
       </c>
     </row>
@@ -9440,7 +9452,7 @@
       <c r="Q155" t="n">
         <v>34</v>
       </c>
-      <c r="R155" s="1" t="n">
+      <c r="R155" s="2" t="n">
         <v>44835</v>
       </c>
     </row>
@@ -9498,7 +9510,7 @@
       <c r="Q156" t="n">
         <v>-15</v>
       </c>
-      <c r="R156" s="1" t="n">
+      <c r="R156" s="2" t="n">
         <v>44866</v>
       </c>
     </row>
@@ -9556,7 +9568,7 @@
       <c r="Q157" t="n">
         <v>211</v>
       </c>
-      <c r="R157" s="1" t="n">
+      <c r="R157" s="2" t="n">
         <v>44896</v>
       </c>
     </row>
@@ -9614,7 +9626,7 @@
       <c r="Q158" t="n">
         <v>-228</v>
       </c>
-      <c r="R158" s="1" t="n">
+      <c r="R158" s="2" t="n">
         <v>44927</v>
       </c>
     </row>
@@ -9672,7 +9684,7 @@
       <c r="Q159" t="n">
         <v>157</v>
       </c>
-      <c r="R159" s="1" t="n">
+      <c r="R159" s="2" t="n">
         <v>44958</v>
       </c>
     </row>
@@ -9730,7 +9742,7 @@
       <c r="Q160" t="n">
         <v>77</v>
       </c>
-      <c r="R160" s="1" t="n">
+      <c r="R160" s="2" t="n">
         <v>44986</v>
       </c>
     </row>
@@ -9788,7 +9800,7 @@
       <c r="Q161" t="n">
         <v>60</v>
       </c>
-      <c r="R161" s="1" t="n">
+      <c r="R161" s="2" t="n">
         <v>45017</v>
       </c>
     </row>
@@ -9846,7 +9858,7 @@
       <c r="Q162" t="n">
         <v>21</v>
       </c>
-      <c r="R162" s="1" t="n">
+      <c r="R162" s="2" t="n">
         <v>45047</v>
       </c>
     </row>
@@ -9904,7 +9916,7 @@
       <c r="Q163" t="n">
         <v>190</v>
       </c>
-      <c r="R163" s="1" t="n">
+      <c r="R163" s="2" t="n">
         <v>45078</v>
       </c>
     </row>
@@ -9962,7 +9974,7 @@
       <c r="Q164" t="n">
         <v>-81</v>
       </c>
-      <c r="R164" s="1" t="n">
+      <c r="R164" s="2" t="n">
         <v>45108</v>
       </c>
     </row>
@@ -10020,7 +10032,7 @@
       <c r="Q165" t="n">
         <v>89</v>
       </c>
-      <c r="R165" s="1" t="n">
+      <c r="R165" s="2" t="n">
         <v>45139</v>
       </c>
     </row>
@@ -10078,7 +10090,7 @@
       <c r="Q166" t="n">
         <v>197</v>
       </c>
-      <c r="R166" s="1" t="n">
+      <c r="R166" s="2" t="n">
         <v>45170</v>
       </c>
     </row>
@@ -10136,7 +10148,7 @@
       <c r="Q167" t="n">
         <v>-53</v>
       </c>
-      <c r="R167" s="1" t="n">
+      <c r="R167" s="2" t="n">
         <v>45200</v>
       </c>
     </row>
@@ -10194,7 +10206,7 @@
       <c r="Q168" t="n">
         <v>-21</v>
       </c>
-      <c r="R168" s="1" t="n">
+      <c r="R168" s="2" t="n">
         <v>45231</v>
       </c>
     </row>
@@ -10252,7 +10264,7 @@
       <c r="Q169" t="n">
         <v>149</v>
       </c>
-      <c r="R169" s="1" t="n">
+      <c r="R169" s="2" t="n">
         <v>45261</v>
       </c>
     </row>
@@ -10310,7 +10322,7 @@
       <c r="Q170" t="n">
         <v>-157</v>
       </c>
-      <c r="R170" s="1" t="n">
+      <c r="R170" s="2" t="n">
         <v>45292</v>
       </c>
     </row>
@@ -10368,7 +10380,7 @@
       <c r="Q171" t="n">
         <v>-123</v>
       </c>
-      <c r="R171" s="1" t="n">
+      <c r="R171" s="2" t="n">
         <v>45323</v>
       </c>
     </row>
@@ -10426,7 +10438,7 @@
       <c r="Q172" t="n">
         <v>-206</v>
       </c>
-      <c r="R172" s="1" t="n">
+      <c r="R172" s="2" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -10484,7 +10496,7 @@
       <c r="Q173" t="n">
         <v>520</v>
       </c>
-      <c r="R173" s="1" t="n">
+      <c r="R173" s="2" t="n">
         <v>45383</v>
       </c>
     </row>
@@ -10542,7 +10554,7 @@
       <c r="Q174" t="n">
         <v>-152</v>
       </c>
-      <c r="R174" s="1" t="n">
+      <c r="R174" s="2" t="n">
         <v>45413</v>
       </c>
     </row>
@@ -10600,7 +10612,7 @@
       <c r="Q175" t="n">
         <v>3</v>
       </c>
-      <c r="R175" s="1" t="n">
+      <c r="R175" s="2" t="n">
         <v>45444</v>
       </c>
     </row>
@@ -10658,7 +10670,7 @@
       <c r="Q176" t="n">
         <v>92</v>
       </c>
-      <c r="R176" s="1" t="n">
+      <c r="R176" s="2" t="n">
         <v>45474</v>
       </c>
     </row>
@@ -10716,7 +10728,7 @@
       <c r="Q177" t="n">
         <v>-5</v>
       </c>
-      <c r="R177" s="1" t="n">
+      <c r="R177" s="2" t="n">
         <v>45505</v>
       </c>
     </row>
@@ -10774,7 +10786,7 @@
       <c r="Q178" t="n">
         <v>-19</v>
       </c>
-      <c r="R178" s="1" t="n">
+      <c r="R178" s="2" t="n">
         <v>45536</v>
       </c>
     </row>
@@ -10832,7 +10844,7 @@
       <c r="Q179" t="n">
         <v>-15</v>
       </c>
-      <c r="R179" s="1" t="n">
+      <c r="R179" s="2" t="n">
         <v>45566</v>
       </c>
     </row>
@@ -10890,7 +10902,7 @@
       <c r="Q180" t="n">
         <v>21</v>
       </c>
-      <c r="R180" s="1" t="n">
+      <c r="R180" s="2" t="n">
         <v>45597</v>
       </c>
     </row>
@@ -10948,7 +10960,7 @@
       <c r="Q181" t="n">
         <v>113</v>
       </c>
-      <c r="R181" s="1" t="n">
+      <c r="R181" s="2" t="n">
         <v>45627</v>
       </c>
     </row>
@@ -11006,7 +11018,7 @@
       <c r="Q182" t="n">
         <v>-154</v>
       </c>
-      <c r="R182" s="1" t="n">
+      <c r="R182" s="2" t="n">
         <v>45658</v>
       </c>
     </row>
@@ -11064,7 +11076,7 @@
       <c r="Q183" t="n">
         <v>8</v>
       </c>
-      <c r="R183" s="1" t="n">
+      <c r="R183" s="2" t="n">
         <v>45689</v>
       </c>
     </row>
@@ -11122,7 +11134,7 @@
       <c r="Q184" t="n">
         <v>-9</v>
       </c>
-      <c r="R184" s="1" t="n">
+      <c r="R184" s="2" t="n">
         <v>45717</v>
       </c>
     </row>
@@ -11180,7 +11192,7 @@
       <c r="Q185" t="n">
         <v>-104</v>
       </c>
-      <c r="R185" s="1" t="n">
+      <c r="R185" s="2" t="n">
         <v>45748</v>
       </c>
     </row>
@@ -11238,7 +11250,7 @@
       <c r="Q186" t="n">
         <v>-25</v>
       </c>
-      <c r="R186" s="1" t="n">
+      <c r="R186" s="2" t="n">
         <v>45778</v>
       </c>
     </row>
@@ -11296,7 +11308,7 @@
       <c r="Q187" t="n">
         <v>-82</v>
       </c>
-      <c r="R187" s="1" t="n">
+      <c r="R187" s="2" t="n">
         <v>45809</v>
       </c>
     </row>
@@ -11354,7 +11366,7 @@
       <c r="Q188" t="n">
         <v>-153</v>
       </c>
-      <c r="R188" s="1" t="n">
+      <c r="R188" s="2" t="n">
         <v>45839</v>
       </c>
     </row>
@@ -11412,7 +11424,7 @@
       <c r="Q189" t="n">
         <v>-21</v>
       </c>
-      <c r="R189" s="1" t="n">
+      <c r="R189" s="2" t="n">
         <v>45870</v>
       </c>
     </row>
@@ -11470,7 +11482,7 @@
       <c r="Q190" t="n">
         <v>89</v>
       </c>
-      <c r="R190" s="1" t="n">
+      <c r="R190" s="2" t="n">
         <v>45901</v>
       </c>
     </row>
@@ -11528,7 +11540,7 @@
       <c r="Q191" t="n">
         <v>-7</v>
       </c>
-      <c r="R191" s="1" t="n">
+      <c r="R191" s="2" t="n">
         <v>45931</v>
       </c>
     </row>
@@ -11586,7 +11598,7 @@
       <c r="Q192" t="n">
         <v>13</v>
       </c>
-      <c r="R192" s="1" t="n">
+      <c r="R192" s="2" t="n">
         <v>45962</v>
       </c>
     </row>
@@ -11644,7 +11656,7 @@
       <c r="Q193" t="n">
         <v>-99</v>
       </c>
-      <c r="R193" s="1" t="n">
+      <c r="R193" s="2" t="n">
         <v>45992</v>
       </c>
     </row>
@@ -11702,7 +11714,7 @@
       <c r="Q194" t="n">
         <v>-314</v>
       </c>
-      <c r="R194" s="1" t="n">
+      <c r="R194" s="2" t="n">
         <v>46023</v>
       </c>
     </row>
@@ -11760,7 +11772,7 @@
       <c r="Q195" t="n">
         <v>-193</v>
       </c>
-      <c r="R195" s="1" t="n">
+      <c r="R195" s="2" t="n">
         <v>46054</v>
       </c>
     </row>
@@ -11818,7 +11830,7 @@
       <c r="Q196" t="n">
         <v>-245</v>
       </c>
-      <c r="R196" s="1" t="n">
+      <c r="R196" s="2" t="n">
         <v>46082</v>
       </c>
     </row>
@@ -11876,7 +11888,7 @@
       <c r="Q197" t="n">
         <v>-143</v>
       </c>
-      <c r="R197" s="1" t="n">
+      <c r="R197" s="2" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -11934,7 +11946,7 @@
       <c r="Q198" t="n">
         <v>-164</v>
       </c>
-      <c r="R198" s="1" t="n">
+      <c r="R198" s="2" t="n">
         <v>46143</v>
       </c>
     </row>
@@ -11992,7 +12004,7 @@
       <c r="Q199" t="n">
         <v>-729</v>
       </c>
-      <c r="R199" s="1" t="n">
+      <c r="R199" s="2" t="n">
         <v>46174</v>
       </c>
     </row>
@@ -12050,7 +12062,7 @@
       <c r="Q200" t="n">
         <v>-56</v>
       </c>
-      <c r="R200" s="1" t="n">
+      <c r="R200" s="2" t="n">
         <v>46204</v>
       </c>
     </row>

--- a/cari acik/odemeler_dengesi_raw.xlsx
+++ b/cari acik/odemeler_dengesi_raw.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R200"/>
+  <dimension ref="A1:R201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10263,7 +10263,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-2543</v>
+        <v>-2538</v>
       </c>
       <c r="C170" t="n">
         <v>-4332</v>
@@ -10284,19 +10284,19 @@
         <v>1024</v>
       </c>
       <c r="I170" t="n">
-        <v>3135</v>
+        <v>3140</v>
       </c>
       <c r="J170" t="n">
-        <v>7180</v>
+        <v>7184</v>
       </c>
       <c r="K170" t="n">
-        <v>4045</v>
+        <v>4044</v>
       </c>
       <c r="L170" t="n">
-        <v>2887</v>
+        <v>2891</v>
       </c>
       <c r="M170" t="n">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="N170" t="n">
         <v>2955</v>
@@ -10321,7 +10321,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-3202</v>
+        <v>-3197</v>
       </c>
       <c r="C171" t="n">
         <v>-4682</v>
@@ -10342,19 +10342,19 @@
         <v>1108</v>
       </c>
       <c r="I171" t="n">
-        <v>2330</v>
+        <v>2335</v>
       </c>
       <c r="J171" t="n">
-        <v>6538</v>
+        <v>6542</v>
       </c>
       <c r="K171" t="n">
-        <v>4208</v>
+        <v>4207</v>
       </c>
       <c r="L171" t="n">
-        <v>2817</v>
+        <v>2821</v>
       </c>
       <c r="M171" t="n">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="N171" t="n">
         <v>2449</v>
@@ -10379,7 +10379,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-4079</v>
+        <v>-4074</v>
       </c>
       <c r="C172" t="n">
         <v>-5011</v>
@@ -10400,19 +10400,19 @@
         <v>1608</v>
       </c>
       <c r="I172" t="n">
-        <v>2749</v>
+        <v>2754</v>
       </c>
       <c r="J172" t="n">
-        <v>7773</v>
+        <v>7777</v>
       </c>
       <c r="K172" t="n">
-        <v>5024</v>
+        <v>5023</v>
       </c>
       <c r="L172" t="n">
-        <v>3199</v>
+        <v>3203</v>
       </c>
       <c r="M172" t="n">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="N172" t="n">
         <v>2736</v>
@@ -10495,7 +10495,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>-855</v>
+        <v>-853</v>
       </c>
       <c r="C174" t="n">
         <v>-4153</v>
@@ -10516,19 +10516,19 @@
         <v>1430</v>
       </c>
       <c r="I174" t="n">
-        <v>5272</v>
+        <v>5274</v>
       </c>
       <c r="J174" t="n">
-        <v>9825</v>
+        <v>9828</v>
       </c>
       <c r="K174" t="n">
-        <v>4553</v>
+        <v>4554</v>
       </c>
       <c r="L174" t="n">
-        <v>3465</v>
+        <v>3468</v>
       </c>
       <c r="M174" t="n">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="N174" t="n">
         <v>4876</v>
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C175" t="n">
         <v>-4109</v>
@@ -10574,16 +10574,16 @@
         <v>1063</v>
       </c>
       <c r="I175" t="n">
-        <v>5963</v>
+        <v>5964</v>
       </c>
       <c r="J175" t="n">
-        <v>10697</v>
+        <v>10698</v>
       </c>
       <c r="K175" t="n">
         <v>4734</v>
       </c>
       <c r="L175" t="n">
-        <v>3519</v>
+        <v>3520</v>
       </c>
       <c r="M175" t="n">
         <v>1656</v>
@@ -10611,7 +10611,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="C176" t="n">
         <v>-5063</v>
@@ -10632,19 +10632,19 @@
         <v>998</v>
       </c>
       <c r="I176" t="n">
-        <v>7666</v>
+        <v>7664</v>
       </c>
       <c r="J176" t="n">
-        <v>12433</v>
+        <v>12432</v>
       </c>
       <c r="K176" t="n">
-        <v>4767</v>
+        <v>4768</v>
       </c>
       <c r="L176" t="n">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="M176" t="n">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="N176" t="n">
         <v>6883</v>
@@ -10669,7 +10669,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>4415</v>
+        <v>4412</v>
       </c>
       <c r="C177" t="n">
         <v>-2886</v>
@@ -10690,16 +10690,16 @@
         <v>1293</v>
       </c>
       <c r="I177" t="n">
-        <v>9207</v>
+        <v>9204</v>
       </c>
       <c r="J177" t="n">
-        <v>13667</v>
+        <v>13664</v>
       </c>
       <c r="K177" t="n">
         <v>4460</v>
       </c>
       <c r="L177" t="n">
-        <v>4086</v>
+        <v>4083</v>
       </c>
       <c r="M177" t="n">
         <v>1778</v>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="C178" t="n">
         <v>-3108</v>
@@ -10748,16 +10748,16 @@
         <v>1205</v>
       </c>
       <c r="I178" t="n">
-        <v>7170</v>
+        <v>7167</v>
       </c>
       <c r="J178" t="n">
-        <v>11965</v>
+        <v>11962</v>
       </c>
       <c r="K178" t="n">
         <v>4795</v>
       </c>
       <c r="L178" t="n">
-        <v>3799</v>
+        <v>3796</v>
       </c>
       <c r="M178" t="n">
         <v>1731</v>
@@ -10785,7 +10785,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1714</v>
+        <v>1697</v>
       </c>
       <c r="C179" t="n">
         <v>-3504</v>
@@ -10806,16 +10806,16 @@
         <v>1739</v>
       </c>
       <c r="I179" t="n">
-        <v>6871</v>
+        <v>6854</v>
       </c>
       <c r="J179" t="n">
-        <v>11493</v>
+        <v>11476</v>
       </c>
       <c r="K179" t="n">
         <v>4622</v>
       </c>
       <c r="L179" t="n">
-        <v>3724</v>
+        <v>3707</v>
       </c>
       <c r="M179" t="n">
         <v>1853</v>
@@ -10843,7 +10843,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>-3448</v>
+        <v>-3446</v>
       </c>
       <c r="C180" t="n">
         <v>-5242</v>
@@ -10864,19 +10864,19 @@
         <v>2080</v>
       </c>
       <c r="I180" t="n">
-        <v>3837</v>
+        <v>3839</v>
       </c>
       <c r="J180" t="n">
-        <v>8545</v>
+        <v>8548</v>
       </c>
       <c r="K180" t="n">
-        <v>4708</v>
+        <v>4709</v>
       </c>
       <c r="L180" t="n">
-        <v>3114</v>
+        <v>3117</v>
       </c>
       <c r="M180" t="n">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="N180" t="n">
         <v>3686</v>
@@ -10901,7 +10901,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-5010</v>
+        <v>-5003</v>
       </c>
       <c r="C181" t="n">
         <v>-6231</v>
@@ -10922,19 +10922,19 @@
         <v>2001</v>
       </c>
       <c r="I181" t="n">
-        <v>2946</v>
+        <v>2953</v>
       </c>
       <c r="J181" t="n">
-        <v>9109</v>
+        <v>9115</v>
       </c>
       <c r="K181" t="n">
-        <v>6163</v>
+        <v>6162</v>
       </c>
       <c r="L181" t="n">
-        <v>3406</v>
+        <v>3412</v>
       </c>
       <c r="M181" t="n">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="N181" t="n">
         <v>2863</v>
@@ -10959,16 +10959,16 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>-3987</v>
+        <v>-3989</v>
       </c>
       <c r="C182" t="n">
-        <v>-5499</v>
+        <v>-5500</v>
       </c>
       <c r="D182" t="n">
         <v>21075</v>
       </c>
       <c r="E182" t="n">
-        <v>26574</v>
+        <v>26575</v>
       </c>
       <c r="F182" t="n">
         <v>-1092</v>
@@ -10980,19 +10980,19 @@
         <v>1472</v>
       </c>
       <c r="I182" t="n">
-        <v>3052</v>
+        <v>3049</v>
       </c>
       <c r="J182" t="n">
         <v>7794</v>
       </c>
       <c r="K182" t="n">
-        <v>4742</v>
+        <v>4745</v>
       </c>
       <c r="L182" t="n">
         <v>2952</v>
       </c>
       <c r="M182" t="n">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="N182" t="n">
         <v>3251</v>
@@ -11001,7 +11001,7 @@
         <v>852</v>
       </c>
       <c r="P182" t="n">
-        <v>-1386</v>
+        <v>-1384</v>
       </c>
       <c r="Q182" t="n">
         <v>-154</v>
@@ -11017,16 +11017,16 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>-5290</v>
+        <v>-5284</v>
       </c>
       <c r="C183" t="n">
-        <v>-5435</v>
+        <v>-5433</v>
       </c>
       <c r="D183" t="n">
         <v>21141</v>
       </c>
       <c r="E183" t="n">
-        <v>26576</v>
+        <v>26574</v>
       </c>
       <c r="F183" t="n">
         <v>-1850</v>
@@ -11038,19 +11038,19 @@
         <v>2110</v>
       </c>
       <c r="I183" t="n">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="J183" t="n">
-        <v>6720</v>
+        <v>6726</v>
       </c>
       <c r="K183" t="n">
-        <v>4567</v>
+        <v>4570</v>
       </c>
       <c r="L183" t="n">
-        <v>2612</v>
+        <v>2618</v>
       </c>
       <c r="M183" t="n">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="N183" t="n">
         <v>2695</v>
@@ -11059,7 +11059,7 @@
         <v>807</v>
       </c>
       <c r="P183" t="n">
-        <v>-2016</v>
+        <v>-2015</v>
       </c>
       <c r="Q183" t="n">
         <v>8</v>
@@ -11075,16 +11075,16 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>-4996</v>
+        <v>-4994</v>
       </c>
       <c r="C184" t="n">
-        <v>-4800</v>
+        <v>-4798</v>
       </c>
       <c r="D184" t="n">
         <v>23417</v>
       </c>
       <c r="E184" t="n">
-        <v>28217</v>
+        <v>28215</v>
       </c>
       <c r="F184" t="n">
         <v>-1147</v>
@@ -11096,19 +11096,19 @@
         <v>1593</v>
       </c>
       <c r="I184" t="n">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="J184" t="n">
-        <v>7608</v>
+        <v>7611</v>
       </c>
       <c r="K184" t="n">
-        <v>5047</v>
+        <v>5049</v>
       </c>
       <c r="L184" t="n">
-        <v>2986</v>
+        <v>2989</v>
       </c>
       <c r="M184" t="n">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="N184" t="n">
         <v>2842</v>
@@ -11117,7 +11117,7 @@
         <v>652</v>
       </c>
       <c r="P184" t="n">
-        <v>-2748</v>
+        <v>-2749</v>
       </c>
       <c r="Q184" t="n">
         <v>-9</v>
@@ -11133,16 +11133,16 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>-8497</v>
+        <v>-8503</v>
       </c>
       <c r="C185" t="n">
-        <v>-9850</v>
+        <v>-9859</v>
       </c>
       <c r="D185" t="n">
         <v>20741</v>
       </c>
       <c r="E185" t="n">
-        <v>30591</v>
+        <v>30600</v>
       </c>
       <c r="F185" t="n">
         <v>-2185</v>
@@ -11154,19 +11154,19 @@
         <v>2402</v>
       </c>
       <c r="I185" t="n">
-        <v>3841</v>
+        <v>3839</v>
       </c>
       <c r="J185" t="n">
-        <v>8924</v>
+        <v>8923</v>
       </c>
       <c r="K185" t="n">
-        <v>5083</v>
+        <v>5084</v>
       </c>
       <c r="L185" t="n">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="M185" t="n">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="N185" t="n">
         <v>3917</v>
@@ -11175,7 +11175,7 @@
         <v>859</v>
       </c>
       <c r="P185" t="n">
-        <v>-2384</v>
+        <v>-2379</v>
       </c>
       <c r="Q185" t="n">
         <v>-104</v>
@@ -11191,16 +11191,16 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-1049</v>
+        <v>-1057</v>
       </c>
       <c r="C186" t="n">
-        <v>-4726</v>
+        <v>-4738</v>
       </c>
       <c r="D186" t="n">
         <v>24294</v>
       </c>
       <c r="E186" t="n">
-        <v>29020</v>
+        <v>29032</v>
       </c>
       <c r="F186" t="n">
         <v>-1774</v>
@@ -11212,19 +11212,19 @@
         <v>2113</v>
       </c>
       <c r="I186" t="n">
-        <v>5545</v>
+        <v>5547</v>
       </c>
       <c r="J186" t="n">
         <v>10326</v>
       </c>
       <c r="K186" t="n">
-        <v>4781</v>
+        <v>4779</v>
       </c>
       <c r="L186" t="n">
         <v>3550</v>
       </c>
       <c r="M186" t="n">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="N186" t="n">
         <v>5109</v>
@@ -11233,7 +11233,7 @@
         <v>811</v>
       </c>
       <c r="P186" t="n">
-        <v>-1843</v>
+        <v>-1841</v>
       </c>
       <c r="Q186" t="n">
         <v>-25</v>
@@ -11249,16 +11249,16 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>-2197</v>
+        <v>-2205</v>
       </c>
       <c r="C187" t="n">
-        <v>-6471</v>
+        <v>-6482</v>
       </c>
       <c r="D187" t="n">
         <v>20331</v>
       </c>
       <c r="E187" t="n">
-        <v>26802</v>
+        <v>26813</v>
       </c>
       <c r="F187" t="n">
         <v>-1423</v>
@@ -11270,19 +11270,19 @@
         <v>1551</v>
       </c>
       <c r="I187" t="n">
-        <v>6111</v>
+        <v>6114</v>
       </c>
       <c r="J187" t="n">
-        <v>11551</v>
+        <v>11552</v>
       </c>
       <c r="K187" t="n">
-        <v>5440</v>
+        <v>5438</v>
       </c>
       <c r="L187" t="n">
-        <v>3673</v>
+        <v>3674</v>
       </c>
       <c r="M187" t="n">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="N187" t="n">
         <v>5953</v>
@@ -11307,16 +11307,16 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1762</v>
+        <v>1739</v>
       </c>
       <c r="C188" t="n">
-        <v>-4561</v>
+        <v>-4586</v>
       </c>
       <c r="D188" t="n">
         <v>24620</v>
       </c>
       <c r="E188" t="n">
-        <v>29181</v>
+        <v>29206</v>
       </c>
       <c r="F188" t="n">
         <v>-501</v>
@@ -11331,16 +11331,16 @@
         <v>8015</v>
       </c>
       <c r="J188" t="n">
-        <v>13162</v>
+        <v>13164</v>
       </c>
       <c r="K188" t="n">
-        <v>5147</v>
+        <v>5149</v>
       </c>
       <c r="L188" t="n">
-        <v>4145</v>
+        <v>4147</v>
       </c>
       <c r="M188" t="n">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="N188" t="n">
         <v>7021</v>
@@ -11349,7 +11349,7 @@
         <v>819</v>
       </c>
       <c r="P188" t="n">
-        <v>-1539</v>
+        <v>-1537</v>
       </c>
       <c r="Q188" t="n">
         <v>-153</v>
@@ -11365,16 +11365,16 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>4654</v>
+        <v>4622</v>
       </c>
       <c r="C189" t="n">
-        <v>-2773</v>
+        <v>-2800</v>
       </c>
       <c r="D189" t="n">
         <v>21409</v>
       </c>
       <c r="E189" t="n">
-        <v>24182</v>
+        <v>24209</v>
       </c>
       <c r="F189" t="n">
         <v>-987</v>
@@ -11386,19 +11386,19 @@
         <v>1146</v>
       </c>
       <c r="I189" t="n">
-        <v>9349</v>
+        <v>9343</v>
       </c>
       <c r="J189" t="n">
-        <v>14319</v>
+        <v>14314</v>
       </c>
       <c r="K189" t="n">
-        <v>4970</v>
+        <v>4971</v>
       </c>
       <c r="L189" t="n">
-        <v>4279</v>
+        <v>4274</v>
       </c>
       <c r="M189" t="n">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="N189" t="n">
         <v>8378</v>
@@ -11407,7 +11407,7 @@
         <v>755</v>
       </c>
       <c r="P189" t="n">
-        <v>-1901</v>
+        <v>-1900</v>
       </c>
       <c r="Q189" t="n">
         <v>-21</v>
@@ -11423,16 +11423,16 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>611</v>
+        <v>588</v>
       </c>
       <c r="C190" t="n">
-        <v>-5333</v>
+        <v>-5354</v>
       </c>
       <c r="D190" t="n">
         <v>22126</v>
       </c>
       <c r="E190" t="n">
-        <v>27459</v>
+        <v>27480</v>
       </c>
       <c r="F190" t="n">
         <v>-2329</v>
@@ -11444,19 +11444,19 @@
         <v>2501</v>
       </c>
       <c r="I190" t="n">
-        <v>7738</v>
+        <v>7736</v>
       </c>
       <c r="J190" t="n">
-        <v>13048</v>
+        <v>13047</v>
       </c>
       <c r="K190" t="n">
-        <v>5310</v>
+        <v>5311</v>
       </c>
       <c r="L190" t="n">
-        <v>3895</v>
+        <v>3894</v>
       </c>
       <c r="M190" t="n">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="N190" t="n">
         <v>6976</v>
@@ -11481,16 +11481,16 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>477</v>
+        <v>448</v>
       </c>
       <c r="C191" t="n">
-        <v>-5884</v>
+        <v>-5911</v>
       </c>
       <c r="D191" t="n">
         <v>23490</v>
       </c>
       <c r="E191" t="n">
-        <v>29374</v>
+        <v>29401</v>
       </c>
       <c r="F191" t="n">
         <v>-2744</v>
@@ -11502,19 +11502,19 @@
         <v>2838</v>
       </c>
       <c r="I191" t="n">
-        <v>7937</v>
+        <v>7932</v>
       </c>
       <c r="J191" t="n">
-        <v>12791</v>
+        <v>12788</v>
       </c>
       <c r="K191" t="n">
-        <v>4854</v>
+        <v>4856</v>
       </c>
       <c r="L191" t="n">
-        <v>4095</v>
+        <v>4092</v>
       </c>
       <c r="M191" t="n">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="N191" t="n">
         <v>6748</v>
@@ -11523,7 +11523,7 @@
         <v>555</v>
       </c>
       <c r="P191" t="n">
-        <v>-1569</v>
+        <v>-1566</v>
       </c>
       <c r="Q191" t="n">
         <v>-7</v>
@@ -11539,16 +11539,16 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>-4198</v>
+        <v>-4209</v>
       </c>
       <c r="C192" t="n">
-        <v>-6351</v>
+        <v>-6363</v>
       </c>
       <c r="D192" t="n">
         <v>22146</v>
       </c>
       <c r="E192" t="n">
-        <v>28497</v>
+        <v>28509</v>
       </c>
       <c r="F192" t="n">
         <v>-2385</v>
@@ -11560,19 +11560,19 @@
         <v>2464</v>
       </c>
       <c r="I192" t="n">
-        <v>4087</v>
+        <v>4085</v>
       </c>
       <c r="J192" t="n">
         <v>9090</v>
       </c>
       <c r="K192" t="n">
-        <v>5003</v>
+        <v>5005</v>
       </c>
       <c r="L192" t="n">
         <v>3337</v>
       </c>
       <c r="M192" t="n">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="N192" t="n">
         <v>4005</v>
@@ -11581,7 +11581,7 @@
         <v>606</v>
       </c>
       <c r="P192" t="n">
-        <v>-1947</v>
+        <v>-1944</v>
       </c>
       <c r="Q192" t="n">
         <v>13</v>
@@ -11597,16 +11597,16 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-7420</v>
+        <v>-7432</v>
       </c>
       <c r="C193" t="n">
-        <v>-7460</v>
+        <v>-7482</v>
       </c>
       <c r="D193" t="n">
         <v>25850</v>
       </c>
       <c r="E193" t="n">
-        <v>33310</v>
+        <v>33332</v>
       </c>
       <c r="F193" t="n">
         <v>-1658</v>
@@ -11618,19 +11618,19 @@
         <v>1996</v>
       </c>
       <c r="I193" t="n">
-        <v>2607</v>
+        <v>2617</v>
       </c>
       <c r="J193" t="n">
-        <v>9547</v>
+        <v>9548</v>
       </c>
       <c r="K193" t="n">
-        <v>6940</v>
+        <v>6931</v>
       </c>
       <c r="L193" t="n">
-        <v>3610</v>
+        <v>3611</v>
       </c>
       <c r="M193" t="n">
-        <v>1938</v>
+        <v>1929</v>
       </c>
       <c r="N193" t="n">
         <v>3143</v>
@@ -11655,16 +11655,16 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>-6739</v>
+        <v>-6758</v>
       </c>
       <c r="C194" t="n">
-        <v>-6885</v>
+        <v>-6894</v>
       </c>
       <c r="D194" t="n">
         <v>19767</v>
       </c>
       <c r="E194" t="n">
-        <v>26652</v>
+        <v>26661</v>
       </c>
       <c r="F194" t="n">
         <v>-1371</v>
@@ -11697,7 +11697,7 @@
         <v>789</v>
       </c>
       <c r="P194" t="n">
-        <v>-2220</v>
+        <v>-2230</v>
       </c>
       <c r="Q194" t="n">
         <v>-314</v>
@@ -11713,16 +11713,16 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>-7365</v>
+        <v>-7495</v>
       </c>
       <c r="C195" t="n">
-        <v>-7511</v>
+        <v>-7512</v>
       </c>
       <c r="D195" t="n">
         <v>20636</v>
       </c>
       <c r="E195" t="n">
-        <v>28147</v>
+        <v>28148</v>
       </c>
       <c r="F195" t="n">
         <v>-1946</v>
@@ -11755,7 +11755,7 @@
         <v>634</v>
       </c>
       <c r="P195" t="n">
-        <v>-1915</v>
+        <v>-2044</v>
       </c>
       <c r="Q195" t="n">
         <v>-193</v>
@@ -11771,16 +11771,16 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>-9604</v>
+        <v>-9749</v>
       </c>
       <c r="C196" t="n">
-        <v>-9472</v>
+        <v>-9486</v>
       </c>
       <c r="D196" t="n">
         <v>21704</v>
       </c>
       <c r="E196" t="n">
-        <v>31176</v>
+        <v>31190</v>
       </c>
       <c r="F196" t="n">
         <v>-1603</v>
@@ -11813,7 +11813,7 @@
         <v>659</v>
       </c>
       <c r="P196" t="n">
-        <v>-2439</v>
+        <v>-2570</v>
       </c>
       <c r="Q196" t="n">
         <v>-245</v>
@@ -11829,16 +11829,16 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>-5505</v>
+        <v>-5621</v>
       </c>
       <c r="C197" t="n">
-        <v>-6900</v>
+        <v>-6955</v>
       </c>
       <c r="D197" t="n">
-        <v>24738</v>
+        <v>24737</v>
       </c>
       <c r="E197" t="n">
-        <v>31638</v>
+        <v>31692</v>
       </c>
       <c r="F197" t="n">
         <v>-824</v>
@@ -11871,7 +11871,7 @@
         <v>823</v>
       </c>
       <c r="P197" t="n">
-        <v>-2281</v>
+        <v>-2342</v>
       </c>
       <c r="Q197" t="n">
         <v>-143</v>
@@ -11887,16 +11887,16 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>-1320</v>
+        <v>-1367</v>
       </c>
       <c r="C198" t="n">
-        <v>-4452</v>
+        <v>-4496</v>
       </c>
       <c r="D198" t="n">
-        <v>21819</v>
+        <v>21813</v>
       </c>
       <c r="E198" t="n">
-        <v>26271</v>
+        <v>26309</v>
       </c>
       <c r="F198" t="n">
         <v>-563</v>
@@ -11929,7 +11929,7 @@
         <v>1026</v>
       </c>
       <c r="P198" t="n">
-        <v>-2214</v>
+        <v>-2217</v>
       </c>
       <c r="Q198" t="n">
         <v>-164</v>
@@ -11945,16 +11945,16 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>-4333</v>
+        <v>-4472</v>
       </c>
       <c r="C199" t="n">
-        <v>-8566</v>
+        <v>-8606</v>
       </c>
       <c r="D199" t="n">
-        <v>24396</v>
+        <v>24397</v>
       </c>
       <c r="E199" t="n">
-        <v>32962</v>
+        <v>33003</v>
       </c>
       <c r="F199" t="n">
         <v>-1160</v>
@@ -11987,7 +11987,7 @@
         <v>942</v>
       </c>
       <c r="P199" t="n">
-        <v>-1792</v>
+        <v>-1891</v>
       </c>
       <c r="Q199" t="n">
         <v>-729</v>
@@ -12003,16 +12003,16 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>36</v>
+        <v>-89</v>
       </c>
       <c r="C200" t="n">
-        <v>-5579</v>
+        <v>-5643</v>
       </c>
       <c r="D200" t="n">
-        <v>25185</v>
+        <v>25182</v>
       </c>
       <c r="E200" t="n">
-        <v>30764</v>
+        <v>30825</v>
       </c>
       <c r="F200" t="n">
         <v>-462</v>
@@ -12024,13 +12024,13 @@
         <v>946</v>
       </c>
       <c r="I200" t="n">
-        <v>8228</v>
+        <v>8222</v>
       </c>
       <c r="J200" t="n">
         <v>13325</v>
       </c>
       <c r="K200" t="n">
-        <v>5097</v>
+        <v>5103</v>
       </c>
       <c r="L200" t="n">
         <v>4585</v>
@@ -12045,13 +12045,71 @@
         <v>996</v>
       </c>
       <c r="P200" t="n">
-        <v>-2557</v>
+        <v>-2600</v>
       </c>
       <c r="Q200" t="n">
-        <v>-56</v>
+        <v>-68</v>
       </c>
       <c r="R200" s="1" t="n">
         <v>46204</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-8</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>4053</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-3746</v>
+      </c>
+      <c r="D201" t="n">
+        <v>23327</v>
+      </c>
+      <c r="E201" t="n">
+        <v>27073</v>
+      </c>
+      <c r="F201" t="n">
+        <v>826</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1149</v>
+      </c>
+      <c r="H201" t="n">
+        <v>323</v>
+      </c>
+      <c r="I201" t="n">
+        <v>9711</v>
+      </c>
+      <c r="J201" t="n">
+        <v>14658</v>
+      </c>
+      <c r="K201" t="n">
+        <v>4947</v>
+      </c>
+      <c r="L201" t="n">
+        <v>4952</v>
+      </c>
+      <c r="M201" t="n">
+        <v>1687</v>
+      </c>
+      <c r="N201" t="n">
+        <v>8197</v>
+      </c>
+      <c r="O201" t="n">
+        <v>912</v>
+      </c>
+      <c r="P201" t="n">
+        <v>-1894</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>-18</v>
+      </c>
+      <c r="R201" s="1" t="n">
+        <v>46235</v>
       </c>
     </row>
   </sheetData>

--- a/cari acik/odemeler_dengesi_raw.xlsx
+++ b/cari acik/odemeler_dengesi_raw.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,92 +433,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Cari İşlemler Dengesi</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Dış Ticaret Dengesi</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Toplam Mal İhracatı</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Toplam Mal İthalatı</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Parasal Olmayan Altın (net)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Altın İhracatı</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Altın İthalatı</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Hizmetler Dengesi</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Hizmet Gelirleri</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Hizmet Giderleri</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Taşımacılık - Gelir</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Taşımacılık - Gider</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Seyahat - Gelir</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Seyahat - Gider</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Birincil Gelir Dengesi</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>İkincil Gelir Dengesi</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Tarih_dt</t>
         </is>
@@ -566,7 +578,7 @@
       <c r="Q2" t="n">
         <v>115</v>
       </c>
-      <c r="R2" s="1" t="n">
+      <c r="R2" s="2" t="n">
         <v>40179</v>
       </c>
     </row>
@@ -624,7 +636,7 @@
       <c r="Q3" t="n">
         <v>72</v>
       </c>
-      <c r="R3" s="1" t="n">
+      <c r="R3" s="2" t="n">
         <v>40210</v>
       </c>
     </row>
@@ -682,7 +694,7 @@
       <c r="Q4" t="n">
         <v>114</v>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="R4" s="2" t="n">
         <v>40238</v>
       </c>
     </row>
@@ -740,7 +752,7 @@
       <c r="Q5" t="n">
         <v>82</v>
       </c>
-      <c r="R5" s="1" t="n">
+      <c r="R5" s="2" t="n">
         <v>40269</v>
       </c>
     </row>
@@ -798,7 +810,7 @@
       <c r="Q6" t="n">
         <v>73</v>
       </c>
-      <c r="R6" s="1" t="n">
+      <c r="R6" s="2" t="n">
         <v>40299</v>
       </c>
     </row>
@@ -856,7 +868,7 @@
       <c r="Q7" t="n">
         <v>121</v>
       </c>
-      <c r="R7" s="1" t="n">
+      <c r="R7" s="2" t="n">
         <v>40330</v>
       </c>
     </row>
@@ -914,7 +926,7 @@
       <c r="Q8" t="n">
         <v>109</v>
       </c>
-      <c r="R8" s="1" t="n">
+      <c r="R8" s="2" t="n">
         <v>40360</v>
       </c>
     </row>
@@ -972,7 +984,7 @@
       <c r="Q9" t="n">
         <v>155</v>
       </c>
-      <c r="R9" s="1" t="n">
+      <c r="R9" s="2" t="n">
         <v>40391</v>
       </c>
     </row>
@@ -1030,7 +1042,7 @@
       <c r="Q10" t="n">
         <v>159</v>
       </c>
-      <c r="R10" s="1" t="n">
+      <c r="R10" s="2" t="n">
         <v>40422</v>
       </c>
     </row>
@@ -1088,7 +1100,7 @@
       <c r="Q11" t="n">
         <v>183</v>
       </c>
-      <c r="R11" s="1" t="n">
+      <c r="R11" s="2" t="n">
         <v>40452</v>
       </c>
     </row>
@@ -1146,7 +1158,7 @@
       <c r="Q12" t="n">
         <v>100</v>
       </c>
-      <c r="R12" s="1" t="n">
+      <c r="R12" s="2" t="n">
         <v>40483</v>
       </c>
     </row>
@@ -1204,7 +1216,7 @@
       <c r="Q13" t="n">
         <v>192</v>
       </c>
-      <c r="R13" s="1" t="n">
+      <c r="R13" s="2" t="n">
         <v>40513</v>
       </c>
     </row>
@@ -1262,7 +1274,7 @@
       <c r="Q14" t="n">
         <v>222</v>
       </c>
-      <c r="R14" s="1" t="n">
+      <c r="R14" s="2" t="n">
         <v>40544</v>
       </c>
     </row>
@@ -1320,7 +1332,7 @@
       <c r="Q15" t="n">
         <v>85</v>
       </c>
-      <c r="R15" s="1" t="n">
+      <c r="R15" s="2" t="n">
         <v>40575</v>
       </c>
     </row>
@@ -1378,7 +1390,7 @@
       <c r="Q16" t="n">
         <v>77</v>
       </c>
-      <c r="R16" s="1" t="n">
+      <c r="R16" s="2" t="n">
         <v>40603</v>
       </c>
     </row>
@@ -1436,7 +1448,7 @@
       <c r="Q17" t="n">
         <v>49</v>
       </c>
-      <c r="R17" s="1" t="n">
+      <c r="R17" s="2" t="n">
         <v>40634</v>
       </c>
     </row>
@@ -1494,7 +1506,7 @@
       <c r="Q18" t="n">
         <v>139</v>
       </c>
-      <c r="R18" s="1" t="n">
+      <c r="R18" s="2" t="n">
         <v>40664</v>
       </c>
     </row>
@@ -1552,7 +1564,7 @@
       <c r="Q19" t="n">
         <v>99</v>
       </c>
-      <c r="R19" s="1" t="n">
+      <c r="R19" s="2" t="n">
         <v>40695</v>
       </c>
     </row>
@@ -1610,7 +1622,7 @@
       <c r="Q20" t="n">
         <v>103</v>
       </c>
-      <c r="R20" s="1" t="n">
+      <c r="R20" s="2" t="n">
         <v>40725</v>
       </c>
     </row>
@@ -1668,7 +1680,7 @@
       <c r="Q21" t="n">
         <v>241</v>
       </c>
-      <c r="R21" s="1" t="n">
+      <c r="R21" s="2" t="n">
         <v>40756</v>
       </c>
     </row>
@@ -1726,7 +1738,7 @@
       <c r="Q22" t="n">
         <v>149</v>
       </c>
-      <c r="R22" s="1" t="n">
+      <c r="R22" s="2" t="n">
         <v>40787</v>
       </c>
     </row>
@@ -1784,7 +1796,7 @@
       <c r="Q23" t="n">
         <v>67</v>
       </c>
-      <c r="R23" s="1" t="n">
+      <c r="R23" s="2" t="n">
         <v>40817</v>
       </c>
     </row>
@@ -1842,7 +1854,7 @@
       <c r="Q24" t="n">
         <v>106</v>
       </c>
-      <c r="R24" s="1" t="n">
+      <c r="R24" s="2" t="n">
         <v>40848</v>
       </c>
     </row>
@@ -1900,7 +1912,7 @@
       <c r="Q25" t="n">
         <v>382</v>
       </c>
-      <c r="R25" s="1" t="n">
+      <c r="R25" s="2" t="n">
         <v>40878</v>
       </c>
     </row>
@@ -1958,7 +1970,7 @@
       <c r="Q26" t="n">
         <v>69</v>
       </c>
-      <c r="R26" s="1" t="n">
+      <c r="R26" s="2" t="n">
         <v>40909</v>
       </c>
     </row>
@@ -2016,7 +2028,7 @@
       <c r="Q27" t="n">
         <v>224</v>
       </c>
-      <c r="R27" s="1" t="n">
+      <c r="R27" s="2" t="n">
         <v>40940</v>
       </c>
     </row>
@@ -2074,7 +2086,7 @@
       <c r="Q28" t="n">
         <v>57</v>
       </c>
-      <c r="R28" s="1" t="n">
+      <c r="R28" s="2" t="n">
         <v>40969</v>
       </c>
     </row>
@@ -2132,7 +2144,7 @@
       <c r="Q29" t="n">
         <v>105</v>
       </c>
-      <c r="R29" s="1" t="n">
+      <c r="R29" s="2" t="n">
         <v>41000</v>
       </c>
     </row>
@@ -2190,7 +2202,7 @@
       <c r="Q30" t="n">
         <v>90</v>
       </c>
-      <c r="R30" s="1" t="n">
+      <c r="R30" s="2" t="n">
         <v>41030</v>
       </c>
     </row>
@@ -2248,7 +2260,7 @@
       <c r="Q31" t="n">
         <v>73</v>
       </c>
-      <c r="R31" s="1" t="n">
+      <c r="R31" s="2" t="n">
         <v>41061</v>
       </c>
     </row>
@@ -2306,7 +2318,7 @@
       <c r="Q32" t="n">
         <v>72</v>
       </c>
-      <c r="R32" s="1" t="n">
+      <c r="R32" s="2" t="n">
         <v>41091</v>
       </c>
     </row>
@@ -2364,7 +2376,7 @@
       <c r="Q33" t="n">
         <v>156</v>
       </c>
-      <c r="R33" s="1" t="n">
+      <c r="R33" s="2" t="n">
         <v>41122</v>
       </c>
     </row>
@@ -2422,7 +2434,7 @@
       <c r="Q34" t="n">
         <v>122</v>
       </c>
-      <c r="R34" s="1" t="n">
+      <c r="R34" s="2" t="n">
         <v>41153</v>
       </c>
     </row>
@@ -2480,7 +2492,7 @@
       <c r="Q35" t="n">
         <v>89</v>
       </c>
-      <c r="R35" s="1" t="n">
+      <c r="R35" s="2" t="n">
         <v>41183</v>
       </c>
     </row>
@@ -2538,7 +2550,7 @@
       <c r="Q36" t="n">
         <v>116</v>
       </c>
-      <c r="R36" s="1" t="n">
+      <c r="R36" s="2" t="n">
         <v>41214</v>
       </c>
     </row>
@@ -2596,7 +2608,7 @@
       <c r="Q37" t="n">
         <v>278</v>
       </c>
-      <c r="R37" s="1" t="n">
+      <c r="R37" s="2" t="n">
         <v>41244</v>
       </c>
     </row>
@@ -2654,7 +2666,7 @@
       <c r="Q38" t="n">
         <v>49</v>
       </c>
-      <c r="R38" s="1" t="n">
+      <c r="R38" s="2" t="n">
         <v>41275</v>
       </c>
     </row>
@@ -2712,7 +2724,7 @@
       <c r="Q39" t="n">
         <v>161</v>
       </c>
-      <c r="R39" s="1" t="n">
+      <c r="R39" s="2" t="n">
         <v>41306</v>
       </c>
     </row>
@@ -2770,7 +2782,7 @@
       <c r="Q40" t="n">
         <v>66</v>
       </c>
-      <c r="R40" s="1" t="n">
+      <c r="R40" s="2" t="n">
         <v>41334</v>
       </c>
     </row>
@@ -2828,7 +2840,7 @@
       <c r="Q41" t="n">
         <v>45</v>
       </c>
-      <c r="R41" s="1" t="n">
+      <c r="R41" s="2" t="n">
         <v>41365</v>
       </c>
     </row>
@@ -2886,7 +2898,7 @@
       <c r="Q42" t="n">
         <v>159</v>
       </c>
-      <c r="R42" s="1" t="n">
+      <c r="R42" s="2" t="n">
         <v>41395</v>
       </c>
     </row>
@@ -2944,7 +2956,7 @@
       <c r="Q43" t="n">
         <v>92</v>
       </c>
-      <c r="R43" s="1" t="n">
+      <c r="R43" s="2" t="n">
         <v>41426</v>
       </c>
     </row>
@@ -3002,7 +3014,7 @@
       <c r="Q44" t="n">
         <v>107</v>
       </c>
-      <c r="R44" s="1" t="n">
+      <c r="R44" s="2" t="n">
         <v>41456</v>
       </c>
     </row>
@@ -3060,7 +3072,7 @@
       <c r="Q45" t="n">
         <v>108</v>
       </c>
-      <c r="R45" s="1" t="n">
+      <c r="R45" s="2" t="n">
         <v>41487</v>
       </c>
     </row>
@@ -3118,7 +3130,7 @@
       <c r="Q46" t="n">
         <v>110</v>
       </c>
-      <c r="R46" s="1" t="n">
+      <c r="R46" s="2" t="n">
         <v>41518</v>
       </c>
     </row>
@@ -3176,7 +3188,7 @@
       <c r="Q47" t="n">
         <v>113</v>
       </c>
-      <c r="R47" s="1" t="n">
+      <c r="R47" s="2" t="n">
         <v>41548</v>
       </c>
     </row>
@@ -3234,7 +3246,7 @@
       <c r="Q48" t="n">
         <v>115</v>
       </c>
-      <c r="R48" s="1" t="n">
+      <c r="R48" s="2" t="n">
         <v>41579</v>
       </c>
     </row>
@@ -3292,7 +3304,7 @@
       <c r="Q49" t="n">
         <v>152</v>
       </c>
-      <c r="R49" s="1" t="n">
+      <c r="R49" s="2" t="n">
         <v>41609</v>
       </c>
     </row>
@@ -3350,7 +3362,7 @@
       <c r="Q50" t="n">
         <v>35</v>
       </c>
-      <c r="R50" s="1" t="n">
+      <c r="R50" s="2" t="n">
         <v>41640</v>
       </c>
     </row>
@@ -3408,7 +3420,7 @@
       <c r="Q51" t="n">
         <v>157</v>
       </c>
-      <c r="R51" s="1" t="n">
+      <c r="R51" s="2" t="n">
         <v>41671</v>
       </c>
     </row>
@@ -3466,7 +3478,7 @@
       <c r="Q52" t="n">
         <v>222</v>
       </c>
-      <c r="R52" s="1" t="n">
+      <c r="R52" s="2" t="n">
         <v>41699</v>
       </c>
     </row>
@@ -3524,7 +3536,7 @@
       <c r="Q53" t="n">
         <v>37</v>
       </c>
-      <c r="R53" s="1" t="n">
+      <c r="R53" s="2" t="n">
         <v>41730</v>
       </c>
     </row>
@@ -3582,7 +3594,7 @@
       <c r="Q54" t="n">
         <v>86</v>
       </c>
-      <c r="R54" s="1" t="n">
+      <c r="R54" s="2" t="n">
         <v>41760</v>
       </c>
     </row>
@@ -3640,7 +3652,7 @@
       <c r="Q55" t="n">
         <v>111</v>
       </c>
-      <c r="R55" s="1" t="n">
+      <c r="R55" s="2" t="n">
         <v>41791</v>
       </c>
     </row>
@@ -3698,7 +3710,7 @@
       <c r="Q56" t="n">
         <v>19</v>
       </c>
-      <c r="R56" s="1" t="n">
+      <c r="R56" s="2" t="n">
         <v>41821</v>
       </c>
     </row>
@@ -3756,7 +3768,7 @@
       <c r="Q57" t="n">
         <v>121</v>
       </c>
-      <c r="R57" s="1" t="n">
+      <c r="R57" s="2" t="n">
         <v>41852</v>
       </c>
     </row>
@@ -3814,7 +3826,7 @@
       <c r="Q58" t="n">
         <v>263</v>
       </c>
-      <c r="R58" s="1" t="n">
+      <c r="R58" s="2" t="n">
         <v>41883</v>
       </c>
     </row>
@@ -3872,7 +3884,7 @@
       <c r="Q59" t="n">
         <v>88</v>
       </c>
-      <c r="R59" s="1" t="n">
+      <c r="R59" s="2" t="n">
         <v>41913</v>
       </c>
     </row>
@@ -3930,7 +3942,7 @@
       <c r="Q60" t="n">
         <v>169</v>
       </c>
-      <c r="R60" s="1" t="n">
+      <c r="R60" s="2" t="n">
         <v>41944</v>
       </c>
     </row>
@@ -3988,7 +4000,7 @@
       <c r="Q61" t="n">
         <v>212</v>
       </c>
-      <c r="R61" s="1" t="n">
+      <c r="R61" s="2" t="n">
         <v>41974</v>
       </c>
     </row>
@@ -4046,7 +4058,7 @@
       <c r="Q62" t="n">
         <v>15</v>
       </c>
-      <c r="R62" s="1" t="n">
+      <c r="R62" s="2" t="n">
         <v>42005</v>
       </c>
     </row>
@@ -4104,7 +4116,7 @@
       <c r="Q63" t="n">
         <v>231</v>
       </c>
-      <c r="R63" s="1" t="n">
+      <c r="R63" s="2" t="n">
         <v>42036</v>
       </c>
     </row>
@@ -4162,7 +4174,7 @@
       <c r="Q64" t="n">
         <v>145</v>
       </c>
-      <c r="R64" s="1" t="n">
+      <c r="R64" s="2" t="n">
         <v>42064</v>
       </c>
     </row>
@@ -4220,7 +4232,7 @@
       <c r="Q65" t="n">
         <v>62</v>
       </c>
-      <c r="R65" s="1" t="n">
+      <c r="R65" s="2" t="n">
         <v>42095</v>
       </c>
     </row>
@@ -4278,7 +4290,7 @@
       <c r="Q66" t="n">
         <v>21</v>
       </c>
-      <c r="R66" s="1" t="n">
+      <c r="R66" s="2" t="n">
         <v>42125</v>
       </c>
     </row>
@@ -4336,7 +4348,7 @@
       <c r="Q67" t="n">
         <v>86</v>
       </c>
-      <c r="R67" s="1" t="n">
+      <c r="R67" s="2" t="n">
         <v>42156</v>
       </c>
     </row>
@@ -4394,7 +4406,7 @@
       <c r="Q68" t="n">
         <v>125</v>
       </c>
-      <c r="R68" s="1" t="n">
+      <c r="R68" s="2" t="n">
         <v>42186</v>
       </c>
     </row>
@@ -4452,7 +4464,7 @@
       <c r="Q69" t="n">
         <v>109</v>
       </c>
-      <c r="R69" s="1" t="n">
+      <c r="R69" s="2" t="n">
         <v>42217</v>
       </c>
     </row>
@@ -4510,7 +4522,7 @@
       <c r="Q70" t="n">
         <v>110</v>
       </c>
-      <c r="R70" s="1" t="n">
+      <c r="R70" s="2" t="n">
         <v>42248</v>
       </c>
     </row>
@@ -4568,7 +4580,7 @@
       <c r="Q71" t="n">
         <v>55</v>
       </c>
-      <c r="R71" s="1" t="n">
+      <c r="R71" s="2" t="n">
         <v>42278</v>
       </c>
     </row>
@@ -4626,7 +4638,7 @@
       <c r="Q72" t="n">
         <v>213</v>
       </c>
-      <c r="R72" s="1" t="n">
+      <c r="R72" s="2" t="n">
         <v>42309</v>
       </c>
     </row>
@@ -4684,7 +4696,7 @@
       <c r="Q73" t="n">
         <v>225</v>
       </c>
-      <c r="R73" s="1" t="n">
+      <c r="R73" s="2" t="n">
         <v>42339</v>
       </c>
     </row>
@@ -4742,7 +4754,7 @@
       <c r="Q74" t="n">
         <v>112</v>
       </c>
-      <c r="R74" s="1" t="n">
+      <c r="R74" s="2" t="n">
         <v>42370</v>
       </c>
     </row>
@@ -4800,7 +4812,7 @@
       <c r="Q75" t="n">
         <v>365</v>
       </c>
-      <c r="R75" s="1" t="n">
+      <c r="R75" s="2" t="n">
         <v>42401</v>
       </c>
     </row>
@@ -4858,7 +4870,7 @@
       <c r="Q76" t="n">
         <v>-19</v>
       </c>
-      <c r="R76" s="1" t="n">
+      <c r="R76" s="2" t="n">
         <v>42430</v>
       </c>
     </row>
@@ -4916,7 +4928,7 @@
       <c r="Q77" t="n">
         <v>292</v>
       </c>
-      <c r="R77" s="1" t="n">
+      <c r="R77" s="2" t="n">
         <v>42461</v>
       </c>
     </row>
@@ -4974,7 +4986,7 @@
       <c r="Q78" t="n">
         <v>-42</v>
       </c>
-      <c r="R78" s="1" t="n">
+      <c r="R78" s="2" t="n">
         <v>42491</v>
       </c>
     </row>
@@ -5032,7 +5044,7 @@
       <c r="Q79" t="n">
         <v>71</v>
       </c>
-      <c r="R79" s="1" t="n">
+      <c r="R79" s="2" t="n">
         <v>42522</v>
       </c>
     </row>
@@ -5090,7 +5102,7 @@
       <c r="Q80" t="n">
         <v>46</v>
       </c>
-      <c r="R80" s="1" t="n">
+      <c r="R80" s="2" t="n">
         <v>42552</v>
       </c>
     </row>
@@ -5148,7 +5160,7 @@
       <c r="Q81" t="n">
         <v>49</v>
       </c>
-      <c r="R81" s="1" t="n">
+      <c r="R81" s="2" t="n">
         <v>42583</v>
       </c>
     </row>
@@ -5206,7 +5218,7 @@
       <c r="Q82" t="n">
         <v>138</v>
       </c>
-      <c r="R82" s="1" t="n">
+      <c r="R82" s="2" t="n">
         <v>42614</v>
       </c>
     </row>
@@ -5264,7 +5276,7 @@
       <c r="Q83" t="n">
         <v>112</v>
       </c>
-      <c r="R83" s="1" t="n">
+      <c r="R83" s="2" t="n">
         <v>42644</v>
       </c>
     </row>
@@ -5322,7 +5334,7 @@
       <c r="Q84" t="n">
         <v>199</v>
       </c>
-      <c r="R84" s="1" t="n">
+      <c r="R84" s="2" t="n">
         <v>42675</v>
       </c>
     </row>
@@ -5380,7 +5392,7 @@
       <c r="Q85" t="n">
         <v>235</v>
       </c>
-      <c r="R85" s="1" t="n">
+      <c r="R85" s="2" t="n">
         <v>42705</v>
       </c>
     </row>
@@ -5438,7 +5450,7 @@
       <c r="Q86" t="n">
         <v>133</v>
       </c>
-      <c r="R86" s="1" t="n">
+      <c r="R86" s="2" t="n">
         <v>42736</v>
       </c>
     </row>
@@ -5496,7 +5508,7 @@
       <c r="Q87" t="n">
         <v>103</v>
       </c>
-      <c r="R87" s="1" t="n">
+      <c r="R87" s="2" t="n">
         <v>42767</v>
       </c>
     </row>
@@ -5554,7 +5566,7 @@
       <c r="Q88" t="n">
         <v>223</v>
       </c>
-      <c r="R88" s="1" t="n">
+      <c r="R88" s="2" t="n">
         <v>42795</v>
       </c>
     </row>
@@ -5612,7 +5624,7 @@
       <c r="Q89" t="n">
         <v>31</v>
       </c>
-      <c r="R89" s="1" t="n">
+      <c r="R89" s="2" t="n">
         <v>42826</v>
       </c>
     </row>
@@ -5670,7 +5682,7 @@
       <c r="Q90" t="n">
         <v>245</v>
       </c>
-      <c r="R90" s="1" t="n">
+      <c r="R90" s="2" t="n">
         <v>42856</v>
       </c>
     </row>
@@ -5728,7 +5740,7 @@
       <c r="Q91" t="n">
         <v>273</v>
       </c>
-      <c r="R91" s="1" t="n">
+      <c r="R91" s="2" t="n">
         <v>42887</v>
       </c>
     </row>
@@ -5786,7 +5798,7 @@
       <c r="Q92" t="n">
         <v>305</v>
       </c>
-      <c r="R92" s="1" t="n">
+      <c r="R92" s="2" t="n">
         <v>42917</v>
       </c>
     </row>
@@ -5844,7 +5856,7 @@
       <c r="Q93" t="n">
         <v>213</v>
       </c>
-      <c r="R93" s="1" t="n">
+      <c r="R93" s="2" t="n">
         <v>42948</v>
       </c>
     </row>
@@ -5902,7 +5914,7 @@
       <c r="Q94" t="n">
         <v>209</v>
       </c>
-      <c r="R94" s="1" t="n">
+      <c r="R94" s="2" t="n">
         <v>42979</v>
       </c>
     </row>
@@ -5960,7 +5972,7 @@
       <c r="Q95" t="n">
         <v>262</v>
       </c>
-      <c r="R95" s="1" t="n">
+      <c r="R95" s="2" t="n">
         <v>43009</v>
       </c>
     </row>
@@ -6018,7 +6030,7 @@
       <c r="Q96" t="n">
         <v>277</v>
       </c>
-      <c r="R96" s="1" t="n">
+      <c r="R96" s="2" t="n">
         <v>43040</v>
       </c>
     </row>
@@ -6076,7 +6088,7 @@
       <c r="Q97" t="n">
         <v>259</v>
       </c>
-      <c r="R97" s="1" t="n">
+      <c r="R97" s="2" t="n">
         <v>43070</v>
       </c>
     </row>
@@ -6134,7 +6146,7 @@
       <c r="Q98" t="n">
         <v>201</v>
       </c>
-      <c r="R98" s="1" t="n">
+      <c r="R98" s="2" t="n">
         <v>43101</v>
       </c>
     </row>
@@ -6192,7 +6204,7 @@
       <c r="Q99" t="n">
         <v>-9</v>
       </c>
-      <c r="R99" s="1" t="n">
+      <c r="R99" s="2" t="n">
         <v>43132</v>
       </c>
     </row>
@@ -6250,7 +6262,7 @@
       <c r="Q100" t="n">
         <v>-3</v>
       </c>
-      <c r="R100" s="1" t="n">
+      <c r="R100" s="2" t="n">
         <v>43160</v>
       </c>
     </row>
@@ -6308,7 +6320,7 @@
       <c r="Q101" t="n">
         <v>65</v>
       </c>
-      <c r="R101" s="1" t="n">
+      <c r="R101" s="2" t="n">
         <v>43191</v>
       </c>
     </row>
@@ -6366,7 +6378,7 @@
       <c r="Q102" t="n">
         <v>-145</v>
       </c>
-      <c r="R102" s="1" t="n">
+      <c r="R102" s="2" t="n">
         <v>43221</v>
       </c>
     </row>
@@ -6424,7 +6436,7 @@
       <c r="Q103" t="n">
         <v>35</v>
       </c>
-      <c r="R103" s="1" t="n">
+      <c r="R103" s="2" t="n">
         <v>43252</v>
       </c>
     </row>
@@ -6482,7 +6494,7 @@
       <c r="Q104" t="n">
         <v>62</v>
       </c>
-      <c r="R104" s="1" t="n">
+      <c r="R104" s="2" t="n">
         <v>43282</v>
       </c>
     </row>
@@ -6540,7 +6552,7 @@
       <c r="Q105" t="n">
         <v>28</v>
       </c>
-      <c r="R105" s="1" t="n">
+      <c r="R105" s="2" t="n">
         <v>43313</v>
       </c>
     </row>
@@ -6598,7 +6610,7 @@
       <c r="Q106" t="n">
         <v>104</v>
       </c>
-      <c r="R106" s="1" t="n">
+      <c r="R106" s="2" t="n">
         <v>43344</v>
       </c>
     </row>
@@ -6656,7 +6668,7 @@
       <c r="Q107" t="n">
         <v>111</v>
       </c>
-      <c r="R107" s="1" t="n">
+      <c r="R107" s="2" t="n">
         <v>43374</v>
       </c>
     </row>
@@ -6714,7 +6726,7 @@
       <c r="Q108" t="n">
         <v>212</v>
       </c>
-      <c r="R108" s="1" t="n">
+      <c r="R108" s="2" t="n">
         <v>43405</v>
       </c>
     </row>
@@ -6772,7 +6784,7 @@
       <c r="Q109" t="n">
         <v>120</v>
       </c>
-      <c r="R109" s="1" t="n">
+      <c r="R109" s="2" t="n">
         <v>43435</v>
       </c>
     </row>
@@ -6830,7 +6842,7 @@
       <c r="Q110" t="n">
         <v>92</v>
       </c>
-      <c r="R110" s="1" t="n">
+      <c r="R110" s="2" t="n">
         <v>43466</v>
       </c>
     </row>
@@ -6888,7 +6900,7 @@
       <c r="Q111" t="n">
         <v>-67</v>
       </c>
-      <c r="R111" s="1" t="n">
+      <c r="R111" s="2" t="n">
         <v>43497</v>
       </c>
     </row>
@@ -6946,7 +6958,7 @@
       <c r="Q112" t="n">
         <v>125</v>
       </c>
-      <c r="R112" s="1" t="n">
+      <c r="R112" s="2" t="n">
         <v>43525</v>
       </c>
     </row>
@@ -7004,7 +7016,7 @@
       <c r="Q113" t="n">
         <v>-16</v>
       </c>
-      <c r="R113" s="1" t="n">
+      <c r="R113" s="2" t="n">
         <v>43556</v>
       </c>
     </row>
@@ -7062,7 +7074,7 @@
       <c r="Q114" t="n">
         <v>-71</v>
       </c>
-      <c r="R114" s="1" t="n">
+      <c r="R114" s="2" t="n">
         <v>43586</v>
       </c>
     </row>
@@ -7120,7 +7132,7 @@
       <c r="Q115" t="n">
         <v>19</v>
       </c>
-      <c r="R115" s="1" t="n">
+      <c r="R115" s="2" t="n">
         <v>43617</v>
       </c>
     </row>
@@ -7178,7 +7190,7 @@
       <c r="Q116" t="n">
         <v>141</v>
       </c>
-      <c r="R116" s="1" t="n">
+      <c r="R116" s="2" t="n">
         <v>43647</v>
       </c>
     </row>
@@ -7236,7 +7248,7 @@
       <c r="Q117" t="n">
         <v>99</v>
       </c>
-      <c r="R117" s="1" t="n">
+      <c r="R117" s="2" t="n">
         <v>43678</v>
       </c>
     </row>
@@ -7294,7 +7306,7 @@
       <c r="Q118" t="n">
         <v>100</v>
       </c>
-      <c r="R118" s="1" t="n">
+      <c r="R118" s="2" t="n">
         <v>43709</v>
       </c>
     </row>
@@ -7352,7 +7364,7 @@
       <c r="Q119" t="n">
         <v>109</v>
       </c>
-      <c r="R119" s="1" t="n">
+      <c r="R119" s="2" t="n">
         <v>43739</v>
       </c>
     </row>
@@ -7410,7 +7422,7 @@
       <c r="Q120" t="n">
         <v>92</v>
       </c>
-      <c r="R120" s="1" t="n">
+      <c r="R120" s="2" t="n">
         <v>43770</v>
       </c>
     </row>
@@ -7468,7 +7480,7 @@
       <c r="Q121" t="n">
         <v>248</v>
       </c>
-      <c r="R121" s="1" t="n">
+      <c r="R121" s="2" t="n">
         <v>43800</v>
       </c>
     </row>
@@ -7526,7 +7538,7 @@
       <c r="Q122" t="n">
         <v>94</v>
       </c>
-      <c r="R122" s="1" t="n">
+      <c r="R122" s="2" t="n">
         <v>43831</v>
       </c>
     </row>
@@ -7584,7 +7596,7 @@
       <c r="Q123" t="n">
         <v>-130</v>
       </c>
-      <c r="R123" s="1" t="n">
+      <c r="R123" s="2" t="n">
         <v>43862</v>
       </c>
     </row>
@@ -7642,7 +7654,7 @@
       <c r="Q124" t="n">
         <v>-266</v>
       </c>
-      <c r="R124" s="1" t="n">
+      <c r="R124" s="2" t="n">
         <v>43891</v>
       </c>
     </row>
@@ -7700,7 +7712,7 @@
       <c r="Q125" t="n">
         <v>40</v>
       </c>
-      <c r="R125" s="1" t="n">
+      <c r="R125" s="2" t="n">
         <v>43922</v>
       </c>
     </row>
@@ -7758,7 +7770,7 @@
       <c r="Q126" t="n">
         <v>-35</v>
       </c>
-      <c r="R126" s="1" t="n">
+      <c r="R126" s="2" t="n">
         <v>43952</v>
       </c>
     </row>
@@ -7816,7 +7828,7 @@
       <c r="Q127" t="n">
         <v>-60</v>
       </c>
-      <c r="R127" s="1" t="n">
+      <c r="R127" s="2" t="n">
         <v>43983</v>
       </c>
     </row>
@@ -7874,7 +7886,7 @@
       <c r="Q128" t="n">
         <v>85</v>
       </c>
-      <c r="R128" s="1" t="n">
+      <c r="R128" s="2" t="n">
         <v>44013</v>
       </c>
     </row>
@@ -7932,7 +7944,7 @@
       <c r="Q129" t="n">
         <v>150</v>
       </c>
-      <c r="R129" s="1" t="n">
+      <c r="R129" s="2" t="n">
         <v>44044</v>
       </c>
     </row>
@@ -7990,7 +8002,7 @@
       <c r="Q130" t="n">
         <v>206</v>
       </c>
-      <c r="R130" s="1" t="n">
+      <c r="R130" s="2" t="n">
         <v>44075</v>
       </c>
     </row>
@@ -8048,7 +8060,7 @@
       <c r="Q131" t="n">
         <v>-23</v>
       </c>
-      <c r="R131" s="1" t="n">
+      <c r="R131" s="2" t="n">
         <v>44105</v>
       </c>
     </row>
@@ -8106,7 +8118,7 @@
       <c r="Q132" t="n">
         <v>174</v>
       </c>
-      <c r="R132" s="1" t="n">
+      <c r="R132" s="2" t="n">
         <v>44136</v>
       </c>
     </row>
@@ -8164,7 +8176,7 @@
       <c r="Q133" t="n">
         <v>-34</v>
       </c>
-      <c r="R133" s="1" t="n">
+      <c r="R133" s="2" t="n">
         <v>44166</v>
       </c>
     </row>
@@ -8222,7 +8234,7 @@
       <c r="Q134" t="n">
         <v>44</v>
       </c>
-      <c r="R134" s="1" t="n">
+      <c r="R134" s="2" t="n">
         <v>44197</v>
       </c>
     </row>
@@ -8280,7 +8292,7 @@
       <c r="Q135" t="n">
         <v>146</v>
       </c>
-      <c r="R135" s="1" t="n">
+      <c r="R135" s="2" t="n">
         <v>44228</v>
       </c>
     </row>
@@ -8338,7 +8350,7 @@
       <c r="Q136" t="n">
         <v>44</v>
       </c>
-      <c r="R136" s="1" t="n">
+      <c r="R136" s="2" t="n">
         <v>44256</v>
       </c>
     </row>
@@ -8396,7 +8408,7 @@
       <c r="Q137" t="n">
         <v>282</v>
       </c>
-      <c r="R137" s="1" t="n">
+      <c r="R137" s="2" t="n">
         <v>44287</v>
       </c>
     </row>
@@ -8454,7 +8466,7 @@
       <c r="Q138" t="n">
         <v>152</v>
       </c>
-      <c r="R138" s="1" t="n">
+      <c r="R138" s="2" t="n">
         <v>44317</v>
       </c>
     </row>
@@ -8512,7 +8524,7 @@
       <c r="Q139" t="n">
         <v>-23</v>
       </c>
-      <c r="R139" s="1" t="n">
+      <c r="R139" s="2" t="n">
         <v>44348</v>
       </c>
     </row>
@@ -8570,7 +8582,7 @@
       <c r="Q140" t="n">
         <v>53</v>
       </c>
-      <c r="R140" s="1" t="n">
+      <c r="R140" s="2" t="n">
         <v>44378</v>
       </c>
     </row>
@@ -8628,7 +8640,7 @@
       <c r="Q141" t="n">
         <v>81</v>
       </c>
-      <c r="R141" s="1" t="n">
+      <c r="R141" s="2" t="n">
         <v>44409</v>
       </c>
     </row>
@@ -8686,7 +8698,7 @@
       <c r="Q142" t="n">
         <v>50</v>
       </c>
-      <c r="R142" s="1" t="n">
+      <c r="R142" s="2" t="n">
         <v>44440</v>
       </c>
     </row>
@@ -8744,7 +8756,7 @@
       <c r="Q143" t="n">
         <v>115</v>
       </c>
-      <c r="R143" s="1" t="n">
+      <c r="R143" s="2" t="n">
         <v>44470</v>
       </c>
     </row>
@@ -8802,7 +8814,7 @@
       <c r="Q144" t="n">
         <v>-106</v>
       </c>
-      <c r="R144" s="1" t="n">
+      <c r="R144" s="2" t="n">
         <v>44501</v>
       </c>
     </row>
@@ -8860,7 +8872,7 @@
       <c r="Q145" t="n">
         <v>112</v>
       </c>
-      <c r="R145" s="1" t="n">
+      <c r="R145" s="2" t="n">
         <v>44531</v>
       </c>
     </row>
@@ -8918,7 +8930,7 @@
       <c r="Q146" t="n">
         <v>-158</v>
       </c>
-      <c r="R146" s="1" t="n">
+      <c r="R146" s="2" t="n">
         <v>44562</v>
       </c>
     </row>
@@ -8976,7 +8988,7 @@
       <c r="Q147" t="n">
         <v>-43</v>
       </c>
-      <c r="R147" s="1" t="n">
+      <c r="R147" s="2" t="n">
         <v>44593</v>
       </c>
     </row>
@@ -9034,7 +9046,7 @@
       <c r="Q148" t="n">
         <v>-190</v>
       </c>
-      <c r="R148" s="1" t="n">
+      <c r="R148" s="2" t="n">
         <v>44621</v>
       </c>
     </row>
@@ -9092,7 +9104,7 @@
       <c r="Q149" t="n">
         <v>-107</v>
       </c>
-      <c r="R149" s="1" t="n">
+      <c r="R149" s="2" t="n">
         <v>44652</v>
       </c>
     </row>
@@ -9150,7 +9162,7 @@
       <c r="Q150" t="n">
         <v>-92</v>
       </c>
-      <c r="R150" s="1" t="n">
+      <c r="R150" s="2" t="n">
         <v>44682</v>
       </c>
     </row>
@@ -9208,7 +9220,7 @@
       <c r="Q151" t="n">
         <v>-123</v>
       </c>
-      <c r="R151" s="1" t="n">
+      <c r="R151" s="2" t="n">
         <v>44713</v>
       </c>
     </row>
@@ -9266,7 +9278,7 @@
       <c r="Q152" t="n">
         <v>60</v>
       </c>
-      <c r="R152" s="1" t="n">
+      <c r="R152" s="2" t="n">
         <v>44743</v>
       </c>
     </row>
@@ -9324,7 +9336,7 @@
       <c r="Q153" t="n">
         <v>53</v>
       </c>
-      <c r="R153" s="1" t="n">
+      <c r="R153" s="2" t="n">
         <v>44774</v>
       </c>
     </row>
@@ -9382,7 +9394,7 @@
       <c r="Q154" t="n">
         <v>1</v>
       </c>
-      <c r="R154" s="1" t="n">
+      <c r="R154" s="2" t="n">
         <v>44805</v>
       </c>
     </row>
@@ -9440,7 +9452,7 @@
       <c r="Q155" t="n">
         <v>34</v>
       </c>
-      <c r="R155" s="1" t="n">
+      <c r="R155" s="2" t="n">
         <v>44835</v>
       </c>
     </row>
@@ -9498,7 +9510,7 @@
       <c r="Q156" t="n">
         <v>-15</v>
       </c>
-      <c r="R156" s="1" t="n">
+      <c r="R156" s="2" t="n">
         <v>44866</v>
       </c>
     </row>
@@ -9556,7 +9568,7 @@
       <c r="Q157" t="n">
         <v>211</v>
       </c>
-      <c r="R157" s="1" t="n">
+      <c r="R157" s="2" t="n">
         <v>44896</v>
       </c>
     </row>
@@ -9614,7 +9626,7 @@
       <c r="Q158" t="n">
         <v>-228</v>
       </c>
-      <c r="R158" s="1" t="n">
+      <c r="R158" s="2" t="n">
         <v>44927</v>
       </c>
     </row>
@@ -9672,7 +9684,7 @@
       <c r="Q159" t="n">
         <v>157</v>
       </c>
-      <c r="R159" s="1" t="n">
+      <c r="R159" s="2" t="n">
         <v>44958</v>
       </c>
     </row>
@@ -9730,7 +9742,7 @@
       <c r="Q160" t="n">
         <v>77</v>
       </c>
-      <c r="R160" s="1" t="n">
+      <c r="R160" s="2" t="n">
         <v>44986</v>
       </c>
     </row>
@@ -9788,7 +9800,7 @@
       <c r="Q161" t="n">
         <v>60</v>
       </c>
-      <c r="R161" s="1" t="n">
+      <c r="R161" s="2" t="n">
         <v>45017</v>
       </c>
     </row>
@@ -9846,7 +9858,7 @@
       <c r="Q162" t="n">
         <v>21</v>
       </c>
-      <c r="R162" s="1" t="n">
+      <c r="R162" s="2" t="n">
         <v>45047</v>
       </c>
     </row>
@@ -9904,7 +9916,7 @@
       <c r="Q163" t="n">
         <v>190</v>
       </c>
-      <c r="R163" s="1" t="n">
+      <c r="R163" s="2" t="n">
         <v>45078</v>
       </c>
     </row>
@@ -9962,7 +9974,7 @@
       <c r="Q164" t="n">
         <v>-81</v>
       </c>
-      <c r="R164" s="1" t="n">
+      <c r="R164" s="2" t="n">
         <v>45108</v>
       </c>
     </row>
@@ -10020,7 +10032,7 @@
       <c r="Q165" t="n">
         <v>89</v>
       </c>
-      <c r="R165" s="1" t="n">
+      <c r="R165" s="2" t="n">
         <v>45139</v>
       </c>
     </row>
@@ -10078,7 +10090,7 @@
       <c r="Q166" t="n">
         <v>197</v>
       </c>
-      <c r="R166" s="1" t="n">
+      <c r="R166" s="2" t="n">
         <v>45170</v>
       </c>
     </row>
@@ -10136,7 +10148,7 @@
       <c r="Q167" t="n">
         <v>-53</v>
       </c>
-      <c r="R167" s="1" t="n">
+      <c r="R167" s="2" t="n">
         <v>45200</v>
       </c>
     </row>
@@ -10194,7 +10206,7 @@
       <c r="Q168" t="n">
         <v>-21</v>
       </c>
-      <c r="R168" s="1" t="n">
+      <c r="R168" s="2" t="n">
         <v>45231</v>
       </c>
     </row>
@@ -10252,7 +10264,7 @@
       <c r="Q169" t="n">
         <v>149</v>
       </c>
-      <c r="R169" s="1" t="n">
+      <c r="R169" s="2" t="n">
         <v>45261</v>
       </c>
     </row>
@@ -10310,7 +10322,7 @@
       <c r="Q170" t="n">
         <v>-157</v>
       </c>
-      <c r="R170" s="1" t="n">
+      <c r="R170" s="2" t="n">
         <v>45292</v>
       </c>
     </row>
@@ -10368,7 +10380,7 @@
       <c r="Q171" t="n">
         <v>-123</v>
       </c>
-      <c r="R171" s="1" t="n">
+      <c r="R171" s="2" t="n">
         <v>45323</v>
       </c>
     </row>
@@ -10426,7 +10438,7 @@
       <c r="Q172" t="n">
         <v>-206</v>
       </c>
-      <c r="R172" s="1" t="n">
+      <c r="R172" s="2" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -10484,7 +10496,7 @@
       <c r="Q173" t="n">
         <v>520</v>
       </c>
-      <c r="R173" s="1" t="n">
+      <c r="R173" s="2" t="n">
         <v>45383</v>
       </c>
     </row>
@@ -10542,7 +10554,7 @@
       <c r="Q174" t="n">
         <v>-152</v>
       </c>
-      <c r="R174" s="1" t="n">
+      <c r="R174" s="2" t="n">
         <v>45413</v>
       </c>
     </row>
@@ -10600,7 +10612,7 @@
       <c r="Q175" t="n">
         <v>3</v>
       </c>
-      <c r="R175" s="1" t="n">
+      <c r="R175" s="2" t="n">
         <v>45444</v>
       </c>
     </row>
@@ -10658,7 +10670,7 @@
       <c r="Q176" t="n">
         <v>92</v>
       </c>
-      <c r="R176" s="1" t="n">
+      <c r="R176" s="2" t="n">
         <v>45474</v>
       </c>
     </row>
@@ -10716,7 +10728,7 @@
       <c r="Q177" t="n">
         <v>-5</v>
       </c>
-      <c r="R177" s="1" t="n">
+      <c r="R177" s="2" t="n">
         <v>45505</v>
       </c>
     </row>
@@ -10774,7 +10786,7 @@
       <c r="Q178" t="n">
         <v>-19</v>
       </c>
-      <c r="R178" s="1" t="n">
+      <c r="R178" s="2" t="n">
         <v>45536</v>
       </c>
     </row>
@@ -10832,7 +10844,7 @@
       <c r="Q179" t="n">
         <v>-15</v>
       </c>
-      <c r="R179" s="1" t="n">
+      <c r="R179" s="2" t="n">
         <v>45566</v>
       </c>
     </row>
@@ -10890,7 +10902,7 @@
       <c r="Q180" t="n">
         <v>21</v>
       </c>
-      <c r="R180" s="1" t="n">
+      <c r="R180" s="2" t="n">
         <v>45597</v>
       </c>
     </row>
@@ -10948,7 +10960,7 @@
       <c r="Q181" t="n">
         <v>113</v>
       </c>
-      <c r="R181" s="1" t="n">
+      <c r="R181" s="2" t="n">
         <v>45627</v>
       </c>
     </row>
@@ -11006,7 +11018,7 @@
       <c r="Q182" t="n">
         <v>-154</v>
       </c>
-      <c r="R182" s="1" t="n">
+      <c r="R182" s="2" t="n">
         <v>45658</v>
       </c>
     </row>
@@ -11064,7 +11076,7 @@
       <c r="Q183" t="n">
         <v>8</v>
       </c>
-      <c r="R183" s="1" t="n">
+      <c r="R183" s="2" t="n">
         <v>45689</v>
       </c>
     </row>
@@ -11122,7 +11134,7 @@
       <c r="Q184" t="n">
         <v>-9</v>
       </c>
-      <c r="R184" s="1" t="n">
+      <c r="R184" s="2" t="n">
         <v>45717</v>
       </c>
     </row>
@@ -11180,7 +11192,7 @@
       <c r="Q185" t="n">
         <v>-104</v>
       </c>
-      <c r="R185" s="1" t="n">
+      <c r="R185" s="2" t="n">
         <v>45748</v>
       </c>
     </row>
@@ -11238,7 +11250,7 @@
       <c r="Q186" t="n">
         <v>-25</v>
       </c>
-      <c r="R186" s="1" t="n">
+      <c r="R186" s="2" t="n">
         <v>45778</v>
       </c>
     </row>
@@ -11296,7 +11308,7 @@
       <c r="Q187" t="n">
         <v>-82</v>
       </c>
-      <c r="R187" s="1" t="n">
+      <c r="R187" s="2" t="n">
         <v>45809</v>
       </c>
     </row>
@@ -11354,7 +11366,7 @@
       <c r="Q188" t="n">
         <v>-153</v>
       </c>
-      <c r="R188" s="1" t="n">
+      <c r="R188" s="2" t="n">
         <v>45839</v>
       </c>
     </row>
@@ -11412,7 +11424,7 @@
       <c r="Q189" t="n">
         <v>-21</v>
       </c>
-      <c r="R189" s="1" t="n">
+      <c r="R189" s="2" t="n">
         <v>45870</v>
       </c>
     </row>
@@ -11470,7 +11482,7 @@
       <c r="Q190" t="n">
         <v>89</v>
       </c>
-      <c r="R190" s="1" t="n">
+      <c r="R190" s="2" t="n">
         <v>45901</v>
       </c>
     </row>
@@ -11528,7 +11540,7 @@
       <c r="Q191" t="n">
         <v>-7</v>
       </c>
-      <c r="R191" s="1" t="n">
+      <c r="R191" s="2" t="n">
         <v>45931</v>
       </c>
     </row>
@@ -11586,7 +11598,7 @@
       <c r="Q192" t="n">
         <v>13</v>
       </c>
-      <c r="R192" s="1" t="n">
+      <c r="R192" s="2" t="n">
         <v>45962</v>
       </c>
     </row>
@@ -11644,7 +11656,7 @@
       <c r="Q193" t="n">
         <v>-99</v>
       </c>
-      <c r="R193" s="1" t="n">
+      <c r="R193" s="2" t="n">
         <v>45992</v>
       </c>
     </row>
@@ -11702,7 +11714,7 @@
       <c r="Q194" t="n">
         <v>-314</v>
       </c>
-      <c r="R194" s="1" t="n">
+      <c r="R194" s="2" t="n">
         <v>46023</v>
       </c>
     </row>
@@ -11760,7 +11772,7 @@
       <c r="Q195" t="n">
         <v>-193</v>
       </c>
-      <c r="R195" s="1" t="n">
+      <c r="R195" s="2" t="n">
         <v>46054</v>
       </c>
     </row>
@@ -11818,7 +11830,7 @@
       <c r="Q196" t="n">
         <v>-245</v>
       </c>
-      <c r="R196" s="1" t="n">
+      <c r="R196" s="2" t="n">
         <v>46082</v>
       </c>
     </row>
@@ -11876,7 +11888,7 @@
       <c r="Q197" t="n">
         <v>-143</v>
       </c>
-      <c r="R197" s="1" t="n">
+      <c r="R197" s="2" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -11934,7 +11946,7 @@
       <c r="Q198" t="n">
         <v>-164</v>
       </c>
-      <c r="R198" s="1" t="n">
+      <c r="R198" s="2" t="n">
         <v>46143</v>
       </c>
     </row>
@@ -11992,7 +12004,7 @@
       <c r="Q199" t="n">
         <v>-729</v>
       </c>
-      <c r="R199" s="1" t="n">
+      <c r="R199" s="2" t="n">
         <v>46174</v>
       </c>
     </row>
@@ -12050,7 +12062,7 @@
       <c r="Q200" t="n">
         <v>-68</v>
       </c>
-      <c r="R200" s="1" t="n">
+      <c r="R200" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -12108,7 +12120,7 @@
       <c r="Q201" t="n">
         <v>-18</v>
       </c>
-      <c r="R201" s="1" t="n">
+      <c r="R201" s="2" t="n">
         <v>46235</v>
       </c>
     </row>

--- a/cari acik/odemeler_dengesi_raw.xlsx
+++ b/cari acik/odemeler_dengesi_raw.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,92 +421,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Cari İşlemler Dengesi</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Dış Ticaret Dengesi</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Toplam Mal İhracatı</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Toplam Mal İthalatı</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Parasal Olmayan Altın (net)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Altın İhracatı</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Altın İthalatı</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Hizmetler Dengesi</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Hizmet Gelirleri</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Hizmet Giderleri</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Taşımacılık - Gelir</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Taşımacılık - Gider</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Seyahat - Gelir</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Seyahat - Gider</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Birincil Gelir Dengesi</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>İkincil Gelir Dengesi</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Tarih_dt</t>
         </is>
@@ -578,7 +566,7 @@
       <c r="Q2" t="n">
         <v>115</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="R2" s="1" t="n">
         <v>40179</v>
       </c>
     </row>
@@ -636,7 +624,7 @@
       <c r="Q3" t="n">
         <v>72</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="R3" s="1" t="n">
         <v>40210</v>
       </c>
     </row>
@@ -694,7 +682,7 @@
       <c r="Q4" t="n">
         <v>114</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="R4" s="1" t="n">
         <v>40238</v>
       </c>
     </row>
@@ -752,7 +740,7 @@
       <c r="Q5" t="n">
         <v>82</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="R5" s="1" t="n">
         <v>40269</v>
       </c>
     </row>
@@ -810,7 +798,7 @@
       <c r="Q6" t="n">
         <v>73</v>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="R6" s="1" t="n">
         <v>40299</v>
       </c>
     </row>
@@ -868,7 +856,7 @@
       <c r="Q7" t="n">
         <v>121</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="R7" s="1" t="n">
         <v>40330</v>
       </c>
     </row>
@@ -926,7 +914,7 @@
       <c r="Q8" t="n">
         <v>109</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R8" s="1" t="n">
         <v>40360</v>
       </c>
     </row>
@@ -984,7 +972,7 @@
       <c r="Q9" t="n">
         <v>155</v>
       </c>
-      <c r="R9" s="2" t="n">
+      <c r="R9" s="1" t="n">
         <v>40391</v>
       </c>
     </row>
@@ -1042,7 +1030,7 @@
       <c r="Q10" t="n">
         <v>159</v>
       </c>
-      <c r="R10" s="2" t="n">
+      <c r="R10" s="1" t="n">
         <v>40422</v>
       </c>
     </row>
@@ -1100,7 +1088,7 @@
       <c r="Q11" t="n">
         <v>183</v>
       </c>
-      <c r="R11" s="2" t="n">
+      <c r="R11" s="1" t="n">
         <v>40452</v>
       </c>
     </row>
@@ -1158,7 +1146,7 @@
       <c r="Q12" t="n">
         <v>100</v>
       </c>
-      <c r="R12" s="2" t="n">
+      <c r="R12" s="1" t="n">
         <v>40483</v>
       </c>
     </row>
@@ -1216,7 +1204,7 @@
       <c r="Q13" t="n">
         <v>192</v>
       </c>
-      <c r="R13" s="2" t="n">
+      <c r="R13" s="1" t="n">
         <v>40513</v>
       </c>
     </row>
@@ -1274,7 +1262,7 @@
       <c r="Q14" t="n">
         <v>222</v>
       </c>
-      <c r="R14" s="2" t="n">
+      <c r="R14" s="1" t="n">
         <v>40544</v>
       </c>
     </row>
@@ -1332,7 +1320,7 @@
       <c r="Q15" t="n">
         <v>85</v>
       </c>
-      <c r="R15" s="2" t="n">
+      <c r="R15" s="1" t="n">
         <v>40575</v>
       </c>
     </row>
@@ -1390,7 +1378,7 @@
       <c r="Q16" t="n">
         <v>77</v>
       </c>
-      <c r="R16" s="2" t="n">
+      <c r="R16" s="1" t="n">
         <v>40603</v>
       </c>
     </row>
@@ -1448,7 +1436,7 @@
       <c r="Q17" t="n">
         <v>49</v>
       </c>
-      <c r="R17" s="2" t="n">
+      <c r="R17" s="1" t="n">
         <v>40634</v>
       </c>
     </row>
@@ -1506,7 +1494,7 @@
       <c r="Q18" t="n">
         <v>139</v>
       </c>
-      <c r="R18" s="2" t="n">
+      <c r="R18" s="1" t="n">
         <v>40664</v>
       </c>
     </row>
@@ -1564,7 +1552,7 @@
       <c r="Q19" t="n">
         <v>99</v>
       </c>
-      <c r="R19" s="2" t="n">
+      <c r="R19" s="1" t="n">
         <v>40695</v>
       </c>
     </row>
@@ -1622,7 +1610,7 @@
       <c r="Q20" t="n">
         <v>103</v>
       </c>
-      <c r="R20" s="2" t="n">
+      <c r="R20" s="1" t="n">
         <v>40725</v>
       </c>
     </row>
@@ -1680,7 +1668,7 @@
       <c r="Q21" t="n">
         <v>241</v>
       </c>
-      <c r="R21" s="2" t="n">
+      <c r="R21" s="1" t="n">
         <v>40756</v>
       </c>
     </row>
@@ -1738,7 +1726,7 @@
       <c r="Q22" t="n">
         <v>149</v>
       </c>
-      <c r="R22" s="2" t="n">
+      <c r="R22" s="1" t="n">
         <v>40787</v>
       </c>
     </row>
@@ -1796,7 +1784,7 @@
       <c r="Q23" t="n">
         <v>67</v>
       </c>
-      <c r="R23" s="2" t="n">
+      <c r="R23" s="1" t="n">
         <v>40817</v>
       </c>
     </row>
@@ -1854,7 +1842,7 @@
       <c r="Q24" t="n">
         <v>106</v>
       </c>
-      <c r="R24" s="2" t="n">
+      <c r="R24" s="1" t="n">
         <v>40848</v>
       </c>
     </row>
@@ -1912,7 +1900,7 @@
       <c r="Q25" t="n">
         <v>382</v>
       </c>
-      <c r="R25" s="2" t="n">
+      <c r="R25" s="1" t="n">
         <v>40878</v>
       </c>
     </row>
@@ -1970,7 +1958,7 @@
       <c r="Q26" t="n">
         <v>69</v>
       </c>
-      <c r="R26" s="2" t="n">
+      <c r="R26" s="1" t="n">
         <v>40909</v>
       </c>
     </row>
@@ -2028,7 +2016,7 @@
       <c r="Q27" t="n">
         <v>224</v>
       </c>
-      <c r="R27" s="2" t="n">
+      <c r="R27" s="1" t="n">
         <v>40940</v>
       </c>
     </row>
@@ -2086,7 +2074,7 @@
       <c r="Q28" t="n">
         <v>57</v>
       </c>
-      <c r="R28" s="2" t="n">
+      <c r="R28" s="1" t="n">
         <v>40969</v>
       </c>
     </row>
@@ -2144,7 +2132,7 @@
       <c r="Q29" t="n">
         <v>105</v>
       </c>
-      <c r="R29" s="2" t="n">
+      <c r="R29" s="1" t="n">
         <v>41000</v>
       </c>
     </row>
@@ -2202,7 +2190,7 @@
       <c r="Q30" t="n">
         <v>90</v>
       </c>
-      <c r="R30" s="2" t="n">
+      <c r="R30" s="1" t="n">
         <v>41030</v>
       </c>
     </row>
@@ -2260,7 +2248,7 @@
       <c r="Q31" t="n">
         <v>73</v>
       </c>
-      <c r="R31" s="2" t="n">
+      <c r="R31" s="1" t="n">
         <v>41061</v>
       </c>
     </row>
@@ -2318,7 +2306,7 @@
       <c r="Q32" t="n">
         <v>72</v>
       </c>
-      <c r="R32" s="2" t="n">
+      <c r="R32" s="1" t="n">
         <v>41091</v>
       </c>
     </row>
@@ -2376,7 +2364,7 @@
       <c r="Q33" t="n">
         <v>156</v>
       </c>
-      <c r="R33" s="2" t="n">
+      <c r="R33" s="1" t="n">
         <v>41122</v>
       </c>
     </row>
@@ -2434,7 +2422,7 @@
       <c r="Q34" t="n">
         <v>122</v>
       </c>
-      <c r="R34" s="2" t="n">
+      <c r="R34" s="1" t="n">
         <v>41153</v>
       </c>
     </row>
@@ -2492,7 +2480,7 @@
       <c r="Q35" t="n">
         <v>89</v>
       </c>
-      <c r="R35" s="2" t="n">
+      <c r="R35" s="1" t="n">
         <v>41183</v>
       </c>
     </row>
@@ -2550,7 +2538,7 @@
       <c r="Q36" t="n">
         <v>116</v>
       </c>
-      <c r="R36" s="2" t="n">
+      <c r="R36" s="1" t="n">
         <v>41214</v>
       </c>
     </row>
@@ -2608,7 +2596,7 @@
       <c r="Q37" t="n">
         <v>278</v>
       </c>
-      <c r="R37" s="2" t="n">
+      <c r="R37" s="1" t="n">
         <v>41244</v>
       </c>
     </row>
@@ -2666,7 +2654,7 @@
       <c r="Q38" t="n">
         <v>49</v>
       </c>
-      <c r="R38" s="2" t="n">
+      <c r="R38" s="1" t="n">
         <v>41275</v>
       </c>
     </row>
@@ -2724,7 +2712,7 @@
       <c r="Q39" t="n">
         <v>161</v>
       </c>
-      <c r="R39" s="2" t="n">
+      <c r="R39" s="1" t="n">
         <v>41306</v>
       </c>
     </row>
@@ -2782,7 +2770,7 @@
       <c r="Q40" t="n">
         <v>66</v>
       </c>
-      <c r="R40" s="2" t="n">
+      <c r="R40" s="1" t="n">
         <v>41334</v>
       </c>
     </row>
@@ -2840,7 +2828,7 @@
       <c r="Q41" t="n">
         <v>45</v>
       </c>
-      <c r="R41" s="2" t="n">
+      <c r="R41" s="1" t="n">
         <v>41365</v>
       </c>
     </row>
@@ -2898,7 +2886,7 @@
       <c r="Q42" t="n">
         <v>159</v>
       </c>
-      <c r="R42" s="2" t="n">
+      <c r="R42" s="1" t="n">
         <v>41395</v>
       </c>
     </row>
@@ -2956,7 +2944,7 @@
       <c r="Q43" t="n">
         <v>92</v>
       </c>
-      <c r="R43" s="2" t="n">
+      <c r="R43" s="1" t="n">
         <v>41426</v>
       </c>
     </row>
@@ -3014,7 +3002,7 @@
       <c r="Q44" t="n">
         <v>107</v>
       </c>
-      <c r="R44" s="2" t="n">
+      <c r="R44" s="1" t="n">
         <v>41456</v>
       </c>
     </row>
@@ -3072,7 +3060,7 @@
       <c r="Q45" t="n">
         <v>108</v>
       </c>
-      <c r="R45" s="2" t="n">
+      <c r="R45" s="1" t="n">
         <v>41487</v>
       </c>
     </row>
@@ -3130,7 +3118,7 @@
       <c r="Q46" t="n">
         <v>110</v>
       </c>
-      <c r="R46" s="2" t="n">
+      <c r="R46" s="1" t="n">
         <v>41518</v>
       </c>
     </row>
@@ -3188,7 +3176,7 @@
       <c r="Q47" t="n">
         <v>113</v>
       </c>
-      <c r="R47" s="2" t="n">
+      <c r="R47" s="1" t="n">
         <v>41548</v>
       </c>
     </row>
@@ -3246,7 +3234,7 @@
       <c r="Q48" t="n">
         <v>115</v>
       </c>
-      <c r="R48" s="2" t="n">
+      <c r="R48" s="1" t="n">
         <v>41579</v>
       </c>
     </row>
@@ -3304,7 +3292,7 @@
       <c r="Q49" t="n">
         <v>152</v>
       </c>
-      <c r="R49" s="2" t="n">
+      <c r="R49" s="1" t="n">
         <v>41609</v>
       </c>
     </row>
@@ -3362,7 +3350,7 @@
       <c r="Q50" t="n">
         <v>35</v>
       </c>
-      <c r="R50" s="2" t="n">
+      <c r="R50" s="1" t="n">
         <v>41640</v>
       </c>
     </row>
@@ -3420,7 +3408,7 @@
       <c r="Q51" t="n">
         <v>157</v>
       </c>
-      <c r="R51" s="2" t="n">
+      <c r="R51" s="1" t="n">
         <v>41671</v>
       </c>
     </row>
@@ -3478,7 +3466,7 @@
       <c r="Q52" t="n">
         <v>222</v>
       </c>
-      <c r="R52" s="2" t="n">
+      <c r="R52" s="1" t="n">
         <v>41699</v>
       </c>
     </row>
@@ -3536,7 +3524,7 @@
       <c r="Q53" t="n">
         <v>37</v>
       </c>
-      <c r="R53" s="2" t="n">
+      <c r="R53" s="1" t="n">
         <v>41730</v>
       </c>
     </row>
@@ -3594,7 +3582,7 @@
       <c r="Q54" t="n">
         <v>86</v>
       </c>
-      <c r="R54" s="2" t="n">
+      <c r="R54" s="1" t="n">
         <v>41760</v>
       </c>
     </row>
@@ -3652,7 +3640,7 @@
       <c r="Q55" t="n">
         <v>111</v>
       </c>
-      <c r="R55" s="2" t="n">
+      <c r="R55" s="1" t="n">
         <v>41791</v>
       </c>
     </row>
@@ -3710,7 +3698,7 @@
       <c r="Q56" t="n">
         <v>19</v>
       </c>
-      <c r="R56" s="2" t="n">
+      <c r="R56" s="1" t="n">
         <v>41821</v>
       </c>
     </row>
@@ -3768,7 +3756,7 @@
       <c r="Q57" t="n">
         <v>121</v>
       </c>
-      <c r="R57" s="2" t="n">
+      <c r="R57" s="1" t="n">
         <v>41852</v>
       </c>
     </row>
@@ -3826,7 +3814,7 @@
       <c r="Q58" t="n">
         <v>263</v>
       </c>
-      <c r="R58" s="2" t="n">
+      <c r="R58" s="1" t="n">
         <v>41883</v>
       </c>
     </row>
@@ -3884,7 +3872,7 @@
       <c r="Q59" t="n">
         <v>88</v>
       </c>
-      <c r="R59" s="2" t="n">
+      <c r="R59" s="1" t="n">
         <v>41913</v>
       </c>
     </row>
@@ -3942,7 +3930,7 @@
       <c r="Q60" t="n">
         <v>169</v>
       </c>
-      <c r="R60" s="2" t="n">
+      <c r="R60" s="1" t="n">
         <v>41944</v>
       </c>
     </row>
@@ -4000,7 +3988,7 @@
       <c r="Q61" t="n">
         <v>212</v>
       </c>
-      <c r="R61" s="2" t="n">
+      <c r="R61" s="1" t="n">
         <v>41974</v>
       </c>
     </row>
@@ -4058,7 +4046,7 @@
       <c r="Q62" t="n">
         <v>15</v>
       </c>
-      <c r="R62" s="2" t="n">
+      <c r="R62" s="1" t="n">
         <v>42005</v>
       </c>
     </row>
@@ -4116,7 +4104,7 @@
       <c r="Q63" t="n">
         <v>231</v>
       </c>
-      <c r="R63" s="2" t="n">
+      <c r="R63" s="1" t="n">
         <v>42036</v>
       </c>
     </row>
@@ -4174,7 +4162,7 @@
       <c r="Q64" t="n">
         <v>145</v>
       </c>
-      <c r="R64" s="2" t="n">
+      <c r="R64" s="1" t="n">
         <v>42064</v>
       </c>
     </row>
@@ -4232,7 +4220,7 @@
       <c r="Q65" t="n">
         <v>62</v>
       </c>
-      <c r="R65" s="2" t="n">
+      <c r="R65" s="1" t="n">
         <v>42095</v>
       </c>
     </row>
@@ -4290,7 +4278,7 @@
       <c r="Q66" t="n">
         <v>21</v>
       </c>
-      <c r="R66" s="2" t="n">
+      <c r="R66" s="1" t="n">
         <v>42125</v>
       </c>
     </row>
@@ -4348,7 +4336,7 @@
       <c r="Q67" t="n">
         <v>86</v>
       </c>
-      <c r="R67" s="2" t="n">
+      <c r="R67" s="1" t="n">
         <v>42156</v>
       </c>
     </row>
@@ -4406,7 +4394,7 @@
       <c r="Q68" t="n">
         <v>125</v>
       </c>
-      <c r="R68" s="2" t="n">
+      <c r="R68" s="1" t="n">
         <v>42186</v>
       </c>
     </row>
@@ -4464,7 +4452,7 @@
       <c r="Q69" t="n">
         <v>109</v>
       </c>
-      <c r="R69" s="2" t="n">
+      <c r="R69" s="1" t="n">
         <v>42217</v>
       </c>
     </row>
@@ -4522,7 +4510,7 @@
       <c r="Q70" t="n">
         <v>110</v>
       </c>
-      <c r="R70" s="2" t="n">
+      <c r="R70" s="1" t="n">
         <v>42248</v>
       </c>
     </row>
@@ -4580,7 +4568,7 @@
       <c r="Q71" t="n">
         <v>55</v>
       </c>
-      <c r="R71" s="2" t="n">
+      <c r="R71" s="1" t="n">
         <v>42278</v>
       </c>
     </row>
@@ -4638,7 +4626,7 @@
       <c r="Q72" t="n">
         <v>213</v>
       </c>
-      <c r="R72" s="2" t="n">
+      <c r="R72" s="1" t="n">
         <v>42309</v>
       </c>
     </row>
@@ -4696,7 +4684,7 @@
       <c r="Q73" t="n">
         <v>225</v>
       </c>
-      <c r="R73" s="2" t="n">
+      <c r="R73" s="1" t="n">
         <v>42339</v>
       </c>
     </row>
@@ -4754,7 +4742,7 @@
       <c r="Q74" t="n">
         <v>112</v>
       </c>
-      <c r="R74" s="2" t="n">
+      <c r="R74" s="1" t="n">
         <v>42370</v>
       </c>
     </row>
@@ -4812,7 +4800,7 @@
       <c r="Q75" t="n">
         <v>365</v>
       </c>
-      <c r="R75" s="2" t="n">
+      <c r="R75" s="1" t="n">
         <v>42401</v>
       </c>
     </row>
@@ -4870,7 +4858,7 @@
       <c r="Q76" t="n">
         <v>-19</v>
       </c>
-      <c r="R76" s="2" t="n">
+      <c r="R76" s="1" t="n">
         <v>42430</v>
       </c>
     </row>
@@ -4928,7 +4916,7 @@
       <c r="Q77" t="n">
         <v>292</v>
       </c>
-      <c r="R77" s="2" t="n">
+      <c r="R77" s="1" t="n">
         <v>42461</v>
       </c>
     </row>
@@ -4986,7 +4974,7 @@
       <c r="Q78" t="n">
         <v>-42</v>
       </c>
-      <c r="R78" s="2" t="n">
+      <c r="R78" s="1" t="n">
         <v>42491</v>
       </c>
     </row>
@@ -5044,7 +5032,7 @@
       <c r="Q79" t="n">
         <v>71</v>
       </c>
-      <c r="R79" s="2" t="n">
+      <c r="R79" s="1" t="n">
         <v>42522</v>
       </c>
     </row>
@@ -5102,7 +5090,7 @@
       <c r="Q80" t="n">
         <v>46</v>
       </c>
-      <c r="R80" s="2" t="n">
+      <c r="R80" s="1" t="n">
         <v>42552</v>
       </c>
     </row>
@@ -5160,7 +5148,7 @@
       <c r="Q81" t="n">
         <v>49</v>
       </c>
-      <c r="R81" s="2" t="n">
+      <c r="R81" s="1" t="n">
         <v>42583</v>
       </c>
     </row>
@@ -5218,7 +5206,7 @@
       <c r="Q82" t="n">
         <v>138</v>
       </c>
-      <c r="R82" s="2" t="n">
+      <c r="R82" s="1" t="n">
         <v>42614</v>
       </c>
     </row>
@@ -5276,7 +5264,7 @@
       <c r="Q83" t="n">
         <v>112</v>
       </c>
-      <c r="R83" s="2" t="n">
+      <c r="R83" s="1" t="n">
         <v>42644</v>
       </c>
     </row>
@@ -5334,7 +5322,7 @@
       <c r="Q84" t="n">
         <v>199</v>
       </c>
-      <c r="R84" s="2" t="n">
+      <c r="R84" s="1" t="n">
         <v>42675</v>
       </c>
     </row>
@@ -5392,7 +5380,7 @@
       <c r="Q85" t="n">
         <v>235</v>
       </c>
-      <c r="R85" s="2" t="n">
+      <c r="R85" s="1" t="n">
         <v>42705</v>
       </c>
     </row>
@@ -5450,7 +5438,7 @@
       <c r="Q86" t="n">
         <v>133</v>
       </c>
-      <c r="R86" s="2" t="n">
+      <c r="R86" s="1" t="n">
         <v>42736</v>
       </c>
     </row>
@@ -5508,7 +5496,7 @@
       <c r="Q87" t="n">
         <v>103</v>
       </c>
-      <c r="R87" s="2" t="n">
+      <c r="R87" s="1" t="n">
         <v>42767</v>
       </c>
     </row>
@@ -5566,7 +5554,7 @@
       <c r="Q88" t="n">
         <v>223</v>
       </c>
-      <c r="R88" s="2" t="n">
+      <c r="R88" s="1" t="n">
         <v>42795</v>
       </c>
     </row>
@@ -5624,7 +5612,7 @@
       <c r="Q89" t="n">
         <v>31</v>
       </c>
-      <c r="R89" s="2" t="n">
+      <c r="R89" s="1" t="n">
         <v>42826</v>
       </c>
     </row>
@@ -5682,7 +5670,7 @@
       <c r="Q90" t="n">
         <v>245</v>
       </c>
-      <c r="R90" s="2" t="n">
+      <c r="R90" s="1" t="n">
         <v>42856</v>
       </c>
     </row>
@@ -5740,7 +5728,7 @@
       <c r="Q91" t="n">
         <v>273</v>
       </c>
-      <c r="R91" s="2" t="n">
+      <c r="R91" s="1" t="n">
         <v>42887</v>
       </c>
     </row>
@@ -5798,7 +5786,7 @@
       <c r="Q92" t="n">
         <v>305</v>
       </c>
-      <c r="R92" s="2" t="n">
+      <c r="R92" s="1" t="n">
         <v>42917</v>
       </c>
     </row>
@@ -5856,7 +5844,7 @@
       <c r="Q93" t="n">
         <v>213</v>
       </c>
-      <c r="R93" s="2" t="n">
+      <c r="R93" s="1" t="n">
         <v>42948</v>
       </c>
     </row>
@@ -5914,7 +5902,7 @@
       <c r="Q94" t="n">
         <v>209</v>
       </c>
-      <c r="R94" s="2" t="n">
+      <c r="R94" s="1" t="n">
         <v>42979</v>
       </c>
     </row>
@@ -5972,7 +5960,7 @@
       <c r="Q95" t="n">
         <v>262</v>
       </c>
-      <c r="R95" s="2" t="n">
+      <c r="R95" s="1" t="n">
         <v>43009</v>
       </c>
     </row>
@@ -6030,7 +6018,7 @@
       <c r="Q96" t="n">
         <v>277</v>
       </c>
-      <c r="R96" s="2" t="n">
+      <c r="R96" s="1" t="n">
         <v>43040</v>
       </c>
     </row>
@@ -6088,7 +6076,7 @@
       <c r="Q97" t="n">
         <v>259</v>
       </c>
-      <c r="R97" s="2" t="n">
+      <c r="R97" s="1" t="n">
         <v>43070</v>
       </c>
     </row>
@@ -6146,7 +6134,7 @@
       <c r="Q98" t="n">
         <v>201</v>
       </c>
-      <c r="R98" s="2" t="n">
+      <c r="R98" s="1" t="n">
         <v>43101</v>
       </c>
     </row>
@@ -6204,7 +6192,7 @@
       <c r="Q99" t="n">
         <v>-9</v>
       </c>
-      <c r="R99" s="2" t="n">
+      <c r="R99" s="1" t="n">
         <v>43132</v>
       </c>
     </row>
@@ -6262,7 +6250,7 @@
       <c r="Q100" t="n">
         <v>-3</v>
       </c>
-      <c r="R100" s="2" t="n">
+      <c r="R100" s="1" t="n">
         <v>43160</v>
       </c>
     </row>
@@ -6320,7 +6308,7 @@
       <c r="Q101" t="n">
         <v>65</v>
       </c>
-      <c r="R101" s="2" t="n">
+      <c r="R101" s="1" t="n">
         <v>43191</v>
       </c>
     </row>
@@ -6378,7 +6366,7 @@
       <c r="Q102" t="n">
         <v>-145</v>
       </c>
-      <c r="R102" s="2" t="n">
+      <c r="R102" s="1" t="n">
         <v>43221</v>
       </c>
     </row>
@@ -6436,7 +6424,7 @@
       <c r="Q103" t="n">
         <v>35</v>
       </c>
-      <c r="R103" s="2" t="n">
+      <c r="R103" s="1" t="n">
         <v>43252</v>
       </c>
     </row>
@@ -6494,7 +6482,7 @@
       <c r="Q104" t="n">
         <v>62</v>
       </c>
-      <c r="R104" s="2" t="n">
+      <c r="R104" s="1" t="n">
         <v>43282</v>
       </c>
     </row>
@@ -6552,7 +6540,7 @@
       <c r="Q105" t="n">
         <v>28</v>
       </c>
-      <c r="R105" s="2" t="n">
+      <c r="R105" s="1" t="n">
         <v>43313</v>
       </c>
     </row>
@@ -6610,7 +6598,7 @@
       <c r="Q106" t="n">
         <v>104</v>
       </c>
-      <c r="R106" s="2" t="n">
+      <c r="R106" s="1" t="n">
         <v>43344</v>
       </c>
     </row>
@@ -6668,7 +6656,7 @@
       <c r="Q107" t="n">
         <v>111</v>
       </c>
-      <c r="R107" s="2" t="n">
+      <c r="R107" s="1" t="n">
         <v>43374</v>
       </c>
     </row>
@@ -6726,7 +6714,7 @@
       <c r="Q108" t="n">
         <v>212</v>
       </c>
-      <c r="R108" s="2" t="n">
+      <c r="R108" s="1" t="n">
         <v>43405</v>
       </c>
     </row>
@@ -6784,7 +6772,7 @@
       <c r="Q109" t="n">
         <v>120</v>
       </c>
-      <c r="R109" s="2" t="n">
+      <c r="R109" s="1" t="n">
         <v>43435</v>
       </c>
     </row>
@@ -6842,7 +6830,7 @@
       <c r="Q110" t="n">
         <v>92</v>
       </c>
-      <c r="R110" s="2" t="n">
+      <c r="R110" s="1" t="n">
         <v>43466</v>
       </c>
     </row>
@@ -6900,7 +6888,7 @@
       <c r="Q111" t="n">
         <v>-67</v>
       </c>
-      <c r="R111" s="2" t="n">
+      <c r="R111" s="1" t="n">
         <v>43497</v>
       </c>
     </row>
@@ -6958,7 +6946,7 @@
       <c r="Q112" t="n">
         <v>125</v>
       </c>
-      <c r="R112" s="2" t="n">
+      <c r="R112" s="1" t="n">
         <v>43525</v>
       </c>
     </row>
@@ -7016,7 +7004,7 @@
       <c r="Q113" t="n">
         <v>-16</v>
       </c>
-      <c r="R113" s="2" t="n">
+      <c r="R113" s="1" t="n">
         <v>43556</v>
       </c>
     </row>
@@ -7074,7 +7062,7 @@
       <c r="Q114" t="n">
         <v>-71</v>
       </c>
-      <c r="R114" s="2" t="n">
+      <c r="R114" s="1" t="n">
         <v>43586</v>
       </c>
     </row>
@@ -7132,7 +7120,7 @@
       <c r="Q115" t="n">
         <v>19</v>
       </c>
-      <c r="R115" s="2" t="n">
+      <c r="R115" s="1" t="n">
         <v>43617</v>
       </c>
     </row>
@@ -7190,7 +7178,7 @@
       <c r="Q116" t="n">
         <v>141</v>
       </c>
-      <c r="R116" s="2" t="n">
+      <c r="R116" s="1" t="n">
         <v>43647</v>
       </c>
     </row>
@@ -7248,7 +7236,7 @@
       <c r="Q117" t="n">
         <v>99</v>
       </c>
-      <c r="R117" s="2" t="n">
+      <c r="R117" s="1" t="n">
         <v>43678</v>
       </c>
     </row>
@@ -7306,7 +7294,7 @@
       <c r="Q118" t="n">
         <v>100</v>
       </c>
-      <c r="R118" s="2" t="n">
+      <c r="R118" s="1" t="n">
         <v>43709</v>
       </c>
     </row>
@@ -7364,7 +7352,7 @@
       <c r="Q119" t="n">
         <v>109</v>
       </c>
-      <c r="R119" s="2" t="n">
+      <c r="R119" s="1" t="n">
         <v>43739</v>
       </c>
     </row>
@@ -7422,7 +7410,7 @@
       <c r="Q120" t="n">
         <v>92</v>
       </c>
-      <c r="R120" s="2" t="n">
+      <c r="R120" s="1" t="n">
         <v>43770</v>
       </c>
     </row>
@@ -7480,7 +7468,7 @@
       <c r="Q121" t="n">
         <v>248</v>
       </c>
-      <c r="R121" s="2" t="n">
+      <c r="R121" s="1" t="n">
         <v>43800</v>
       </c>
     </row>
@@ -7538,7 +7526,7 @@
       <c r="Q122" t="n">
         <v>94</v>
       </c>
-      <c r="R122" s="2" t="n">
+      <c r="R122" s="1" t="n">
         <v>43831</v>
       </c>
     </row>
@@ -7596,7 +7584,7 @@
       <c r="Q123" t="n">
         <v>-130</v>
       </c>
-      <c r="R123" s="2" t="n">
+      <c r="R123" s="1" t="n">
         <v>43862</v>
       </c>
     </row>
@@ -7654,7 +7642,7 @@
       <c r="Q124" t="n">
         <v>-266</v>
       </c>
-      <c r="R124" s="2" t="n">
+      <c r="R124" s="1" t="n">
         <v>43891</v>
       </c>
     </row>
@@ -7712,7 +7700,7 @@
       <c r="Q125" t="n">
         <v>40</v>
       </c>
-      <c r="R125" s="2" t="n">
+      <c r="R125" s="1" t="n">
         <v>43922</v>
       </c>
     </row>
@@ -7770,7 +7758,7 @@
       <c r="Q126" t="n">
         <v>-35</v>
       </c>
-      <c r="R126" s="2" t="n">
+      <c r="R126" s="1" t="n">
         <v>43952</v>
       </c>
     </row>
@@ -7828,7 +7816,7 @@
       <c r="Q127" t="n">
         <v>-60</v>
       </c>
-      <c r="R127" s="2" t="n">
+      <c r="R127" s="1" t="n">
         <v>43983</v>
       </c>
     </row>
@@ -7886,7 +7874,7 @@
       <c r="Q128" t="n">
         <v>85</v>
       </c>
-      <c r="R128" s="2" t="n">
+      <c r="R128" s="1" t="n">
         <v>44013</v>
       </c>
     </row>
@@ -7944,7 +7932,7 @@
       <c r="Q129" t="n">
         <v>150</v>
       </c>
-      <c r="R129" s="2" t="n">
+      <c r="R129" s="1" t="n">
         <v>44044</v>
       </c>
     </row>
@@ -8002,7 +7990,7 @@
       <c r="Q130" t="n">
         <v>206</v>
       </c>
-      <c r="R130" s="2" t="n">
+      <c r="R130" s="1" t="n">
         <v>44075</v>
       </c>
     </row>
@@ -8060,7 +8048,7 @@
       <c r="Q131" t="n">
         <v>-23</v>
       </c>
-      <c r="R131" s="2" t="n">
+      <c r="R131" s="1" t="n">
         <v>44105</v>
       </c>
     </row>
@@ -8118,7 +8106,7 @@
       <c r="Q132" t="n">
         <v>174</v>
       </c>
-      <c r="R132" s="2" t="n">
+      <c r="R132" s="1" t="n">
         <v>44136</v>
       </c>
     </row>
@@ -8176,7 +8164,7 @@
       <c r="Q133" t="n">
         <v>-34</v>
       </c>
-      <c r="R133" s="2" t="n">
+      <c r="R133" s="1" t="n">
         <v>44166</v>
       </c>
     </row>
@@ -8234,7 +8222,7 @@
       <c r="Q134" t="n">
         <v>44</v>
       </c>
-      <c r="R134" s="2" t="n">
+      <c r="R134" s="1" t="n">
         <v>44197</v>
       </c>
     </row>
@@ -8292,7 +8280,7 @@
       <c r="Q135" t="n">
         <v>146</v>
       </c>
-      <c r="R135" s="2" t="n">
+      <c r="R135" s="1" t="n">
         <v>44228</v>
       </c>
     </row>
@@ -8350,7 +8338,7 @@
       <c r="Q136" t="n">
         <v>44</v>
       </c>
-      <c r="R136" s="2" t="n">
+      <c r="R136" s="1" t="n">
         <v>44256</v>
       </c>
     </row>
@@ -8408,7 +8396,7 @@
       <c r="Q137" t="n">
         <v>282</v>
       </c>
-      <c r="R137" s="2" t="n">
+      <c r="R137" s="1" t="n">
         <v>44287</v>
       </c>
     </row>
@@ -8466,7 +8454,7 @@
       <c r="Q138" t="n">
         <v>152</v>
       </c>
-      <c r="R138" s="2" t="n">
+      <c r="R138" s="1" t="n">
         <v>44317</v>
       </c>
     </row>
@@ -8524,7 +8512,7 @@
       <c r="Q139" t="n">
         <v>-23</v>
       </c>
-      <c r="R139" s="2" t="n">
+      <c r="R139" s="1" t="n">
         <v>44348</v>
       </c>
     </row>
@@ -8582,7 +8570,7 @@
       <c r="Q140" t="n">
         <v>53</v>
       </c>
-      <c r="R140" s="2" t="n">
+      <c r="R140" s="1" t="n">
         <v>44378</v>
       </c>
     </row>
@@ -8640,7 +8628,7 @@
       <c r="Q141" t="n">
         <v>81</v>
       </c>
-      <c r="R141" s="2" t="n">
+      <c r="R141" s="1" t="n">
         <v>44409</v>
       </c>
     </row>
@@ -8698,7 +8686,7 @@
       <c r="Q142" t="n">
         <v>50</v>
       </c>
-      <c r="R142" s="2" t="n">
+      <c r="R142" s="1" t="n">
         <v>44440</v>
       </c>
     </row>
@@ -8756,7 +8744,7 @@
       <c r="Q143" t="n">
         <v>115</v>
       </c>
-      <c r="R143" s="2" t="n">
+      <c r="R143" s="1" t="n">
         <v>44470</v>
       </c>
     </row>
@@ -8814,7 +8802,7 @@
       <c r="Q144" t="n">
         <v>-106</v>
       </c>
-      <c r="R144" s="2" t="n">
+      <c r="R144" s="1" t="n">
         <v>44501</v>
       </c>
     </row>
@@ -8872,7 +8860,7 @@
       <c r="Q145" t="n">
         <v>112</v>
       </c>
-      <c r="R145" s="2" t="n">
+      <c r="R145" s="1" t="n">
         <v>44531</v>
       </c>
     </row>
@@ -8930,7 +8918,7 @@
       <c r="Q146" t="n">
         <v>-158</v>
       </c>
-      <c r="R146" s="2" t="n">
+      <c r="R146" s="1" t="n">
         <v>44562</v>
       </c>
     </row>
@@ -8988,7 +8976,7 @@
       <c r="Q147" t="n">
         <v>-43</v>
       </c>
-      <c r="R147" s="2" t="n">
+      <c r="R147" s="1" t="n">
         <v>44593</v>
       </c>
     </row>
@@ -9046,7 +9034,7 @@
       <c r="Q148" t="n">
         <v>-190</v>
       </c>
-      <c r="R148" s="2" t="n">
+      <c r="R148" s="1" t="n">
         <v>44621</v>
       </c>
     </row>
@@ -9104,7 +9092,7 @@
       <c r="Q149" t="n">
         <v>-107</v>
       </c>
-      <c r="R149" s="2" t="n">
+      <c r="R149" s="1" t="n">
         <v>44652</v>
       </c>
     </row>
@@ -9162,7 +9150,7 @@
       <c r="Q150" t="n">
         <v>-92</v>
       </c>
-      <c r="R150" s="2" t="n">
+      <c r="R150" s="1" t="n">
         <v>44682</v>
       </c>
     </row>
@@ -9220,7 +9208,7 @@
       <c r="Q151" t="n">
         <v>-123</v>
       </c>
-      <c r="R151" s="2" t="n">
+      <c r="R151" s="1" t="n">
         <v>44713</v>
       </c>
     </row>
@@ -9278,7 +9266,7 @@
       <c r="Q152" t="n">
         <v>60</v>
       </c>
-      <c r="R152" s="2" t="n">
+      <c r="R152" s="1" t="n">
         <v>44743</v>
       </c>
     </row>
@@ -9336,7 +9324,7 @@
       <c r="Q153" t="n">
         <v>53</v>
       </c>
-      <c r="R153" s="2" t="n">
+      <c r="R153" s="1" t="n">
         <v>44774</v>
       </c>
     </row>
@@ -9394,7 +9382,7 @@
       <c r="Q154" t="n">
         <v>1</v>
       </c>
-      <c r="R154" s="2" t="n">
+      <c r="R154" s="1" t="n">
         <v>44805</v>
       </c>
     </row>
@@ -9452,7 +9440,7 @@
       <c r="Q155" t="n">
         <v>34</v>
       </c>
-      <c r="R155" s="2" t="n">
+      <c r="R155" s="1" t="n">
         <v>44835</v>
       </c>
     </row>
@@ -9510,7 +9498,7 @@
       <c r="Q156" t="n">
         <v>-15</v>
       </c>
-      <c r="R156" s="2" t="n">
+      <c r="R156" s="1" t="n">
         <v>44866</v>
       </c>
     </row>
@@ -9568,7 +9556,7 @@
       <c r="Q157" t="n">
         <v>211</v>
       </c>
-      <c r="R157" s="2" t="n">
+      <c r="R157" s="1" t="n">
         <v>44896</v>
       </c>
     </row>
@@ -9626,7 +9614,7 @@
       <c r="Q158" t="n">
         <v>-228</v>
       </c>
-      <c r="R158" s="2" t="n">
+      <c r="R158" s="1" t="n">
         <v>44927</v>
       </c>
     </row>
@@ -9684,7 +9672,7 @@
       <c r="Q159" t="n">
         <v>157</v>
       </c>
-      <c r="R159" s="2" t="n">
+      <c r="R159" s="1" t="n">
         <v>44958</v>
       </c>
     </row>
@@ -9742,7 +9730,7 @@
       <c r="Q160" t="n">
         <v>77</v>
       </c>
-      <c r="R160" s="2" t="n">
+      <c r="R160" s="1" t="n">
         <v>44986</v>
       </c>
     </row>
@@ -9800,7 +9788,7 @@
       <c r="Q161" t="n">
         <v>60</v>
       </c>
-      <c r="R161" s="2" t="n">
+      <c r="R161" s="1" t="n">
         <v>45017</v>
       </c>
     </row>
@@ -9858,7 +9846,7 @@
       <c r="Q162" t="n">
         <v>21</v>
       </c>
-      <c r="R162" s="2" t="n">
+      <c r="R162" s="1" t="n">
         <v>45047</v>
       </c>
     </row>
@@ -9916,7 +9904,7 @@
       <c r="Q163" t="n">
         <v>190</v>
       </c>
-      <c r="R163" s="2" t="n">
+      <c r="R163" s="1" t="n">
         <v>45078</v>
       </c>
     </row>
@@ -9974,7 +9962,7 @@
       <c r="Q164" t="n">
         <v>-81</v>
       </c>
-      <c r="R164" s="2" t="n">
+      <c r="R164" s="1" t="n">
         <v>45108</v>
       </c>
     </row>
@@ -10032,7 +10020,7 @@
       <c r="Q165" t="n">
         <v>89</v>
       </c>
-      <c r="R165" s="2" t="n">
+      <c r="R165" s="1" t="n">
         <v>45139</v>
       </c>
     </row>
@@ -10090,7 +10078,7 @@
       <c r="Q166" t="n">
         <v>197</v>
       </c>
-      <c r="R166" s="2" t="n">
+      <c r="R166" s="1" t="n">
         <v>45170</v>
       </c>
     </row>
@@ -10148,7 +10136,7 @@
       <c r="Q167" t="n">
         <v>-53</v>
       </c>
-      <c r="R167" s="2" t="n">
+      <c r="R167" s="1" t="n">
         <v>45200</v>
       </c>
     </row>
@@ -10206,7 +10194,7 @@
       <c r="Q168" t="n">
         <v>-21</v>
       </c>
-      <c r="R168" s="2" t="n">
+      <c r="R168" s="1" t="n">
         <v>45231</v>
       </c>
     </row>
@@ -10264,7 +10252,7 @@
       <c r="Q169" t="n">
         <v>149</v>
       </c>
-      <c r="R169" s="2" t="n">
+      <c r="R169" s="1" t="n">
         <v>45261</v>
       </c>
     </row>
@@ -10322,7 +10310,7 @@
       <c r="Q170" t="n">
         <v>-157</v>
       </c>
-      <c r="R170" s="2" t="n">
+      <c r="R170" s="1" t="n">
         <v>45292</v>
       </c>
     </row>
@@ -10380,7 +10368,7 @@
       <c r="Q171" t="n">
         <v>-123</v>
       </c>
-      <c r="R171" s="2" t="n">
+      <c r="R171" s="1" t="n">
         <v>45323</v>
       </c>
     </row>
@@ -10438,7 +10426,7 @@
       <c r="Q172" t="n">
         <v>-206</v>
       </c>
-      <c r="R172" s="2" t="n">
+      <c r="R172" s="1" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -10496,7 +10484,7 @@
       <c r="Q173" t="n">
         <v>520</v>
       </c>
-      <c r="R173" s="2" t="n">
+      <c r="R173" s="1" t="n">
         <v>45383</v>
       </c>
     </row>
@@ -10554,7 +10542,7 @@
       <c r="Q174" t="n">
         <v>-152</v>
       </c>
-      <c r="R174" s="2" t="n">
+      <c r="R174" s="1" t="n">
         <v>45413</v>
       </c>
     </row>
@@ -10612,7 +10600,7 @@
       <c r="Q175" t="n">
         <v>3</v>
       </c>
-      <c r="R175" s="2" t="n">
+      <c r="R175" s="1" t="n">
         <v>45444</v>
       </c>
     </row>
@@ -10670,7 +10658,7 @@
       <c r="Q176" t="n">
         <v>92</v>
       </c>
-      <c r="R176" s="2" t="n">
+      <c r="R176" s="1" t="n">
         <v>45474</v>
       </c>
     </row>
@@ -10728,7 +10716,7 @@
       <c r="Q177" t="n">
         <v>-5</v>
       </c>
-      <c r="R177" s="2" t="n">
+      <c r="R177" s="1" t="n">
         <v>45505</v>
       </c>
     </row>
@@ -10786,7 +10774,7 @@
       <c r="Q178" t="n">
         <v>-19</v>
       </c>
-      <c r="R178" s="2" t="n">
+      <c r="R178" s="1" t="n">
         <v>45536</v>
       </c>
     </row>
@@ -10844,7 +10832,7 @@
       <c r="Q179" t="n">
         <v>-15</v>
       </c>
-      <c r="R179" s="2" t="n">
+      <c r="R179" s="1" t="n">
         <v>45566</v>
       </c>
     </row>
@@ -10902,7 +10890,7 @@
       <c r="Q180" t="n">
         <v>21</v>
       </c>
-      <c r="R180" s="2" t="n">
+      <c r="R180" s="1" t="n">
         <v>45597</v>
       </c>
     </row>
@@ -10960,7 +10948,7 @@
       <c r="Q181" t="n">
         <v>113</v>
       </c>
-      <c r="R181" s="2" t="n">
+      <c r="R181" s="1" t="n">
         <v>45627</v>
       </c>
     </row>
@@ -11018,7 +11006,7 @@
       <c r="Q182" t="n">
         <v>-154</v>
       </c>
-      <c r="R182" s="2" t="n">
+      <c r="R182" s="1" t="n">
         <v>45658</v>
       </c>
     </row>
@@ -11076,7 +11064,7 @@
       <c r="Q183" t="n">
         <v>8</v>
       </c>
-      <c r="R183" s="2" t="n">
+      <c r="R183" s="1" t="n">
         <v>45689</v>
       </c>
     </row>
@@ -11134,7 +11122,7 @@
       <c r="Q184" t="n">
         <v>-9</v>
       </c>
-      <c r="R184" s="2" t="n">
+      <c r="R184" s="1" t="n">
         <v>45717</v>
       </c>
     </row>
@@ -11192,7 +11180,7 @@
       <c r="Q185" t="n">
         <v>-104</v>
       </c>
-      <c r="R185" s="2" t="n">
+      <c r="R185" s="1" t="n">
         <v>45748</v>
       </c>
     </row>
@@ -11250,7 +11238,7 @@
       <c r="Q186" t="n">
         <v>-25</v>
       </c>
-      <c r="R186" s="2" t="n">
+      <c r="R186" s="1" t="n">
         <v>45778</v>
       </c>
     </row>
@@ -11308,7 +11296,7 @@
       <c r="Q187" t="n">
         <v>-82</v>
       </c>
-      <c r="R187" s="2" t="n">
+      <c r="R187" s="1" t="n">
         <v>45809</v>
       </c>
     </row>
@@ -11366,7 +11354,7 @@
       <c r="Q188" t="n">
         <v>-153</v>
       </c>
-      <c r="R188" s="2" t="n">
+      <c r="R188" s="1" t="n">
         <v>45839</v>
       </c>
     </row>
@@ -11424,7 +11412,7 @@
       <c r="Q189" t="n">
         <v>-21</v>
       </c>
-      <c r="R189" s="2" t="n">
+      <c r="R189" s="1" t="n">
         <v>45870</v>
       </c>
     </row>
@@ -11482,7 +11470,7 @@
       <c r="Q190" t="n">
         <v>89</v>
       </c>
-      <c r="R190" s="2" t="n">
+      <c r="R190" s="1" t="n">
         <v>45901</v>
       </c>
     </row>
@@ -11540,7 +11528,7 @@
       <c r="Q191" t="n">
         <v>-7</v>
       </c>
-      <c r="R191" s="2" t="n">
+      <c r="R191" s="1" t="n">
         <v>45931</v>
       </c>
     </row>
@@ -11598,7 +11586,7 @@
       <c r="Q192" t="n">
         <v>13</v>
       </c>
-      <c r="R192" s="2" t="n">
+      <c r="R192" s="1" t="n">
         <v>45962</v>
       </c>
     </row>
@@ -11656,7 +11644,7 @@
       <c r="Q193" t="n">
         <v>-99</v>
       </c>
-      <c r="R193" s="2" t="n">
+      <c r="R193" s="1" t="n">
         <v>45992</v>
       </c>
     </row>
@@ -11714,7 +11702,7 @@
       <c r="Q194" t="n">
         <v>-314</v>
       </c>
-      <c r="R194" s="2" t="n">
+      <c r="R194" s="1" t="n">
         <v>46023</v>
       </c>
     </row>
@@ -11772,7 +11760,7 @@
       <c r="Q195" t="n">
         <v>-193</v>
       </c>
-      <c r="R195" s="2" t="n">
+      <c r="R195" s="1" t="n">
         <v>46054</v>
       </c>
     </row>
@@ -11830,7 +11818,7 @@
       <c r="Q196" t="n">
         <v>-245</v>
       </c>
-      <c r="R196" s="2" t="n">
+      <c r="R196" s="1" t="n">
         <v>46082</v>
       </c>
     </row>
@@ -11888,7 +11876,7 @@
       <c r="Q197" t="n">
         <v>-143</v>
       </c>
-      <c r="R197" s="2" t="n">
+      <c r="R197" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -11946,7 +11934,7 @@
       <c r="Q198" t="n">
         <v>-164</v>
       </c>
-      <c r="R198" s="2" t="n">
+      <c r="R198" s="1" t="n">
         <v>46143</v>
       </c>
     </row>
@@ -12004,7 +11992,7 @@
       <c r="Q199" t="n">
         <v>-729</v>
       </c>
-      <c r="R199" s="2" t="n">
+      <c r="R199" s="1" t="n">
         <v>46174</v>
       </c>
     </row>
@@ -12062,7 +12050,7 @@
       <c r="Q200" t="n">
         <v>-68</v>
       </c>
-      <c r="R200" s="2" t="n">
+      <c r="R200" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -12120,7 +12108,7 @@
       <c r="Q201" t="n">
         <v>-18</v>
       </c>
-      <c r="R201" s="2" t="n">
+      <c r="R201" s="1" t="n">
         <v>46235</v>
       </c>
     </row>
